--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>226185</v>
+        <v>285434</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>48873.16</v>
+        <v>1653</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>177311.84</v>
+        <v>283781</v>
       </c>
       <c r="I2" t="n">
-        <v>176293</v>
+        <v>282744</v>
       </c>
       <c r="J2" t="n">
-        <v>1018</v>
+        <v>1037</v>
       </c>
       <c r="K2" t="n">
-        <v>167311</v>
+        <v>273781</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2374</v>
+        <v>1981</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -539,24 +539,24 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>17617</v>
+        <v>1357</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>742.1%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-15243</v>
+        <v>624</v>
       </c>
       <c r="I3" t="n">
-        <v>-15378</v>
+        <v>489</v>
       </c>
       <c r="J3" t="n">
         <v>135</v>
       </c>
       <c r="K3" t="n">
-        <v>-5243</v>
+        <v>624</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>283989.12</v>
+        <v>299447.84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>85383</v>
+        <v>8006</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>198606.12</v>
+        <v>291441.84</v>
       </c>
       <c r="I4" t="n">
-        <v>204946</v>
+        <v>285430</v>
       </c>
       <c r="J4" t="n">
-        <v>-6340</v>
+        <v>6010</v>
       </c>
       <c r="K4" t="n">
-        <v>207718</v>
+        <v>266655</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>88050</v>
+        <v>132197</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>123069.9</v>
+        <v>162</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>139.8%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-35019.89999999999</v>
+        <v>132035</v>
       </c>
       <c r="I5" t="n">
-        <v>-36407</v>
+        <v>88647</v>
       </c>
       <c r="J5" t="n">
-        <v>1388</v>
+        <v>43388</v>
       </c>
       <c r="K5" t="n">
-        <v>-35019</v>
+        <v>93215</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>282837.46</v>
+        <v>359335.46</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>31751.9</v>
+        <v>6442.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>1.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>251085.56</v>
+        <v>352892.5599999999</v>
       </c>
       <c r="I6" t="n">
-        <v>247266</v>
+        <v>345985</v>
       </c>
       <c r="J6" t="n">
-        <v>3819</v>
+        <v>6907</v>
       </c>
       <c r="K6" t="n">
-        <v>196289</v>
+        <v>285100</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>204887</v>
+        <v>231947</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>31890</v>
+        <v>31441</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>172997</v>
+        <v>200506</v>
       </c>
       <c r="I7" t="n">
-        <v>143178</v>
+        <v>198807</v>
       </c>
       <c r="J7" t="n">
-        <v>29819</v>
+        <v>1699</v>
       </c>
       <c r="K7" t="n">
-        <v>81083</v>
+        <v>94092</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>194751.62</v>
+        <v>206042.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>71584</v>
+        <v>2687</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>123167.62</v>
+        <v>203355.62</v>
       </c>
       <c r="I8" t="n">
-        <v>152130</v>
+        <v>202518</v>
       </c>
       <c r="J8" t="n">
-        <v>-28963</v>
+        <v>837</v>
       </c>
       <c r="K8" t="n">
-        <v>112769</v>
+        <v>182957</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>467449.36</v>
+        <v>534687.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>139000</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>328449.36</v>
+        <v>534687.36</v>
       </c>
       <c r="I9" t="n">
-        <v>222169</v>
+        <v>424207</v>
       </c>
       <c r="J9" t="n">
-        <v>106280</v>
+        <v>110480</v>
       </c>
       <c r="K9" t="n">
-        <v>183971</v>
+        <v>330971</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>559150.6</v>
+        <v>906375.24</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>558851.6</v>
+        <v>906067.24</v>
       </c>
       <c r="I10" t="n">
-        <v>220995</v>
+        <v>340223</v>
       </c>
       <c r="J10" t="n">
-        <v>337856</v>
+        <v>565844</v>
       </c>
       <c r="K10" t="n">
-        <v>508453</v>
+        <v>844475</v>
       </c>
     </row>
     <row r="11">
@@ -875,32 +875,32 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>143231.35</v>
+        <v>143638.35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>26399.98</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>116831.37</v>
+        <v>143638.35</v>
       </c>
       <c r="I11" t="n">
-        <v>18445</v>
+        <v>28854</v>
       </c>
       <c r="J11" t="n">
-        <v>98176</v>
+        <v>114574</v>
       </c>
       <c r="K11" t="n">
-        <v>75651</v>
+        <v>75660</v>
       </c>
     </row>
     <row r="12">
@@ -918,32 +918,32 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>201094</v>
+        <v>281083</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10028</v>
+        <v>57</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>191066</v>
+        <v>281026</v>
       </c>
       <c r="I12" t="n">
-        <v>52699</v>
+        <v>53163</v>
       </c>
       <c r="J12" t="n">
-        <v>138367</v>
+        <v>227863</v>
       </c>
       <c r="K12" t="n">
-        <v>4868</v>
+        <v>19814</v>
       </c>
     </row>
     <row r="13">
@@ -961,32 +961,32 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>211257.18</v>
+        <v>309747.18</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>25908.67</v>
+        <v>394</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>185348.51</v>
+        <v>309353.18</v>
       </c>
       <c r="I13" t="n">
-        <v>17307</v>
+        <v>13947</v>
       </c>
       <c r="J13" t="n">
-        <v>161225</v>
+        <v>288590</v>
       </c>
       <c r="K13" t="n">
-        <v>-3429</v>
+        <v>33879</v>
       </c>
     </row>
     <row r="14">
@@ -1004,32 +1004,32 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>123464.2</v>
+        <v>147271.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>14866</v>
+        <v>67</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>108598.2</v>
+        <v>147204.3</v>
       </c>
       <c r="I14" t="n">
-        <v>49420</v>
+        <v>54766</v>
       </c>
       <c r="J14" t="n">
-        <v>51902</v>
+        <v>82596</v>
       </c>
       <c r="K14" t="n">
-        <v>17020</v>
+        <v>19932</v>
       </c>
     </row>
     <row r="15">
@@ -1047,32 +1047,32 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>77070</v>
+        <v>98100</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>15857</v>
+        <v>38</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>61213</v>
+        <v>98062</v>
       </c>
       <c r="I15" t="n">
-        <v>442</v>
+        <v>6735</v>
       </c>
       <c r="J15" t="n">
-        <v>60771</v>
+        <v>91327</v>
       </c>
       <c r="K15" t="n">
-        <v>27421</v>
+        <v>36480</v>
       </c>
     </row>
     <row r="16">
@@ -1090,32 +1090,32 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>107075</v>
+        <v>197885</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>106677</v>
+        <v>197885</v>
       </c>
       <c r="I16" t="n">
-        <v>12495</v>
+        <v>16715</v>
       </c>
       <c r="J16" t="n">
-        <v>94182</v>
+        <v>181170</v>
       </c>
       <c r="K16" t="n">
-        <v>39693</v>
+        <v>41011</v>
       </c>
     </row>
     <row r="17">
@@ -1133,32 +1133,32 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>192525.4</v>
+        <v>229924.41</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>46658</v>
+        <v>229</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>145867.4</v>
+        <v>229695.41</v>
       </c>
       <c r="I17" t="n">
-        <v>2053</v>
+        <v>3295</v>
       </c>
       <c r="J17" t="n">
-        <v>125082</v>
+        <v>206472</v>
       </c>
       <c r="K17" t="n">
-        <v>-16808</v>
+        <v>20835</v>
       </c>
     </row>
     <row r="18">
@@ -1176,32 +1176,32 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>285737.9</v>
+        <v>632424.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>19666</v>
+        <v>47</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>266071.9</v>
+        <v>632377.9</v>
       </c>
       <c r="I18" t="n">
-        <v>99340</v>
+        <v>188736</v>
       </c>
       <c r="J18" t="n">
-        <v>166731</v>
+        <v>442791</v>
       </c>
       <c r="K18" t="n">
-        <v>148479</v>
+        <v>393977</v>
       </c>
     </row>
     <row r="19">
@@ -1219,15 +1219,15 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>113893.06</v>
+        <v>161943.52</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>113884.06</v>
+        <v>161928.52</v>
       </c>
       <c r="I19" t="n">
-        <v>10376</v>
+        <v>28516</v>
       </c>
       <c r="J19" t="n">
-        <v>100092</v>
+        <v>126392</v>
       </c>
       <c r="K19" t="n">
-        <v>20298</v>
+        <v>24252</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>228790.9</v>
+        <v>250143.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>40737</v>
+        <v>351</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>188053.9</v>
+        <v>249792.9</v>
       </c>
       <c r="I20" t="n">
-        <v>82993</v>
+        <v>91262</v>
       </c>
       <c r="J20" t="n">
-        <v>105060</v>
+        <v>158530</v>
       </c>
       <c r="K20" t="n">
-        <v>31967</v>
+        <v>46016</v>
       </c>
     </row>
     <row r="21">
@@ -1313,24 +1313,24 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>13111</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1809</v>
+        <v>14920</v>
       </c>
       <c r="I21" t="n">
-        <v>-11391</v>
+        <v>1720</v>
       </c>
       <c r="J21" t="n">
         <v>13200</v>
       </c>
       <c r="K21" t="n">
-        <v>-770</v>
+        <v>1720</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -492,28 +492,28 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1653</v>
+        <v>66158.16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>283781</v>
+        <v>219275.84</v>
       </c>
       <c r="I2" t="n">
-        <v>282744</v>
+        <v>218238</v>
       </c>
       <c r="J2" t="n">
         <v>1037</v>
       </c>
       <c r="K2" t="n">
-        <v>273781</v>
+        <v>209275</v>
       </c>
     </row>
     <row r="3">
@@ -539,24 +539,24 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1357</v>
+        <v>17617</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>889.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>624</v>
+        <v>-15636</v>
       </c>
       <c r="I3" t="n">
-        <v>489</v>
+        <v>-15771</v>
       </c>
       <c r="J3" t="n">
         <v>135</v>
       </c>
       <c r="K3" t="n">
-        <v>624</v>
+        <v>-5636</v>
       </c>
     </row>
     <row r="4">
@@ -578,28 +578,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>8006</v>
+        <v>96968</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>291441.84</v>
+        <v>202479.84</v>
       </c>
       <c r="I4" t="n">
-        <v>285430</v>
+        <v>208468</v>
       </c>
       <c r="J4" t="n">
-        <v>6010</v>
+        <v>-5989</v>
       </c>
       <c r="K4" t="n">
-        <v>266655</v>
+        <v>211193</v>
       </c>
     </row>
     <row r="5">
@@ -621,28 +621,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>162</v>
+        <v>136695.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>103.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>132035</v>
+        <v>-4498.899999999994</v>
       </c>
       <c r="I5" t="n">
-        <v>88647</v>
+        <v>-5886</v>
       </c>
       <c r="J5" t="n">
-        <v>43388</v>
+        <v>1388</v>
       </c>
       <c r="K5" t="n">
-        <v>93215</v>
+        <v>-43318</v>
       </c>
     </row>
     <row r="6">
@@ -664,28 +664,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6442.9</v>
+        <v>36387.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>352892.5599999999</v>
+        <v>322947.5599999999</v>
       </c>
       <c r="I6" t="n">
-        <v>345985</v>
+        <v>316040</v>
       </c>
       <c r="J6" t="n">
         <v>6907</v>
       </c>
       <c r="K6" t="n">
-        <v>285100</v>
+        <v>255155</v>
       </c>
     </row>
     <row r="7">
@@ -707,28 +707,28 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>31441</v>
+        <v>62463</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>200506</v>
+        <v>169484</v>
       </c>
       <c r="I7" t="n">
-        <v>198807</v>
+        <v>167785</v>
       </c>
       <c r="J7" t="n">
         <v>1699</v>
       </c>
       <c r="K7" t="n">
-        <v>94092</v>
+        <v>67570</v>
       </c>
     </row>
     <row r="8">
@@ -750,28 +750,28 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2687</v>
+        <v>73425</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>203355.62</v>
+        <v>132617.62</v>
       </c>
       <c r="I8" t="n">
-        <v>202518</v>
+        <v>161580</v>
       </c>
       <c r="J8" t="n">
-        <v>837</v>
+        <v>-28963</v>
       </c>
       <c r="K8" t="n">
-        <v>182957</v>
+        <v>122219</v>
       </c>
     </row>
     <row r="9">
@@ -793,28 +793,28 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>170300</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>534687.36</v>
+        <v>364387.36</v>
       </c>
       <c r="I9" t="n">
-        <v>424207</v>
+        <v>258107</v>
       </c>
       <c r="J9" t="n">
-        <v>110480</v>
+        <v>106280</v>
       </c>
       <c r="K9" t="n">
-        <v>330971</v>
+        <v>194171</v>
       </c>
     </row>
     <row r="10">
@@ -879,25 +879,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>26399.98</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>143638.35</v>
+        <v>117238.37</v>
       </c>
       <c r="I11" t="n">
-        <v>28854</v>
+        <v>18454</v>
       </c>
       <c r="J11" t="n">
-        <v>114574</v>
+        <v>98574</v>
       </c>
       <c r="K11" t="n">
         <v>75660</v>
@@ -922,25 +922,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>57</v>
+        <v>23057</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>281026</v>
+        <v>258026</v>
       </c>
       <c r="I12" t="n">
         <v>53163</v>
       </c>
       <c r="J12" t="n">
-        <v>227863</v>
+        <v>204863</v>
       </c>
       <c r="K12" t="n">
         <v>19814</v>
@@ -965,28 +965,28 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>394</v>
+        <v>25927.67</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>309353.18</v>
+        <v>283819.51</v>
       </c>
       <c r="I13" t="n">
-        <v>13947</v>
+        <v>13899</v>
       </c>
       <c r="J13" t="n">
-        <v>288590</v>
+        <v>263104</v>
       </c>
       <c r="K13" t="n">
-        <v>33879</v>
+        <v>13945</v>
       </c>
     </row>
     <row r="14">
@@ -1008,28 +1008,28 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>67</v>
+        <v>14866</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>147204.3</v>
+        <v>132405.3</v>
       </c>
       <c r="I14" t="n">
-        <v>54766</v>
+        <v>49467</v>
       </c>
       <c r="J14" t="n">
-        <v>82596</v>
+        <v>73096</v>
       </c>
       <c r="K14" t="n">
-        <v>19932</v>
+        <v>19633</v>
       </c>
     </row>
     <row r="15">
@@ -1051,28 +1051,28 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>38</v>
+        <v>15876</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>98062</v>
+        <v>82224</v>
       </c>
       <c r="I15" t="n">
-        <v>6735</v>
+        <v>6697</v>
       </c>
       <c r="J15" t="n">
-        <v>91327</v>
+        <v>75527</v>
       </c>
       <c r="K15" t="n">
-        <v>36480</v>
+        <v>36442</v>
       </c>
     </row>
     <row r="16">
@@ -1094,22 +1094,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>197885</v>
+        <v>197487</v>
       </c>
       <c r="I16" t="n">
-        <v>16715</v>
+        <v>16317</v>
       </c>
       <c r="J16" t="n">
         <v>181170</v>
@@ -1137,28 +1137,28 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>229</v>
+        <v>46658</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>229695.41</v>
+        <v>183266.41</v>
       </c>
       <c r="I17" t="n">
-        <v>3295</v>
+        <v>3266</v>
       </c>
       <c r="J17" t="n">
-        <v>206472</v>
+        <v>160072</v>
       </c>
       <c r="K17" t="n">
-        <v>20835</v>
+        <v>-15593</v>
       </c>
     </row>
     <row r="18">
@@ -1180,28 +1180,28 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>47</v>
+        <v>19675</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>632377.9</v>
+        <v>612749.9</v>
       </c>
       <c r="I18" t="n">
-        <v>188736</v>
+        <v>188708</v>
       </c>
       <c r="J18" t="n">
-        <v>442791</v>
+        <v>423191</v>
       </c>
       <c r="K18" t="n">
-        <v>393977</v>
+        <v>393949</v>
       </c>
     </row>
     <row r="19">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>161928.52</v>
+        <v>161919.52</v>
       </c>
       <c r="I19" t="n">
-        <v>28516</v>
+        <v>28507</v>
       </c>
       <c r="J19" t="n">
         <v>126392</v>
       </c>
       <c r="K19" t="n">
-        <v>24252</v>
+        <v>24243</v>
       </c>
     </row>
     <row r="20">
@@ -1266,28 +1266,28 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>351</v>
+        <v>40832</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>249792.9</v>
+        <v>209311.9</v>
       </c>
       <c r="I20" t="n">
-        <v>91262</v>
+        <v>85081</v>
       </c>
       <c r="J20" t="n">
-        <v>158530</v>
+        <v>124230</v>
       </c>
       <c r="K20" t="n">
-        <v>46016</v>
+        <v>36035</v>
       </c>
     </row>
     <row r="21">
@@ -1313,24 +1313,24 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>13111</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>14920</v>
+        <v>1809</v>
       </c>
       <c r="I21" t="n">
-        <v>1720</v>
+        <v>-11391</v>
       </c>
       <c r="J21" t="n">
         <v>13200</v>
       </c>
       <c r="K21" t="n">
-        <v>1720</v>
+        <v>-770</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>285434</v>
+        <v>299635</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>66158.16</v>
+        <v>76730.16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>219275.84</v>
+        <v>222904.84</v>
       </c>
       <c r="I2" t="n">
-        <v>218238</v>
+        <v>221818</v>
       </c>
       <c r="J2" t="n">
-        <v>1037</v>
+        <v>1086</v>
       </c>
       <c r="K2" t="n">
-        <v>209275</v>
+        <v>212506</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1981</v>
+        <v>2000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -543,20 +543,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>889.3%</t>
+          <t>880.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-15636</v>
+        <v>-15617</v>
       </c>
       <c r="I3" t="n">
-        <v>-15771</v>
+        <v>-15752</v>
       </c>
       <c r="J3" t="n">
         <v>135</v>
       </c>
       <c r="K3" t="n">
-        <v>-5636</v>
+        <v>-5617</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>299447.84</v>
+        <v>382919.84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>36.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>96968</v>
+        <v>102367</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>202479.84</v>
+        <v>280552.84</v>
       </c>
       <c r="I4" t="n">
-        <v>208468</v>
+        <v>286522</v>
       </c>
       <c r="J4" t="n">
-        <v>-5989</v>
+        <v>-5970</v>
       </c>
       <c r="K4" t="n">
-        <v>211193</v>
+        <v>277266</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>132197</v>
+        <v>176035</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>136695.9</v>
+        <v>176695.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>103.4%</t>
+          <t>100.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-4498.899999999994</v>
+        <v>-660.8999999999942</v>
       </c>
       <c r="I5" t="n">
-        <v>-5886</v>
+        <v>-2048</v>
       </c>
       <c r="J5" t="n">
         <v>1388</v>
       </c>
       <c r="K5" t="n">
-        <v>-43318</v>
+        <v>-78300</v>
       </c>
     </row>
     <row r="6">
@@ -660,15 +660,15 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>359335.46</v>
+        <v>370755.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>36387.9</v>
+        <v>37549.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -676,16 +676,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>322947.5599999999</v>
+        <v>333205.5499999999</v>
       </c>
       <c r="I6" t="n">
-        <v>316040</v>
+        <v>326298</v>
       </c>
       <c r="J6" t="n">
         <v>6907</v>
       </c>
       <c r="K6" t="n">
-        <v>255155</v>
+        <v>265413</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>231947</v>
+        <v>253168</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>62463</v>
+        <v>62719</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>169484</v>
+        <v>190449</v>
       </c>
       <c r="I7" t="n">
-        <v>167785</v>
+        <v>188750</v>
       </c>
       <c r="J7" t="n">
         <v>1699</v>
       </c>
       <c r="K7" t="n">
-        <v>67570</v>
+        <v>88535</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>206042.62</v>
+        <v>278809.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>73425</v>
+        <v>73780</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>132617.62</v>
+        <v>205029.62</v>
       </c>
       <c r="I8" t="n">
-        <v>161580</v>
+        <v>233594</v>
       </c>
       <c r="J8" t="n">
-        <v>-28963</v>
+        <v>-28565</v>
       </c>
       <c r="K8" t="n">
-        <v>122219</v>
+        <v>171835</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>534687.36</v>
+        <v>551647.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>170300</v>
+        <v>176900</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>364387.36</v>
+        <v>374747.36</v>
       </c>
       <c r="I9" t="n">
-        <v>258107</v>
+        <v>261507</v>
       </c>
       <c r="J9" t="n">
-        <v>106280</v>
+        <v>113240</v>
       </c>
       <c r="K9" t="n">
-        <v>194171</v>
+        <v>194531</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>906375.24</v>
+        <v>920186.24</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>308</v>
+        <v>1308</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>906067.24</v>
+        <v>918878.24</v>
       </c>
       <c r="I10" t="n">
-        <v>340223</v>
+        <v>364346</v>
       </c>
       <c r="J10" t="n">
-        <v>565844</v>
+        <v>554532</v>
       </c>
       <c r="K10" t="n">
-        <v>844475</v>
+        <v>857490</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>143638.35</v>
+        <v>157851.35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>117238.37</v>
+        <v>131451.37</v>
       </c>
       <c r="I11" t="n">
-        <v>18454</v>
+        <v>18852</v>
       </c>
       <c r="J11" t="n">
-        <v>98574</v>
+        <v>112389</v>
       </c>
       <c r="K11" t="n">
-        <v>75660</v>
+        <v>78479</v>
       </c>
     </row>
     <row r="12">
@@ -918,32 +918,32 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>281083</v>
+        <v>288179</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>23057</v>
+        <v>23076</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>258026</v>
+        <v>265103</v>
       </c>
       <c r="I12" t="n">
-        <v>53163</v>
+        <v>54862</v>
       </c>
       <c r="J12" t="n">
-        <v>204863</v>
+        <v>210241</v>
       </c>
       <c r="K12" t="n">
-        <v>19814</v>
+        <v>26493</v>
       </c>
     </row>
     <row r="13">
@@ -961,32 +961,32 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>309747.18</v>
+        <v>326952.78</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>25927.67</v>
+        <v>44927.67</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>13.7%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>283819.51</v>
+        <v>282025.11</v>
       </c>
       <c r="I13" t="n">
-        <v>13899</v>
+        <v>12718</v>
       </c>
       <c r="J13" t="n">
-        <v>263104</v>
+        <v>261984</v>
       </c>
       <c r="K13" t="n">
-        <v>13945</v>
+        <v>16351</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>147271.3</v>
+        <v>137761.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>132405.3</v>
+        <v>122895.3</v>
       </c>
       <c r="I14" t="n">
         <v>49467</v>
       </c>
       <c r="J14" t="n">
-        <v>73096</v>
+        <v>63494</v>
       </c>
       <c r="K14" t="n">
-        <v>19633</v>
+        <v>19725</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>98100</v>
+        <v>98498</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,17 +1059,17 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>82224</v>
+        <v>82622</v>
       </c>
       <c r="I15" t="n">
         <v>6697</v>
       </c>
       <c r="J15" t="n">
-        <v>75527</v>
+        <v>75925</v>
       </c>
       <c r="K15" t="n">
         <v>36442</v>
@@ -1090,32 +1090,32 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>197885</v>
+        <v>215302</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>398</v>
+        <v>9198</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>197487</v>
+        <v>206104</v>
       </c>
       <c r="I16" t="n">
-        <v>16317</v>
+        <v>7536</v>
       </c>
       <c r="J16" t="n">
-        <v>181170</v>
+        <v>198568</v>
       </c>
       <c r="K16" t="n">
-        <v>41011</v>
+        <v>41030</v>
       </c>
     </row>
     <row r="17">
@@ -1133,32 +1133,32 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>229924.41</v>
+        <v>288920.41</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>46658</v>
+        <v>48658</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>183266.41</v>
+        <v>240262.41</v>
       </c>
       <c r="I17" t="n">
-        <v>3266</v>
+        <v>3664</v>
       </c>
       <c r="J17" t="n">
-        <v>160072</v>
+        <v>193670</v>
       </c>
       <c r="K17" t="n">
-        <v>-15593</v>
+        <v>8406</v>
       </c>
     </row>
     <row r="18">
@@ -1176,32 +1176,32 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>632424.9</v>
+        <v>677602.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>19675</v>
+        <v>26275</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>612749.9</v>
+        <v>651327.9</v>
       </c>
       <c r="I18" t="n">
-        <v>188708</v>
+        <v>210706</v>
       </c>
       <c r="J18" t="n">
-        <v>423191</v>
+        <v>439771</v>
       </c>
       <c r="K18" t="n">
-        <v>393949</v>
+        <v>395929</v>
       </c>
     </row>
     <row r="19">
@@ -1219,11 +1219,11 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>161943.52</v>
+        <v>193126.13</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>161919.52</v>
+        <v>193102.13</v>
       </c>
       <c r="I19" t="n">
-        <v>28507</v>
+        <v>28227</v>
       </c>
       <c r="J19" t="n">
-        <v>126392</v>
+        <v>157492</v>
       </c>
       <c r="K19" t="n">
-        <v>24243</v>
+        <v>24326</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>250143.9</v>
+        <v>260702.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>40832</v>
+        <v>40870</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>209311.9</v>
+        <v>219832.9</v>
       </c>
       <c r="I20" t="n">
-        <v>85081</v>
+        <v>85204</v>
       </c>
       <c r="J20" t="n">
-        <v>124230</v>
+        <v>134628</v>
       </c>
       <c r="K20" t="n">
-        <v>36035</v>
+        <v>36158</v>
       </c>
     </row>
     <row r="21">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>299635</v>
+        <v>311994</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>76730.16</v>
+        <v>81919.16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>222904.84</v>
+        <v>230074.84</v>
       </c>
       <c r="I2" t="n">
-        <v>221818</v>
+        <v>233968</v>
       </c>
       <c r="J2" t="n">
-        <v>1086</v>
+        <v>-3894</v>
       </c>
       <c r="K2" t="n">
-        <v>212506</v>
+        <v>219676</v>
       </c>
     </row>
     <row r="3">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>382919.84</v>
+        <v>447037.84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>36.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>102367</v>
+        <v>109639</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>280552.84</v>
+        <v>337398.84</v>
       </c>
       <c r="I4" t="n">
-        <v>286522</v>
+        <v>323667</v>
       </c>
       <c r="J4" t="n">
-        <v>-5970</v>
+        <v>13730</v>
       </c>
       <c r="K4" t="n">
-        <v>277266</v>
+        <v>314112</v>
       </c>
     </row>
     <row r="5">
@@ -617,7 +617,7 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>176035</v>
+        <v>176054</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-660.8999999999942</v>
+        <v>-641.8999999999942</v>
       </c>
       <c r="I5" t="n">
-        <v>-2048</v>
+        <v>-2029</v>
       </c>
       <c r="J5" t="n">
         <v>1388</v>
       </c>
       <c r="K5" t="n">
-        <v>-78300</v>
+        <v>-78281</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>370755.45</v>
+        <v>377840.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>37549.9</v>
+        <v>38414.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>333205.5499999999</v>
+        <v>339425.5499999999</v>
       </c>
       <c r="I6" t="n">
-        <v>326298</v>
+        <v>332499</v>
       </c>
       <c r="J6" t="n">
-        <v>6907</v>
+        <v>6926</v>
       </c>
       <c r="K6" t="n">
-        <v>265413</v>
+        <v>271633</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>253168</v>
+        <v>276079.99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>62719</v>
+        <v>62823</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>190449</v>
+        <v>213256.99</v>
       </c>
       <c r="I7" t="n">
-        <v>188750</v>
+        <v>211557</v>
       </c>
       <c r="J7" t="n">
         <v>1699</v>
       </c>
       <c r="K7" t="n">
-        <v>88535</v>
+        <v>103542</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>278809.62</v>
+        <v>302771.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>73780</v>
+        <v>78005</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>205029.62</v>
+        <v>224766.62</v>
       </c>
       <c r="I8" t="n">
-        <v>233594</v>
+        <v>243371</v>
       </c>
       <c r="J8" t="n">
-        <v>-28565</v>
+        <v>-18605</v>
       </c>
       <c r="K8" t="n">
-        <v>171835</v>
+        <v>191572</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>551647.36</v>
+        <v>598562.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>176900</v>
+        <v>215700</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>374747.36</v>
+        <v>382862.36</v>
       </c>
       <c r="I9" t="n">
-        <v>261507</v>
+        <v>269622</v>
       </c>
       <c r="J9" t="n">
         <v>113240</v>
       </c>
       <c r="K9" t="n">
-        <v>194531</v>
+        <v>193248</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>920186.24</v>
+        <v>931293.24</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1308</v>
+        <v>11308</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>918878.24</v>
+        <v>919985.24</v>
       </c>
       <c r="I10" t="n">
-        <v>364346</v>
+        <v>364744</v>
       </c>
       <c r="J10" t="n">
-        <v>554532</v>
+        <v>555241</v>
       </c>
       <c r="K10" t="n">
-        <v>857490</v>
+        <v>868597</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>157851.35</v>
+        <v>170748.35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>131451.37</v>
+        <v>144348.37</v>
       </c>
       <c r="I11" t="n">
-        <v>18852</v>
+        <v>19749</v>
       </c>
       <c r="J11" t="n">
-        <v>112389</v>
+        <v>124389</v>
       </c>
       <c r="K11" t="n">
-        <v>78479</v>
+        <v>78778</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>288179</v>
+        <v>323995</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>265103</v>
+        <v>300919</v>
       </c>
       <c r="I12" t="n">
-        <v>54862</v>
+        <v>55260</v>
       </c>
       <c r="J12" t="n">
-        <v>210241</v>
+        <v>245659</v>
       </c>
       <c r="K12" t="n">
-        <v>26493</v>
+        <v>21513</v>
       </c>
     </row>
     <row r="13">
@@ -961,32 +961,32 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>326952.78</v>
+        <v>331040.18</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>44927.67</v>
+        <v>44984.67</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>282025.11</v>
+        <v>286055.51</v>
       </c>
       <c r="I13" t="n">
-        <v>12718</v>
+        <v>11909</v>
       </c>
       <c r="J13" t="n">
-        <v>261984</v>
+        <v>265958</v>
       </c>
       <c r="K13" t="n">
-        <v>16351</v>
+        <v>19187</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>137761.3</v>
+        <v>139203.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>122895.3</v>
+        <v>124337.3</v>
       </c>
       <c r="I14" t="n">
-        <v>49467</v>
+        <v>39913</v>
       </c>
       <c r="J14" t="n">
-        <v>63494</v>
+        <v>74490</v>
       </c>
       <c r="K14" t="n">
-        <v>19725</v>
+        <v>19773</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>98498</v>
+        <v>98915</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1063,16 +1063,16 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>82622</v>
+        <v>83039</v>
       </c>
       <c r="I15" t="n">
-        <v>6697</v>
+        <v>6716</v>
       </c>
       <c r="J15" t="n">
-        <v>75925</v>
+        <v>76323</v>
       </c>
       <c r="K15" t="n">
-        <v>36442</v>
+        <v>36461</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>215302</v>
+        <v>227151</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>206104</v>
+        <v>217953</v>
       </c>
       <c r="I16" t="n">
-        <v>7536</v>
+        <v>8968</v>
       </c>
       <c r="J16" t="n">
-        <v>198568</v>
+        <v>208985</v>
       </c>
       <c r="K16" t="n">
-        <v>41030</v>
+        <v>41087</v>
       </c>
     </row>
     <row r="17">
@@ -1133,11 +1133,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>288920.41</v>
+        <v>290874.41</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1145,20 +1145,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>240262.41</v>
+        <v>242216.41</v>
       </c>
       <c r="I17" t="n">
         <v>3664</v>
       </c>
       <c r="J17" t="n">
-        <v>193670</v>
+        <v>195264</v>
       </c>
       <c r="K17" t="n">
-        <v>8406</v>
+        <v>8766</v>
       </c>
     </row>
     <row r="18">
@@ -1176,32 +1176,32 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>677602.9</v>
+        <v>693057.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>26275</v>
+        <v>77975</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>651327.9</v>
+        <v>615082.9</v>
       </c>
       <c r="I18" t="n">
-        <v>210706</v>
+        <v>215263</v>
       </c>
       <c r="J18" t="n">
-        <v>439771</v>
+        <v>398969</v>
       </c>
       <c r="K18" t="n">
-        <v>395929</v>
+        <v>364786</v>
       </c>
     </row>
     <row r="19">
@@ -1219,15 +1219,15 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>193126.13</v>
+        <v>183516.83</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>193102.13</v>
+        <v>183454.83</v>
       </c>
       <c r="I19" t="n">
-        <v>28227</v>
+        <v>28507</v>
       </c>
       <c r="J19" t="n">
-        <v>157492</v>
+        <v>147492</v>
       </c>
       <c r="K19" t="n">
-        <v>24326</v>
+        <v>24678</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>260702.9</v>
+        <v>263428.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>40870</v>
+        <v>47926</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>219832.9</v>
+        <v>215502.9</v>
       </c>
       <c r="I20" t="n">
-        <v>85204</v>
+        <v>85780</v>
       </c>
       <c r="J20" t="n">
-        <v>134628</v>
+        <v>129722</v>
       </c>
       <c r="K20" t="n">
-        <v>36158</v>
+        <v>36336</v>
       </c>
     </row>
     <row r="21">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>311994</v>
+        <v>317655.21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>81919.16</v>
+        <v>134066.16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>230074.84</v>
+        <v>183589.05</v>
       </c>
       <c r="I2" t="n">
-        <v>233968</v>
+        <v>187184</v>
       </c>
       <c r="J2" t="n">
-        <v>-3894</v>
+        <v>-3595</v>
       </c>
       <c r="K2" t="n">
-        <v>219676</v>
+        <v>184391</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2000</v>
+        <v>2019</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -543,20 +543,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>880.9%</t>
+          <t>872.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-15617</v>
+        <v>-15598</v>
       </c>
       <c r="I3" t="n">
-        <v>-15752</v>
+        <v>-15733</v>
       </c>
       <c r="J3" t="n">
         <v>135</v>
       </c>
       <c r="K3" t="n">
-        <v>-5617</v>
+        <v>-5598</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>447037.84</v>
+        <v>474893.84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>109639</v>
+        <v>124529</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>337398.84</v>
+        <v>350364.84</v>
       </c>
       <c r="I4" t="n">
-        <v>323667</v>
+        <v>342133</v>
       </c>
       <c r="J4" t="n">
-        <v>13730</v>
+        <v>8230</v>
       </c>
       <c r="K4" t="n">
-        <v>314112</v>
+        <v>332578</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>176054</v>
+        <v>224419</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>176695.9</v>
+        <v>189822.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>100.4%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-641.8999999999942</v>
+        <v>34596.10000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-2029</v>
+        <v>29408</v>
       </c>
       <c r="J5" t="n">
-        <v>1388</v>
+        <v>5188</v>
       </c>
       <c r="K5" t="n">
-        <v>-78281</v>
+        <v>-85563</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>377840.45</v>
+        <v>381749.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>38414.9</v>
+        <v>44245.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>339425.5499999999</v>
+        <v>337503.5499999999</v>
       </c>
       <c r="I6" t="n">
-        <v>332499</v>
+        <v>330577</v>
       </c>
       <c r="J6" t="n">
         <v>6926</v>
       </c>
       <c r="K6" t="n">
-        <v>271633</v>
+        <v>269740</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>276079.99</v>
+        <v>277672.99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>62823</v>
+        <v>77690</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>213256.99</v>
+        <v>199982.99</v>
       </c>
       <c r="I7" t="n">
-        <v>211557</v>
+        <v>198264</v>
       </c>
       <c r="J7" t="n">
-        <v>1699</v>
+        <v>1718</v>
       </c>
       <c r="K7" t="n">
-        <v>103542</v>
+        <v>105088</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>302771.62</v>
+        <v>306180.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>78005</v>
+        <v>78238</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>224766.62</v>
+        <v>227942.62</v>
       </c>
       <c r="I8" t="n">
-        <v>243371</v>
+        <v>246547</v>
       </c>
       <c r="J8" t="n">
         <v>-18605</v>
       </c>
       <c r="K8" t="n">
-        <v>191572</v>
+        <v>194748</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>598562.36</v>
+        <v>698349.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>215700</v>
+        <v>258700</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>382862.36</v>
+        <v>439649.36</v>
       </c>
       <c r="I9" t="n">
-        <v>269622</v>
+        <v>304409</v>
       </c>
       <c r="J9" t="n">
-        <v>113240</v>
+        <v>135240</v>
       </c>
       <c r="K9" t="n">
-        <v>193248</v>
+        <v>151997</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>931293.24</v>
+        <v>1008367.24</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -844,20 +844,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>919985.24</v>
+        <v>997059.24</v>
       </c>
       <c r="I10" t="n">
-        <v>364744</v>
+        <v>372293</v>
       </c>
       <c r="J10" t="n">
-        <v>555241</v>
+        <v>624766</v>
       </c>
       <c r="K10" t="n">
-        <v>868597</v>
+        <v>935671</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>170748.35</v>
+        <v>171155.35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>144348.37</v>
+        <v>144755.37</v>
       </c>
       <c r="I11" t="n">
-        <v>19749</v>
+        <v>19758</v>
       </c>
       <c r="J11" t="n">
-        <v>124389</v>
+        <v>124787</v>
       </c>
       <c r="K11" t="n">
-        <v>78778</v>
+        <v>78787</v>
       </c>
     </row>
     <row r="12">
@@ -918,32 +918,32 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>323995</v>
+        <v>330614</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>23076</v>
+        <v>30076</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>300919</v>
+        <v>300538</v>
       </c>
       <c r="I12" t="n">
-        <v>55260</v>
+        <v>61879</v>
       </c>
       <c r="J12" t="n">
-        <v>245659</v>
+        <v>238659</v>
       </c>
       <c r="K12" t="n">
-        <v>21513</v>
+        <v>28132</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>331040.18</v>
+        <v>390798.18</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>286055.51</v>
+        <v>345813.51</v>
       </c>
       <c r="I13" t="n">
         <v>11909</v>
       </c>
       <c r="J13" t="n">
-        <v>265958</v>
+        <v>325156</v>
       </c>
       <c r="K13" t="n">
-        <v>19187</v>
+        <v>66547</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>139203.3</v>
+        <v>166999.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>124337.3</v>
+        <v>152133.3</v>
       </c>
       <c r="I14" t="n">
-        <v>39913</v>
+        <v>40511</v>
       </c>
       <c r="J14" t="n">
-        <v>74490</v>
+        <v>101688</v>
       </c>
       <c r="K14" t="n">
-        <v>19773</v>
+        <v>26373</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>98915</v>
+        <v>99313</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,14 +1059,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>83039</v>
+        <v>83437</v>
       </c>
       <c r="I15" t="n">
-        <v>6716</v>
+        <v>7114</v>
       </c>
       <c r="J15" t="n">
         <v>76323</v>
@@ -1090,29 +1090,29 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>227151</v>
+        <v>227549</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>9198</v>
+        <v>18398</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>217953</v>
+        <v>209151</v>
       </c>
       <c r="I16" t="n">
         <v>8968</v>
       </c>
       <c r="J16" t="n">
-        <v>208985</v>
+        <v>200183</v>
       </c>
       <c r="K16" t="n">
         <v>41087</v>
@@ -1133,32 +1133,32 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>290874.41</v>
+        <v>296969.41</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>48658</v>
+        <v>59158</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>242216.41</v>
+        <v>237811.41</v>
       </c>
       <c r="I17" t="n">
-        <v>3664</v>
+        <v>4361</v>
       </c>
       <c r="J17" t="n">
-        <v>195264</v>
+        <v>190162</v>
       </c>
       <c r="K17" t="n">
-        <v>8766</v>
+        <v>9463</v>
       </c>
     </row>
     <row r="18">
@@ -1176,32 +1176,32 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>693057.9</v>
+        <v>735249.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>77975</v>
+        <v>77994</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>615082.9</v>
+        <v>657255.9</v>
       </c>
       <c r="I18" t="n">
-        <v>215263</v>
+        <v>215642</v>
       </c>
       <c r="J18" t="n">
-        <v>398969</v>
+        <v>440763</v>
       </c>
       <c r="K18" t="n">
-        <v>364786</v>
+        <v>404367</v>
       </c>
     </row>
     <row r="19">
@@ -1219,32 +1219,32 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>183516.83</v>
+        <v>231996.83</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>62</v>
+        <v>361</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>183454.83</v>
+        <v>231635.83</v>
       </c>
       <c r="I19" t="n">
-        <v>28507</v>
+        <v>29888</v>
       </c>
       <c r="J19" t="n">
-        <v>147492</v>
+        <v>194292</v>
       </c>
       <c r="K19" t="n">
-        <v>24678</v>
+        <v>71659</v>
       </c>
     </row>
     <row r="20">
@@ -1262,11 +1262,11 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>263428.9</v>
+        <v>283526.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>215502.9</v>
+        <v>235600.9</v>
       </c>
       <c r="I20" t="n">
-        <v>85780</v>
+        <v>87082</v>
       </c>
       <c r="J20" t="n">
-        <v>129722</v>
+        <v>148518</v>
       </c>
       <c r="K20" t="n">
-        <v>36336</v>
+        <v>36444</v>
       </c>
     </row>
     <row r="21">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -832,11 +832,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1008367.24</v>
+        <v>1073626.42</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>997059.24</v>
+        <v>1062318.42</v>
       </c>
       <c r="I10" t="n">
-        <v>372293</v>
+        <v>426472</v>
       </c>
       <c r="J10" t="n">
-        <v>624766</v>
+        <v>635845</v>
       </c>
       <c r="K10" t="n">
-        <v>935671</v>
+        <v>1000930</v>
       </c>
     </row>
     <row r="11">
@@ -961,11 +961,11 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>390798.18</v>
+        <v>408275.58</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,11 +973,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>345813.51</v>
+        <v>363290.91</v>
       </c>
       <c r="I13" t="n">
         <v>11909</v>
@@ -986,7 +986,7 @@
         <v>325156</v>
       </c>
       <c r="K13" t="n">
-        <v>66547</v>
+        <v>84024</v>
       </c>
     </row>
     <row r="14">
@@ -1133,7 +1133,7 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>296969.41</v>
+        <v>297284.81</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>237811.41</v>
+        <v>238126.81</v>
       </c>
       <c r="I17" t="n">
         <v>4361</v>
@@ -1158,7 +1158,7 @@
         <v>190162</v>
       </c>
       <c r="K17" t="n">
-        <v>9463</v>
+        <v>9778</v>
       </c>
     </row>
     <row r="18">
@@ -1219,11 +1219,11 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>231996.83</v>
+        <v>233196.83</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>231635.83</v>
+        <v>232835.83</v>
       </c>
       <c r="I19" t="n">
         <v>29888</v>
@@ -1244,7 +1244,7 @@
         <v>194292</v>
       </c>
       <c r="K19" t="n">
-        <v>71659</v>
+        <v>72859</v>
       </c>
     </row>
     <row r="20">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>317655.21</v>
+        <v>431274.21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>134066.16</v>
+        <v>134123.16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>183589.05</v>
+        <v>297151.0499999999</v>
       </c>
       <c r="I2" t="n">
-        <v>187184</v>
+        <v>287546</v>
       </c>
       <c r="J2" t="n">
-        <v>-3595</v>
+        <v>9605</v>
       </c>
       <c r="K2" t="n">
-        <v>184391</v>
+        <v>296957</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2019</v>
+        <v>2047</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -543,20 +543,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>872.6%</t>
+          <t>860.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-15598</v>
+        <v>-15570</v>
       </c>
       <c r="I3" t="n">
-        <v>-15733</v>
+        <v>-15705</v>
       </c>
       <c r="J3" t="n">
         <v>135</v>
       </c>
       <c r="K3" t="n">
-        <v>-5598</v>
+        <v>-5570</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>474893.84</v>
+        <v>484315.24</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>124529</v>
+        <v>132703.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>350364.84</v>
+        <v>351611.44</v>
       </c>
       <c r="I4" t="n">
-        <v>342133</v>
+        <v>342856</v>
       </c>
       <c r="J4" t="n">
-        <v>8230</v>
+        <v>8755</v>
       </c>
       <c r="K4" t="n">
-        <v>332578</v>
+        <v>333825</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>224419</v>
+        <v>224496</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>189822.9</v>
+        <v>197822.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>88.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>34596.10000000001</v>
+        <v>26673.10000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>29408</v>
+        <v>21485</v>
       </c>
       <c r="J5" t="n">
         <v>5188</v>
       </c>
       <c r="K5" t="n">
-        <v>-85563</v>
+        <v>-85486</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>381749.45</v>
+        <v>457528.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>44245.9</v>
+        <v>52496.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>337503.5499999999</v>
+        <v>405031.5499999999</v>
       </c>
       <c r="I6" t="n">
-        <v>330577</v>
+        <v>398105</v>
       </c>
       <c r="J6" t="n">
         <v>6926</v>
       </c>
       <c r="K6" t="n">
-        <v>269740</v>
+        <v>337268</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>277672.99</v>
+        <v>311419.99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>77690</v>
+        <v>78062</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>199982.99</v>
+        <v>233357.99</v>
       </c>
       <c r="I7" t="n">
-        <v>198264</v>
+        <v>231639</v>
       </c>
       <c r="J7" t="n">
         <v>1718</v>
       </c>
       <c r="K7" t="n">
-        <v>105088</v>
+        <v>138463</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>306180.62</v>
+        <v>349022.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>78238</v>
+        <v>78580</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>227942.62</v>
+        <v>270442.62</v>
       </c>
       <c r="I8" t="n">
-        <v>246547</v>
+        <v>289047</v>
       </c>
       <c r="J8" t="n">
         <v>-18605</v>
       </c>
       <c r="K8" t="n">
-        <v>194748</v>
+        <v>229248</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>698349.36</v>
+        <v>728727.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>439649.36</v>
+        <v>470027.36</v>
       </c>
       <c r="I9" t="n">
-        <v>304409</v>
+        <v>334189</v>
       </c>
       <c r="J9" t="n">
-        <v>135240</v>
+        <v>135838</v>
       </c>
       <c r="K9" t="n">
-        <v>151997</v>
+        <v>176797</v>
       </c>
     </row>
     <row r="10">
@@ -832,7 +832,7 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1073626.42</v>
+        <v>1073645.42</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1062318.42</v>
+        <v>1062337.42</v>
       </c>
       <c r="I10" t="n">
-        <v>426472</v>
+        <v>426491</v>
       </c>
       <c r="J10" t="n">
         <v>635845</v>
       </c>
       <c r="K10" t="n">
-        <v>1000930</v>
+        <v>1000949</v>
       </c>
     </row>
     <row r="11">
@@ -875,29 +875,29 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>171155.35</v>
+        <v>172549.35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>26399.98</v>
+        <v>36399.98</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>144755.37</v>
+        <v>136149.37</v>
       </c>
       <c r="I11" t="n">
-        <v>19758</v>
+        <v>20356</v>
       </c>
       <c r="J11" t="n">
-        <v>124787</v>
+        <v>115583</v>
       </c>
       <c r="K11" t="n">
         <v>78787</v>
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>330614</v>
+        <v>347513</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>300538</v>
+        <v>317437</v>
       </c>
       <c r="I12" t="n">
-        <v>61879</v>
+        <v>62178</v>
       </c>
       <c r="J12" t="n">
-        <v>238659</v>
+        <v>255259</v>
       </c>
       <c r="K12" t="n">
-        <v>28132</v>
+        <v>35031</v>
       </c>
     </row>
     <row r="13">
@@ -961,32 +961,32 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>408275.58</v>
+        <v>416207.98</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>44984.67</v>
+        <v>45013.67</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>363290.91</v>
+        <v>371194.31</v>
       </c>
       <c r="I13" t="n">
-        <v>11909</v>
+        <v>12661</v>
       </c>
       <c r="J13" t="n">
-        <v>325156</v>
+        <v>332156</v>
       </c>
       <c r="K13" t="n">
-        <v>84024</v>
+        <v>91530</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>166999.3</v>
+        <v>192199.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,17 +1016,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>152133.3</v>
+        <v>177333.3</v>
       </c>
       <c r="I14" t="n">
         <v>40511</v>
       </c>
       <c r="J14" t="n">
-        <v>101688</v>
+        <v>126888</v>
       </c>
       <c r="K14" t="n">
         <v>26373</v>
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>99313</v>
+        <v>100210</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>83437</v>
+        <v>84334</v>
       </c>
       <c r="I15" t="n">
-        <v>7114</v>
+        <v>7613</v>
       </c>
       <c r="J15" t="n">
-        <v>76323</v>
+        <v>76721</v>
       </c>
       <c r="K15" t="n">
-        <v>36461</v>
+        <v>36960</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>227549</v>
+        <v>239947</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,17 +1102,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>209151</v>
+        <v>221549</v>
       </c>
       <c r="I16" t="n">
-        <v>8968</v>
+        <v>9366</v>
       </c>
       <c r="J16" t="n">
-        <v>200183</v>
+        <v>212183</v>
       </c>
       <c r="K16" t="n">
         <v>41087</v>
@@ -1133,32 +1133,32 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>297284.81</v>
+        <v>327376.81</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>59158</v>
+        <v>88491.39999999999</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>238126.81</v>
+        <v>238885.41</v>
       </c>
       <c r="I17" t="n">
-        <v>4361</v>
+        <v>6055</v>
       </c>
       <c r="J17" t="n">
-        <v>190162</v>
+        <v>189226</v>
       </c>
       <c r="K17" t="n">
-        <v>9778</v>
+        <v>11870</v>
       </c>
     </row>
     <row r="18">
@@ -1176,32 +1176,32 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>735249.9</v>
+        <v>789443.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>77994</v>
+        <v>84494</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>657255.9</v>
+        <v>704949.9</v>
       </c>
       <c r="I18" t="n">
-        <v>215642</v>
+        <v>216040</v>
       </c>
       <c r="J18" t="n">
-        <v>440763</v>
+        <v>488059</v>
       </c>
       <c r="K18" t="n">
-        <v>404367</v>
+        <v>409347</v>
       </c>
     </row>
     <row r="19">
@@ -1219,11 +1219,11 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>233196.83</v>
+        <v>254472.83</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1231,20 +1231,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>232835.83</v>
+        <v>254111.83</v>
       </c>
       <c r="I19" t="n">
-        <v>29888</v>
+        <v>35266</v>
       </c>
       <c r="J19" t="n">
-        <v>194292</v>
+        <v>210190</v>
       </c>
       <c r="K19" t="n">
-        <v>72859</v>
+        <v>77839</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>283526.9</v>
+        <v>307469.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>47926</v>
+        <v>48215</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>235600.9</v>
+        <v>259254.9</v>
       </c>
       <c r="I20" t="n">
-        <v>87082</v>
+        <v>86736</v>
       </c>
       <c r="J20" t="n">
-        <v>148518</v>
+        <v>172518</v>
       </c>
       <c r="K20" t="n">
-        <v>36444</v>
+        <v>36098</v>
       </c>
     </row>
     <row r="21">
@@ -1313,18 +1313,18 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>13111</v>
+        <v>18111</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>121.4%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1809</v>
+        <v>-3191</v>
       </c>
       <c r="I21" t="n">
-        <v>-11391</v>
+        <v>-16391</v>
       </c>
       <c r="J21" t="n">
         <v>13200</v>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>431274.21</v>
+        <v>455793.21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>134123.16</v>
+        <v>135997.16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>297151.0499999999</v>
+        <v>319796.0499999999</v>
       </c>
       <c r="I2" t="n">
-        <v>287546</v>
+        <v>310162</v>
       </c>
       <c r="J2" t="n">
-        <v>9605</v>
+        <v>9634</v>
       </c>
       <c r="K2" t="n">
-        <v>296957</v>
+        <v>318806</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2047</v>
+        <v>2079</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -539,24 +539,24 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>17617</v>
+        <v>17636</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>860.6%</t>
+          <t>848.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-15570</v>
+        <v>-15557</v>
       </c>
       <c r="I3" t="n">
-        <v>-15705</v>
+        <v>-15692</v>
       </c>
       <c r="J3" t="n">
         <v>135</v>
       </c>
       <c r="K3" t="n">
-        <v>-5570</v>
+        <v>-5557</v>
       </c>
     </row>
     <row r="4">
@@ -574,7 +574,7 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>484315.24</v>
+        <v>485207.14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -582,24 +582,24 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>132703.8</v>
+        <v>133581.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>351611.44</v>
+        <v>351625.34</v>
       </c>
       <c r="I4" t="n">
-        <v>342856</v>
+        <v>342638</v>
       </c>
       <c r="J4" t="n">
-        <v>8755</v>
+        <v>8987</v>
       </c>
       <c r="K4" t="n">
-        <v>333825</v>
+        <v>333839</v>
       </c>
     </row>
     <row r="5">
@@ -617,7 +617,7 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>224496</v>
+        <v>224458</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>26673.10000000001</v>
+        <v>26635.10000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>21485</v>
+        <v>21447</v>
       </c>
       <c r="J5" t="n">
         <v>5188</v>
       </c>
       <c r="K5" t="n">
-        <v>-85486</v>
+        <v>-85524</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>457528.45</v>
+        <v>502221.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>52496.9</v>
+        <v>52715.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>405031.5499999999</v>
+        <v>449505.5499999999</v>
       </c>
       <c r="I6" t="n">
-        <v>398105</v>
+        <v>442579</v>
       </c>
       <c r="J6" t="n">
         <v>6926</v>
       </c>
       <c r="K6" t="n">
-        <v>337268</v>
+        <v>371742</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>311419.99</v>
+        <v>337080.89</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>78062</v>
+        <v>81455</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>233357.99</v>
+        <v>255625.89</v>
       </c>
       <c r="I7" t="n">
-        <v>231639</v>
+        <v>253907</v>
       </c>
       <c r="J7" t="n">
         <v>1718</v>
       </c>
       <c r="K7" t="n">
-        <v>138463</v>
+        <v>165711</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>349022.62</v>
+        <v>354005.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>78580</v>
+        <v>83945</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>270442.62</v>
+        <v>270060.62</v>
       </c>
       <c r="I8" t="n">
-        <v>289047</v>
+        <v>288665</v>
       </c>
       <c r="J8" t="n">
         <v>-18605</v>
       </c>
       <c r="K8" t="n">
-        <v>229248</v>
+        <v>228866</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>728727.36</v>
+        <v>824467.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>258700</v>
+        <v>286700</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>470027.36</v>
+        <v>537767.36</v>
       </c>
       <c r="I9" t="n">
-        <v>334189</v>
+        <v>393529</v>
       </c>
       <c r="J9" t="n">
-        <v>135838</v>
+        <v>144238</v>
       </c>
       <c r="K9" t="n">
-        <v>176797</v>
+        <v>228717</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1073645.42</v>
+        <v>1328416.42</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>11308</v>
+        <v>22808</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1062337.42</v>
+        <v>1305608.42</v>
       </c>
       <c r="I10" t="n">
-        <v>426491</v>
+        <v>494845</v>
       </c>
       <c r="J10" t="n">
-        <v>635845</v>
+        <v>810762</v>
       </c>
       <c r="K10" t="n">
-        <v>1000949</v>
+        <v>1254322</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>172549.35</v>
+        <v>206143.35</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>136149.37</v>
+        <v>169743.37</v>
       </c>
       <c r="I11" t="n">
-        <v>20356</v>
+        <v>31552</v>
       </c>
       <c r="J11" t="n">
-        <v>115583</v>
+        <v>137981</v>
       </c>
       <c r="K11" t="n">
-        <v>78787</v>
+        <v>78987</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>347513</v>
+        <v>365307</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>83.8%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>317437</v>
+        <v>335231</v>
       </c>
       <c r="I12" t="n">
-        <v>62178</v>
+        <v>68877</v>
       </c>
       <c r="J12" t="n">
-        <v>255259</v>
+        <v>266354</v>
       </c>
       <c r="K12" t="n">
-        <v>35031</v>
+        <v>41631</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>416207.98</v>
+        <v>469457.47</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>371194.31</v>
+        <v>424443.8</v>
       </c>
       <c r="I13" t="n">
-        <v>12661</v>
+        <v>12674</v>
       </c>
       <c r="J13" t="n">
-        <v>332156</v>
+        <v>380554</v>
       </c>
       <c r="K13" t="n">
-        <v>91530</v>
+        <v>96983</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>192199.3</v>
+        <v>197921.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>177333.3</v>
+        <v>183055.5</v>
       </c>
       <c r="I14" t="n">
-        <v>40511</v>
+        <v>31326</v>
       </c>
       <c r="J14" t="n">
-        <v>126888</v>
+        <v>137884</v>
       </c>
       <c r="K14" t="n">
-        <v>26373</v>
+        <v>30303</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>100210</v>
+        <v>110728</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>84334</v>
+        <v>94852</v>
       </c>
       <c r="I15" t="n">
-        <v>7613</v>
+        <v>7632</v>
       </c>
       <c r="J15" t="n">
-        <v>76721</v>
+        <v>87220</v>
       </c>
       <c r="K15" t="n">
-        <v>36960</v>
+        <v>37478</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>239947</v>
+        <v>265280</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>221549</v>
+        <v>246882</v>
       </c>
       <c r="I16" t="n">
-        <v>9366</v>
+        <v>32709</v>
       </c>
       <c r="J16" t="n">
-        <v>212183</v>
+        <v>214173</v>
       </c>
       <c r="K16" t="n">
-        <v>41087</v>
+        <v>44232</v>
       </c>
     </row>
     <row r="17">
@@ -1133,32 +1133,32 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>327376.81</v>
+        <v>431788.69</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>88491.39999999999</v>
+        <v>88462.39999999999</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>238885.41</v>
+        <v>343326.29</v>
       </c>
       <c r="I17" t="n">
-        <v>6055</v>
+        <v>42482</v>
       </c>
       <c r="J17" t="n">
-        <v>189226</v>
+        <v>232014</v>
       </c>
       <c r="K17" t="n">
-        <v>11870</v>
+        <v>103721</v>
       </c>
     </row>
     <row r="18">
@@ -1176,32 +1176,32 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>789443.9</v>
+        <v>895353.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>84494</v>
+        <v>98495</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>704949.9</v>
+        <v>796858.9</v>
       </c>
       <c r="I18" t="n">
-        <v>216040</v>
+        <v>218371</v>
       </c>
       <c r="J18" t="n">
-        <v>488059</v>
+        <v>577637</v>
       </c>
       <c r="K18" t="n">
-        <v>409347</v>
+        <v>494460</v>
       </c>
     </row>
     <row r="19">
@@ -1219,15 +1219,15 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>254472.83</v>
+        <v>301622.56</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>254111.83</v>
+        <v>301276.56</v>
       </c>
       <c r="I19" t="n">
-        <v>35266</v>
+        <v>41184</v>
       </c>
       <c r="J19" t="n">
-        <v>210190</v>
+        <v>239186</v>
       </c>
       <c r="K19" t="n">
-        <v>77839</v>
+        <v>91710</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>307469.9</v>
+        <v>361182.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>48215</v>
+        <v>49262</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>259254.9</v>
+        <v>311920.9</v>
       </c>
       <c r="I20" t="n">
-        <v>86736</v>
+        <v>86603</v>
       </c>
       <c r="J20" t="n">
-        <v>172518</v>
+        <v>225317</v>
       </c>
       <c r="K20" t="n">
-        <v>36098</v>
+        <v>40964</v>
       </c>
     </row>
     <row r="21">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>455793.21</v>
+        <v>461959.21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>135997.16</v>
+        <v>136120.16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>319796.0499999999</v>
+        <v>325839.0499999999</v>
       </c>
       <c r="I2" t="n">
-        <v>310162</v>
+        <v>316205</v>
       </c>
       <c r="J2" t="n">
         <v>9634</v>
       </c>
       <c r="K2" t="n">
-        <v>318806</v>
+        <v>324849</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2079</v>
+        <v>19</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -539,24 +539,24 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>17636</v>
+        <v>14980</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>848.3%</t>
+          <t>78842.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-15557</v>
+        <v>-14961</v>
       </c>
       <c r="I3" t="n">
-        <v>-15692</v>
+        <v>-14961</v>
       </c>
       <c r="J3" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-5557</v>
+        <v>-4961</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>485207.14</v>
+        <v>452826.14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>133581.8</v>
+        <v>137973.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>351625.34</v>
+        <v>314852.34</v>
       </c>
       <c r="I4" t="n">
-        <v>342638</v>
+        <v>306046</v>
       </c>
       <c r="J4" t="n">
-        <v>8987</v>
+        <v>8806</v>
       </c>
       <c r="K4" t="n">
-        <v>333839</v>
+        <v>307464</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>224458</v>
+        <v>218577</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>197822.9</v>
+        <v>197841.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>88.1%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>26635.10000000001</v>
+        <v>20735.10000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>21447</v>
+        <v>15547</v>
       </c>
       <c r="J5" t="n">
         <v>5188</v>
       </c>
       <c r="K5" t="n">
-        <v>-85524</v>
+        <v>-91424</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>502221.45</v>
+        <v>493990.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>52715.9</v>
+        <v>57758.9</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>449505.5499999999</v>
+        <v>436231.5499999999</v>
       </c>
       <c r="I6" t="n">
-        <v>442579</v>
+        <v>429305</v>
       </c>
       <c r="J6" t="n">
         <v>6926</v>
       </c>
       <c r="K6" t="n">
-        <v>371742</v>
+        <v>370070</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>337080.89</v>
+        <v>355575.89</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>81455</v>
+        <v>81615</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>255625.89</v>
+        <v>273960.89</v>
       </c>
       <c r="I7" t="n">
-        <v>253907</v>
+        <v>272242</v>
       </c>
       <c r="J7" t="n">
         <v>1718</v>
       </c>
       <c r="K7" t="n">
-        <v>165711</v>
+        <v>173648</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>354005.62</v>
+        <v>347770.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>83945</v>
+        <v>97470</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>270060.62</v>
+        <v>250300.62</v>
       </c>
       <c r="I8" t="n">
-        <v>288665</v>
+        <v>268770</v>
       </c>
       <c r="J8" t="n">
-        <v>-18605</v>
+        <v>-18470</v>
       </c>
       <c r="K8" t="n">
-        <v>228866</v>
+        <v>209106</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>824467.36</v>
+        <v>833538.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>537767.36</v>
+        <v>546838.36</v>
       </c>
       <c r="I9" t="n">
-        <v>393529</v>
+        <v>430400</v>
       </c>
       <c r="J9" t="n">
-        <v>144238</v>
+        <v>116438</v>
       </c>
       <c r="K9" t="n">
-        <v>228717</v>
+        <v>237788</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1328416.42</v>
+        <v>1424373.43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -844,20 +844,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1305608.42</v>
+        <v>1401565.43</v>
       </c>
       <c r="I10" t="n">
-        <v>494845</v>
+        <v>529674</v>
       </c>
       <c r="J10" t="n">
-        <v>810762</v>
+        <v>871890</v>
       </c>
       <c r="K10" t="n">
-        <v>1254322</v>
+        <v>1350677</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>206143.35</v>
+        <v>204306.34</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>169743.37</v>
+        <v>167906.36</v>
       </c>
       <c r="I11" t="n">
-        <v>31552</v>
+        <v>31514</v>
       </c>
       <c r="J11" t="n">
-        <v>137981</v>
+        <v>136181</v>
       </c>
       <c r="K11" t="n">
-        <v>78987</v>
+        <v>77150</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>365307</v>
+        <v>344701</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>83.8%</t>
+          <t>78.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>335231</v>
+        <v>314625</v>
       </c>
       <c r="I12" t="n">
-        <v>68877</v>
+        <v>38669</v>
       </c>
       <c r="J12" t="n">
-        <v>266354</v>
+        <v>275956</v>
       </c>
       <c r="K12" t="n">
-        <v>41631</v>
+        <v>41821</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>469457.47</v>
+        <v>473605.47</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>424443.8</v>
+        <v>428591.8</v>
       </c>
       <c r="I13" t="n">
-        <v>12674</v>
+        <v>18924</v>
       </c>
       <c r="J13" t="n">
-        <v>380554</v>
+        <v>378452</v>
       </c>
       <c r="K13" t="n">
-        <v>96983</v>
+        <v>96637</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>197921.5</v>
+        <v>241898.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>183055.5</v>
+        <v>227032.3</v>
       </c>
       <c r="I14" t="n">
-        <v>31326</v>
+        <v>29346</v>
       </c>
       <c r="J14" t="n">
-        <v>137884</v>
+        <v>181332</v>
       </c>
       <c r="K14" t="n">
-        <v>30303</v>
+        <v>64480</v>
       </c>
     </row>
     <row r="15">
@@ -1047,32 +1047,32 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>110728</v>
+        <v>109890</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>15876</v>
+        <v>15857</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>94852</v>
+        <v>94033</v>
       </c>
       <c r="I15" t="n">
-        <v>7632</v>
+        <v>7594</v>
       </c>
       <c r="J15" t="n">
-        <v>87220</v>
+        <v>86439</v>
       </c>
       <c r="K15" t="n">
-        <v>37478</v>
+        <v>36659</v>
       </c>
     </row>
     <row r="16">
@@ -1090,7 +1090,7 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>265280</v>
+        <v>265261</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>246882</v>
+        <v>246863</v>
       </c>
       <c r="I16" t="n">
-        <v>32709</v>
+        <v>32690</v>
       </c>
       <c r="J16" t="n">
         <v>214173</v>
       </c>
       <c r="K16" t="n">
-        <v>44232</v>
+        <v>44213</v>
       </c>
     </row>
     <row r="17">
@@ -1133,32 +1133,32 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>431788.69</v>
+        <v>454157.69</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>88462.39999999999</v>
+        <v>88433.39999999999</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>343326.29</v>
+        <v>365724.29</v>
       </c>
       <c r="I17" t="n">
-        <v>42482</v>
+        <v>42282</v>
       </c>
       <c r="J17" t="n">
-        <v>232014</v>
+        <v>254612</v>
       </c>
       <c r="K17" t="n">
-        <v>103721</v>
+        <v>103521</v>
       </c>
     </row>
     <row r="18">
@@ -1176,11 +1176,11 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>895353.9</v>
+        <v>878621.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1188,20 +1188,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>796858.9</v>
+        <v>780126.9</v>
       </c>
       <c r="I18" t="n">
-        <v>218371</v>
+        <v>178402</v>
       </c>
       <c r="J18" t="n">
-        <v>577637</v>
+        <v>600874</v>
       </c>
       <c r="K18" t="n">
-        <v>494460</v>
+        <v>451528</v>
       </c>
     </row>
     <row r="19">
@@ -1219,11 +1219,11 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>301622.56</v>
+        <v>313911.37</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>301276.56</v>
+        <v>313565.37</v>
       </c>
       <c r="I19" t="n">
-        <v>41184</v>
+        <v>41946</v>
       </c>
       <c r="J19" t="n">
-        <v>239186</v>
+        <v>250282</v>
       </c>
       <c r="K19" t="n">
-        <v>91710</v>
+        <v>92103</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>361182.9</v>
+        <v>338526.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>49262</v>
+        <v>49290</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>311920.9</v>
+        <v>289236.9</v>
       </c>
       <c r="I20" t="n">
-        <v>86603</v>
+        <v>34879</v>
       </c>
       <c r="J20" t="n">
-        <v>225317</v>
+        <v>254357</v>
       </c>
       <c r="K20" t="n">
-        <v>40964</v>
+        <v>39276</v>
       </c>
     </row>
     <row r="21">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,11 +488,11 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>461959.21</v>
+        <v>470209.21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -500,20 +500,20 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>325839.0499999999</v>
+        <v>334089.0499999999</v>
       </c>
       <c r="I2" t="n">
-        <v>316205</v>
+        <v>324455</v>
       </c>
       <c r="J2" t="n">
         <v>9634</v>
       </c>
       <c r="K2" t="n">
-        <v>324849</v>
+        <v>333099</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>1318</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -543,20 +543,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>78842.1%</t>
+          <t>1136.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-14961</v>
+        <v>-13662</v>
       </c>
       <c r="I3" t="n">
-        <v>-14961</v>
+        <v>-13662</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-4961</v>
+        <v>-3662</v>
       </c>
     </row>
     <row r="4">
@@ -574,11 +574,11 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>452826.14</v>
+        <v>493912.14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -586,20 +586,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>314852.34</v>
+        <v>355938.34</v>
       </c>
       <c r="I4" t="n">
-        <v>306046</v>
+        <v>346913</v>
       </c>
       <c r="J4" t="n">
-        <v>8806</v>
+        <v>9025</v>
       </c>
       <c r="K4" t="n">
-        <v>307464</v>
+        <v>338152</v>
       </c>
     </row>
     <row r="5">
@@ -617,11 +617,11 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>218577</v>
+        <v>226501</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -629,20 +629,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>20735.10000000001</v>
+        <v>28659.10000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>15547</v>
+        <v>23471</v>
       </c>
       <c r="J5" t="n">
         <v>5188</v>
       </c>
       <c r="K5" t="n">
-        <v>-91424</v>
+        <v>-83500</v>
       </c>
     </row>
     <row r="6">
@@ -660,11 +660,11 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>493990.45</v>
+        <v>511626.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -672,20 +672,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>436231.5499999999</v>
+        <v>453867.5499999999</v>
       </c>
       <c r="I6" t="n">
-        <v>429305</v>
+        <v>446941</v>
       </c>
       <c r="J6" t="n">
         <v>6926</v>
       </c>
       <c r="K6" t="n">
-        <v>370070</v>
+        <v>375706</v>
       </c>
     </row>
     <row r="7">
@@ -703,11 +703,11 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>355575.89</v>
+        <v>360310.89</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -715,20 +715,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>273960.89</v>
+        <v>278695.89</v>
       </c>
       <c r="I7" t="n">
-        <v>272242</v>
+        <v>276977</v>
       </c>
       <c r="J7" t="n">
         <v>1718</v>
       </c>
       <c r="K7" t="n">
-        <v>173648</v>
+        <v>178383</v>
       </c>
     </row>
     <row r="8">
@@ -746,11 +746,11 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>347770.62</v>
+        <v>355003.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -758,20 +758,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>250300.62</v>
+        <v>257533.62</v>
       </c>
       <c r="I8" t="n">
-        <v>268770</v>
+        <v>276003</v>
       </c>
       <c r="J8" t="n">
         <v>-18470</v>
       </c>
       <c r="K8" t="n">
-        <v>209106</v>
+        <v>216339</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>833538.36</v>
+        <v>864067.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>546838.36</v>
+        <v>577367.36</v>
       </c>
       <c r="I9" t="n">
-        <v>430400</v>
+        <v>433129</v>
       </c>
       <c r="J9" t="n">
-        <v>116438</v>
+        <v>144238</v>
       </c>
       <c r="K9" t="n">
-        <v>237788</v>
+        <v>268317</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1424373.43</v>
+        <v>1429049.43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1401565.43</v>
+        <v>1406241.43</v>
       </c>
       <c r="I10" t="n">
-        <v>529674</v>
+        <v>534350</v>
       </c>
       <c r="J10" t="n">
         <v>871890</v>
       </c>
       <c r="K10" t="n">
-        <v>1350677</v>
+        <v>1354955</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>204306.34</v>
+        <v>206523.34</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>167906.36</v>
+        <v>170123.36</v>
       </c>
       <c r="I11" t="n">
-        <v>31514</v>
+        <v>31533</v>
       </c>
       <c r="J11" t="n">
-        <v>136181</v>
+        <v>138379</v>
       </c>
       <c r="K11" t="n">
-        <v>77150</v>
+        <v>78969</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>344701</v>
+        <v>375497</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.7%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,17 +930,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>314625</v>
+        <v>345421</v>
       </c>
       <c r="I12" t="n">
-        <v>38669</v>
+        <v>69067</v>
       </c>
       <c r="J12" t="n">
-        <v>275956</v>
+        <v>276354</v>
       </c>
       <c r="K12" t="n">
         <v>41821</v>
@@ -961,11 +961,11 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>473605.47</v>
+        <v>481680.47</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>428591.8</v>
+        <v>436666.8</v>
       </c>
       <c r="I13" t="n">
-        <v>18924</v>
+        <v>19299</v>
       </c>
       <c r="J13" t="n">
-        <v>378452</v>
+        <v>386152</v>
       </c>
       <c r="K13" t="n">
-        <v>96637</v>
+        <v>97212</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>241898.3</v>
+        <v>250416.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>227032.3</v>
+        <v>235550.3</v>
       </c>
       <c r="I14" t="n">
-        <v>29346</v>
+        <v>31326</v>
       </c>
       <c r="J14" t="n">
-        <v>181332</v>
+        <v>187870</v>
       </c>
       <c r="K14" t="n">
-        <v>64480</v>
+        <v>72400</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>109890</v>
+        <v>111208</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>94033</v>
+        <v>95351</v>
       </c>
       <c r="I15" t="n">
-        <v>7594</v>
+        <v>7632</v>
       </c>
       <c r="J15" t="n">
-        <v>86439</v>
+        <v>87719</v>
       </c>
       <c r="K15" t="n">
-        <v>36659</v>
+        <v>37977</v>
       </c>
     </row>
     <row r="16">
@@ -1090,7 +1090,7 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>265261</v>
+        <v>265290</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>246863</v>
+        <v>246892</v>
       </c>
       <c r="I16" t="n">
-        <v>32690</v>
+        <v>32719</v>
       </c>
       <c r="J16" t="n">
         <v>214173</v>
       </c>
       <c r="K16" t="n">
-        <v>44213</v>
+        <v>44242</v>
       </c>
     </row>
     <row r="17">
@@ -1133,11 +1133,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>454157.69</v>
+        <v>454755.69</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1145,20 +1145,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>365724.29</v>
+        <v>366322.29</v>
       </c>
       <c r="I17" t="n">
-        <v>42282</v>
+        <v>42482</v>
       </c>
       <c r="J17" t="n">
-        <v>254612</v>
+        <v>255010</v>
       </c>
       <c r="K17" t="n">
-        <v>103521</v>
+        <v>103721</v>
       </c>
     </row>
     <row r="18">
@@ -1176,11 +1176,11 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>878621.9</v>
+        <v>928588.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1188,20 +1188,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>780126.9</v>
+        <v>830093.9</v>
       </c>
       <c r="I18" t="n">
-        <v>178402</v>
+        <v>226389</v>
       </c>
       <c r="J18" t="n">
-        <v>600874</v>
+        <v>602854</v>
       </c>
       <c r="K18" t="n">
-        <v>451528</v>
+        <v>501097</v>
       </c>
     </row>
     <row r="19">
@@ -1219,11 +1219,11 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>313911.37</v>
+        <v>321930.37</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>313565.37</v>
+        <v>321584.37</v>
       </c>
       <c r="I19" t="n">
-        <v>41946</v>
+        <v>41965</v>
       </c>
       <c r="J19" t="n">
-        <v>250282</v>
+        <v>258282</v>
       </c>
       <c r="K19" t="n">
-        <v>92103</v>
+        <v>92122</v>
       </c>
     </row>
     <row r="20">
@@ -1262,11 +1262,11 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>338526.9</v>
+        <v>372221.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>289236.9</v>
+        <v>322931.9</v>
       </c>
       <c r="I20" t="n">
-        <v>34879</v>
+        <v>36196</v>
       </c>
       <c r="J20" t="n">
-        <v>254357</v>
+        <v>286735</v>
       </c>
       <c r="K20" t="n">
-        <v>39276</v>
+        <v>41577</v>
       </c>
     </row>
     <row r="21">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -574,11 +574,11 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>493912.14</v>
+        <v>494663.14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -590,16 +590,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>355938.34</v>
+        <v>356689.34</v>
       </c>
       <c r="I4" t="n">
-        <v>346913</v>
+        <v>347664</v>
       </c>
       <c r="J4" t="n">
         <v>9025</v>
       </c>
       <c r="K4" t="n">
-        <v>338152</v>
+        <v>338903</v>
       </c>
     </row>
     <row r="5">
@@ -703,7 +703,7 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>360310.89</v>
+        <v>360319.89</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>278695.89</v>
+        <v>278704.89</v>
       </c>
       <c r="I7" t="n">
-        <v>276977</v>
+        <v>276986</v>
       </c>
       <c r="J7" t="n">
         <v>1718</v>
       </c>
       <c r="K7" t="n">
-        <v>178383</v>
+        <v>178392</v>
       </c>
     </row>
     <row r="8">
@@ -746,7 +746,7 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>355003.62</v>
+        <v>355041.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -762,16 +762,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>257533.62</v>
+        <v>257571.62</v>
       </c>
       <c r="I8" t="n">
-        <v>276003</v>
+        <v>276041</v>
       </c>
       <c r="J8" t="n">
         <v>-18470</v>
       </c>
       <c r="K8" t="n">
-        <v>216339</v>
+        <v>216377</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>864067.36</v>
+        <v>838247.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>577367.36</v>
+        <v>551547.36</v>
       </c>
       <c r="I9" t="n">
-        <v>433129</v>
+        <v>435109</v>
       </c>
       <c r="J9" t="n">
-        <v>144238</v>
+        <v>116438</v>
       </c>
       <c r="K9" t="n">
-        <v>268317</v>
+        <v>242497</v>
       </c>
     </row>
     <row r="10">
@@ -832,7 +832,7 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1429049.43</v>
+        <v>1429077.43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1406241.43</v>
+        <v>1406269.43</v>
       </c>
       <c r="I10" t="n">
-        <v>534350</v>
+        <v>534378</v>
       </c>
       <c r="J10" t="n">
         <v>871890</v>
       </c>
       <c r="K10" t="n">
-        <v>1354955</v>
+        <v>1354983</v>
       </c>
     </row>
     <row r="11">
@@ -918,7 +918,7 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>375497</v>
+        <v>375545</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>345421</v>
+        <v>345469</v>
       </c>
       <c r="I12" t="n">
-        <v>69067</v>
+        <v>69115</v>
       </c>
       <c r="J12" t="n">
         <v>276354</v>
       </c>
       <c r="K12" t="n">
-        <v>41821</v>
+        <v>41869</v>
       </c>
     </row>
     <row r="13">
@@ -961,7 +961,7 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>481680.47</v>
+        <v>482017.47</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>436666.8</v>
+        <v>437003.8</v>
       </c>
       <c r="I13" t="n">
-        <v>19299</v>
+        <v>19636</v>
       </c>
       <c r="J13" t="n">
         <v>386152</v>
       </c>
       <c r="K13" t="n">
-        <v>97212</v>
+        <v>97549</v>
       </c>
     </row>
     <row r="14">
@@ -1004,7 +1004,7 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>250416.3</v>
+        <v>250435.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>235550.3</v>
+        <v>235569.3</v>
       </c>
       <c r="I14" t="n">
-        <v>31326</v>
+        <v>31345</v>
       </c>
       <c r="J14" t="n">
         <v>187870</v>
       </c>
       <c r="K14" t="n">
-        <v>72400</v>
+        <v>72419</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>111208</v>
+        <v>121227</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>95351</v>
+        <v>105370</v>
       </c>
       <c r="I15" t="n">
-        <v>7632</v>
+        <v>7651</v>
       </c>
       <c r="J15" t="n">
-        <v>87719</v>
+        <v>97719</v>
       </c>
       <c r="K15" t="n">
-        <v>37977</v>
+        <v>37996</v>
       </c>
     </row>
     <row r="16">
@@ -1090,7 +1090,7 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>265290</v>
+        <v>265309</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>246892</v>
+        <v>246911</v>
       </c>
       <c r="I16" t="n">
-        <v>32719</v>
+        <v>32738</v>
       </c>
       <c r="J16" t="n">
         <v>214173</v>
       </c>
       <c r="K16" t="n">
-        <v>44242</v>
+        <v>44261</v>
       </c>
     </row>
     <row r="17">
@@ -1133,7 +1133,7 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>454755.69</v>
+        <v>454784.69</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1149,16 +1149,16 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>366322.29</v>
+        <v>366351.29</v>
       </c>
       <c r="I17" t="n">
-        <v>42482</v>
+        <v>42511</v>
       </c>
       <c r="J17" t="n">
         <v>255010</v>
       </c>
       <c r="K17" t="n">
-        <v>103721</v>
+        <v>103750</v>
       </c>
     </row>
     <row r="18">
@@ -1219,7 +1219,7 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>321930.37</v>
+        <v>321964.37</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>321584.37</v>
+        <v>321618.37</v>
       </c>
       <c r="I19" t="n">
-        <v>41965</v>
+        <v>41999</v>
       </c>
       <c r="J19" t="n">
         <v>258282</v>
       </c>
       <c r="K19" t="n">
-        <v>92122</v>
+        <v>92156</v>
       </c>
     </row>
     <row r="20">
@@ -1262,11 +1262,11 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>372221.9</v>
+        <v>365697.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>322931.9</v>
+        <v>316407.9</v>
       </c>
       <c r="I20" t="n">
-        <v>36196</v>
+        <v>29672</v>
       </c>
       <c r="J20" t="n">
         <v>286735</v>
       </c>
       <c r="K20" t="n">
-        <v>41577</v>
+        <v>35053</v>
       </c>
     </row>
     <row r="21">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -574,11 +574,11 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>494663.14</v>
+        <v>493912.14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -590,16 +590,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>356689.34</v>
+        <v>355938.34</v>
       </c>
       <c r="I4" t="n">
-        <v>347664</v>
+        <v>346913</v>
       </c>
       <c r="J4" t="n">
         <v>9025</v>
       </c>
       <c r="K4" t="n">
-        <v>338903</v>
+        <v>338152</v>
       </c>
     </row>
     <row r="5">
@@ -703,7 +703,7 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>360319.89</v>
+        <v>360310.89</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>278704.89</v>
+        <v>278695.89</v>
       </c>
       <c r="I7" t="n">
-        <v>276986</v>
+        <v>276977</v>
       </c>
       <c r="J7" t="n">
         <v>1718</v>
       </c>
       <c r="K7" t="n">
-        <v>178392</v>
+        <v>178383</v>
       </c>
     </row>
     <row r="8">
@@ -746,7 +746,7 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>355041.62</v>
+        <v>355003.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -762,16 +762,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>257571.62</v>
+        <v>257533.62</v>
       </c>
       <c r="I8" t="n">
-        <v>276041</v>
+        <v>276003</v>
       </c>
       <c r="J8" t="n">
         <v>-18470</v>
       </c>
       <c r="K8" t="n">
-        <v>216377</v>
+        <v>216339</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>838247.36</v>
+        <v>864067.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>551547.36</v>
+        <v>577367.36</v>
       </c>
       <c r="I9" t="n">
-        <v>435109</v>
+        <v>433129</v>
       </c>
       <c r="J9" t="n">
-        <v>116438</v>
+        <v>144238</v>
       </c>
       <c r="K9" t="n">
-        <v>242497</v>
+        <v>268317</v>
       </c>
     </row>
     <row r="10">
@@ -832,7 +832,7 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1429077.43</v>
+        <v>1429049.43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1406269.43</v>
+        <v>1406241.43</v>
       </c>
       <c r="I10" t="n">
-        <v>534378</v>
+        <v>534350</v>
       </c>
       <c r="J10" t="n">
         <v>871890</v>
       </c>
       <c r="K10" t="n">
-        <v>1354983</v>
+        <v>1354955</v>
       </c>
     </row>
     <row r="11">
@@ -918,7 +918,7 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>375545</v>
+        <v>375497</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>345469</v>
+        <v>345421</v>
       </c>
       <c r="I12" t="n">
-        <v>69115</v>
+        <v>69067</v>
       </c>
       <c r="J12" t="n">
         <v>276354</v>
       </c>
       <c r="K12" t="n">
-        <v>41869</v>
+        <v>41821</v>
       </c>
     </row>
     <row r="13">
@@ -961,7 +961,7 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>482017.47</v>
+        <v>481680.47</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>437003.8</v>
+        <v>436666.8</v>
       </c>
       <c r="I13" t="n">
-        <v>19636</v>
+        <v>19299</v>
       </c>
       <c r="J13" t="n">
         <v>386152</v>
       </c>
       <c r="K13" t="n">
-        <v>97549</v>
+        <v>97212</v>
       </c>
     </row>
     <row r="14">
@@ -1004,7 +1004,7 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>250435.3</v>
+        <v>250416.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>235569.3</v>
+        <v>235550.3</v>
       </c>
       <c r="I14" t="n">
-        <v>31345</v>
+        <v>31326</v>
       </c>
       <c r="J14" t="n">
         <v>187870</v>
       </c>
       <c r="K14" t="n">
-        <v>72419</v>
+        <v>72400</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>121227</v>
+        <v>111208</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>105370</v>
+        <v>95351</v>
       </c>
       <c r="I15" t="n">
-        <v>7651</v>
+        <v>7632</v>
       </c>
       <c r="J15" t="n">
-        <v>97719</v>
+        <v>87719</v>
       </c>
       <c r="K15" t="n">
-        <v>37996</v>
+        <v>37977</v>
       </c>
     </row>
     <row r="16">
@@ -1090,7 +1090,7 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>265309</v>
+        <v>265290</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>246911</v>
+        <v>246892</v>
       </c>
       <c r="I16" t="n">
-        <v>32738</v>
+        <v>32719</v>
       </c>
       <c r="J16" t="n">
         <v>214173</v>
       </c>
       <c r="K16" t="n">
-        <v>44261</v>
+        <v>44242</v>
       </c>
     </row>
     <row r="17">
@@ -1133,7 +1133,7 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>454784.69</v>
+        <v>454755.69</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1149,16 +1149,16 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>366351.29</v>
+        <v>366322.29</v>
       </c>
       <c r="I17" t="n">
-        <v>42511</v>
+        <v>42482</v>
       </c>
       <c r="J17" t="n">
         <v>255010</v>
       </c>
       <c r="K17" t="n">
-        <v>103750</v>
+        <v>103721</v>
       </c>
     </row>
     <row r="18">
@@ -1219,7 +1219,7 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>321964.37</v>
+        <v>321930.37</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>321618.37</v>
+        <v>321584.37</v>
       </c>
       <c r="I19" t="n">
-        <v>41999</v>
+        <v>41965</v>
       </c>
       <c r="J19" t="n">
         <v>258282</v>
       </c>
       <c r="K19" t="n">
-        <v>92156</v>
+        <v>92122</v>
       </c>
     </row>
     <row r="20">
@@ -1262,11 +1262,11 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>365697.9</v>
+        <v>372221.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>316407.9</v>
+        <v>322931.9</v>
       </c>
       <c r="I20" t="n">
-        <v>29672</v>
+        <v>36196</v>
       </c>
       <c r="J20" t="n">
         <v>286735</v>
       </c>
       <c r="K20" t="n">
-        <v>35053</v>
+        <v>41577</v>
       </c>
     </row>
     <row r="21">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>470209.21</v>
+        <v>536976.21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>136120.16</v>
+        <v>136571.16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>334089.0499999999</v>
+        <v>400405.0499999999</v>
       </c>
       <c r="I2" t="n">
-        <v>324455</v>
+        <v>390771</v>
       </c>
       <c r="J2" t="n">
         <v>9634</v>
       </c>
       <c r="K2" t="n">
-        <v>333099</v>
+        <v>399415</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>1318</v>
+        <v>2019</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -543,20 +543,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1136.6%</t>
+          <t>742.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-13662</v>
+        <v>-12961</v>
       </c>
       <c r="I3" t="n">
-        <v>-13662</v>
+        <v>-13096</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="K3" t="n">
-        <v>-3662</v>
+        <v>-2961</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>493912.14</v>
+        <v>592959.0499999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>137973.8</v>
+        <v>142094.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>355938.34</v>
+        <v>450864.2499999999</v>
       </c>
       <c r="I4" t="n">
-        <v>346913</v>
+        <v>441641</v>
       </c>
       <c r="J4" t="n">
-        <v>9025</v>
+        <v>9223</v>
       </c>
       <c r="K4" t="n">
-        <v>338152</v>
+        <v>432680</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>226501</v>
+        <v>230387</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>197841.9</v>
+        <v>239927.9</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>104.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>28659.10000000001</v>
+        <v>-9540.899999999994</v>
       </c>
       <c r="I5" t="n">
-        <v>23471</v>
+        <v>-14728</v>
       </c>
       <c r="J5" t="n">
         <v>5188</v>
       </c>
       <c r="K5" t="n">
-        <v>-83500</v>
+        <v>-121700</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>511626.45</v>
+        <v>550501.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>57758.9</v>
+        <v>66616.89999999999</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>453867.5499999999</v>
+        <v>483884.5499999999</v>
       </c>
       <c r="I6" t="n">
-        <v>446941</v>
+        <v>476958</v>
       </c>
       <c r="J6" t="n">
         <v>6926</v>
       </c>
       <c r="K6" t="n">
-        <v>375706</v>
+        <v>405723</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>360310.89</v>
+        <v>384191.89</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>81615</v>
+        <v>87008</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>278695.89</v>
+        <v>297183.89</v>
       </c>
       <c r="I7" t="n">
-        <v>276977</v>
+        <v>295465</v>
       </c>
       <c r="J7" t="n">
         <v>1718</v>
       </c>
       <c r="K7" t="n">
-        <v>178383</v>
+        <v>179871</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>355003.62</v>
+        <v>414738.04</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>97470</v>
+        <v>101687</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>257533.62</v>
+        <v>313051.04</v>
       </c>
       <c r="I8" t="n">
-        <v>276003</v>
+        <v>331455</v>
       </c>
       <c r="J8" t="n">
-        <v>-18470</v>
+        <v>-18404</v>
       </c>
       <c r="K8" t="n">
-        <v>216339</v>
+        <v>271857</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>864067.36</v>
+        <v>863847.36</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>286700</v>
+        <v>295700</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>577367.36</v>
+        <v>568147.36</v>
       </c>
       <c r="I9" t="n">
-        <v>433129</v>
+        <v>430509</v>
       </c>
       <c r="J9" t="n">
-        <v>144238</v>
+        <v>137638</v>
       </c>
       <c r="K9" t="n">
-        <v>268317</v>
+        <v>292097</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1429049.43</v>
+        <v>1503178.43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>22808</v>
+        <v>29808</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1406241.43</v>
+        <v>1473370.43</v>
       </c>
       <c r="I10" t="n">
-        <v>534350</v>
+        <v>554088</v>
       </c>
       <c r="J10" t="n">
-        <v>871890</v>
+        <v>919281</v>
       </c>
       <c r="K10" t="n">
-        <v>1354955</v>
+        <v>1429084</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>206523.34</v>
+        <v>229338.34</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>170123.36</v>
+        <v>192938.36</v>
       </c>
       <c r="I11" t="n">
-        <v>31533</v>
+        <v>44746</v>
       </c>
       <c r="J11" t="n">
-        <v>138379</v>
+        <v>147981</v>
       </c>
       <c r="K11" t="n">
-        <v>78969</v>
+        <v>78988</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>375497</v>
+        <v>375246</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>345421</v>
+        <v>345170</v>
       </c>
       <c r="I12" t="n">
-        <v>69067</v>
+        <v>69115</v>
       </c>
       <c r="J12" t="n">
-        <v>276354</v>
+        <v>276055</v>
       </c>
       <c r="K12" t="n">
-        <v>41821</v>
+        <v>41570</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>481680.47</v>
+        <v>490573.37</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>436666.8</v>
+        <v>445559.7</v>
       </c>
       <c r="I13" t="n">
-        <v>19299</v>
+        <v>20453</v>
       </c>
       <c r="J13" t="n">
-        <v>386152</v>
+        <v>393891</v>
       </c>
       <c r="K13" t="n">
-        <v>97212</v>
+        <v>105309</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>250416.3</v>
+        <v>260814.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.7%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,14 +1016,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>235550.3</v>
+        <v>245948.3</v>
       </c>
       <c r="I14" t="n">
-        <v>31326</v>
+        <v>41724</v>
       </c>
       <c r="J14" t="n">
         <v>187870</v>
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>111208</v>
+        <v>121625</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>95351</v>
+        <v>105768</v>
       </c>
       <c r="I15" t="n">
-        <v>7632</v>
+        <v>8049</v>
       </c>
       <c r="J15" t="n">
-        <v>87719</v>
+        <v>97719</v>
       </c>
       <c r="K15" t="n">
-        <v>37977</v>
+        <v>37996</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>265290</v>
+        <v>273707</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>246892</v>
+        <v>255309</v>
       </c>
       <c r="I16" t="n">
-        <v>32719</v>
+        <v>41136</v>
       </c>
       <c r="J16" t="n">
         <v>214173</v>
       </c>
       <c r="K16" t="n">
-        <v>44242</v>
+        <v>44261</v>
       </c>
     </row>
     <row r="17">
@@ -1133,11 +1133,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>454755.69</v>
+        <v>501582.69</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1145,20 +1145,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>366322.29</v>
+        <v>413149.29</v>
       </c>
       <c r="I17" t="n">
-        <v>42482</v>
+        <v>42911</v>
       </c>
       <c r="J17" t="n">
-        <v>255010</v>
+        <v>301408</v>
       </c>
       <c r="K17" t="n">
-        <v>103721</v>
+        <v>104150</v>
       </c>
     </row>
     <row r="18">
@@ -1176,32 +1176,32 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>928588.9</v>
+        <v>925448.6800000001</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>98495</v>
+        <v>99495</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>830093.9</v>
+        <v>825953.6800000001</v>
       </c>
       <c r="I18" t="n">
-        <v>226389</v>
+        <v>226862</v>
       </c>
       <c r="J18" t="n">
-        <v>602854</v>
+        <v>598241</v>
       </c>
       <c r="K18" t="n">
-        <v>501097</v>
+        <v>497161</v>
       </c>
     </row>
     <row r="19">
@@ -1219,11 +1219,11 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>321930.37</v>
+        <v>325448.53</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>321584.37</v>
+        <v>325102.53</v>
       </c>
       <c r="I19" t="n">
-        <v>41965</v>
+        <v>42018</v>
       </c>
       <c r="J19" t="n">
-        <v>258282</v>
+        <v>258680</v>
       </c>
       <c r="K19" t="n">
-        <v>92122</v>
+        <v>95242</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>372221.9</v>
+        <v>366769.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>49290</v>
+        <v>54328</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>322931.9</v>
+        <v>312441.9</v>
       </c>
       <c r="I20" t="n">
-        <v>36196</v>
+        <v>81128</v>
       </c>
       <c r="J20" t="n">
-        <v>286735</v>
+        <v>231313</v>
       </c>
       <c r="K20" t="n">
-        <v>41577</v>
+        <v>35091</v>
       </c>
     </row>
     <row r="21">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>536976.21</v>
+        <v>541467.21</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>136571.16</v>
+        <v>150423.16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>400405.0499999999</v>
+        <v>391044.0499999999</v>
       </c>
       <c r="I2" t="n">
-        <v>390771</v>
+        <v>380411</v>
       </c>
       <c r="J2" t="n">
-        <v>9634</v>
+        <v>10633</v>
       </c>
       <c r="K2" t="n">
-        <v>399415</v>
+        <v>399656</v>
       </c>
     </row>
     <row r="3">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>592959.0499999999</v>
+        <v>626869.3699999999</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>142094.8</v>
+        <v>152073.8</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>450864.2499999999</v>
+        <v>474795.5699999999</v>
       </c>
       <c r="I4" t="n">
-        <v>441641</v>
+        <v>465572</v>
       </c>
       <c r="J4" t="n">
         <v>9223</v>
       </c>
       <c r="K4" t="n">
-        <v>432680</v>
+        <v>456611</v>
       </c>
     </row>
     <row r="5">
@@ -617,7 +617,7 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>230387</v>
+        <v>230425</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -633,16 +633,16 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-9540.899999999994</v>
+        <v>-9502.899999999994</v>
       </c>
       <c r="I5" t="n">
-        <v>-14728</v>
+        <v>-14690</v>
       </c>
       <c r="J5" t="n">
         <v>5188</v>
       </c>
       <c r="K5" t="n">
-        <v>-121700</v>
+        <v>-121662</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>550501.45</v>
+        <v>588342.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>66616.89999999999</v>
+        <v>69645.89999999999</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>483884.5499999999</v>
+        <v>518696.5499999999</v>
       </c>
       <c r="I6" t="n">
-        <v>476958</v>
+        <v>511770</v>
       </c>
       <c r="J6" t="n">
         <v>6926</v>
       </c>
       <c r="K6" t="n">
-        <v>405723</v>
+        <v>430535</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>384191.89</v>
+        <v>390130.89</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>87008</v>
+        <v>92083</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>297183.89</v>
+        <v>298047.89</v>
       </c>
       <c r="I7" t="n">
-        <v>295465</v>
+        <v>296329</v>
       </c>
       <c r="J7" t="n">
         <v>1718</v>
       </c>
       <c r="K7" t="n">
-        <v>179871</v>
+        <v>175755</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>414738.04</v>
+        <v>423881.04</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>49.5%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>101687</v>
+        <v>106828</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>313051.04</v>
+        <v>317053.04</v>
       </c>
       <c r="I8" t="n">
-        <v>331455</v>
+        <v>335457</v>
       </c>
       <c r="J8" t="n">
         <v>-18404</v>
       </c>
       <c r="K8" t="n">
-        <v>271857</v>
+        <v>275859</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>863847.36</v>
+        <v>843371.8300000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>295700</v>
+        <v>315500</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>568147.36</v>
+        <v>527871.8300000001</v>
       </c>
       <c r="I9" t="n">
-        <v>430509</v>
+        <v>390233</v>
       </c>
       <c r="J9" t="n">
         <v>137638</v>
       </c>
       <c r="K9" t="n">
-        <v>292097</v>
+        <v>317461</v>
       </c>
     </row>
     <row r="10">
@@ -832,7 +832,7 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1503178.43</v>
+        <v>1503391.43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1473370.43</v>
+        <v>1473583.43</v>
       </c>
       <c r="I10" t="n">
-        <v>554088</v>
+        <v>555301</v>
       </c>
       <c r="J10" t="n">
-        <v>919281</v>
+        <v>918281</v>
       </c>
       <c r="K10" t="n">
-        <v>1429084</v>
+        <v>1429297</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>229338.34</v>
+        <v>239150.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>192938.36</v>
+        <v>202750.12</v>
       </c>
       <c r="I11" t="n">
-        <v>44746</v>
+        <v>51744</v>
       </c>
       <c r="J11" t="n">
-        <v>147981</v>
+        <v>150781</v>
       </c>
       <c r="K11" t="n">
-        <v>78988</v>
+        <v>87402</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>375246</v>
+        <v>375683</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>345170</v>
+        <v>345607</v>
       </c>
       <c r="I12" t="n">
-        <v>69115</v>
+        <v>69552</v>
       </c>
       <c r="J12" t="n">
         <v>276055</v>
       </c>
       <c r="K12" t="n">
-        <v>41570</v>
+        <v>41609</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>490573.37</v>
+        <v>527733.37</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>445559.7</v>
+        <v>482719.7</v>
       </c>
       <c r="I13" t="n">
-        <v>20453</v>
+        <v>29617</v>
       </c>
       <c r="J13" t="n">
-        <v>393891</v>
+        <v>421887</v>
       </c>
       <c r="K13" t="n">
-        <v>105309</v>
+        <v>105377</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>260814.3</v>
+        <v>263537.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,11 +1016,11 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>245948.3</v>
+        <v>248671.9</v>
       </c>
       <c r="I14" t="n">
         <v>41724</v>
@@ -1029,7 +1029,7 @@
         <v>187870</v>
       </c>
       <c r="K14" t="n">
-        <v>72400</v>
+        <v>75123</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>121625</v>
+        <v>122055</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1063,16 +1063,16 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>105768</v>
+        <v>106198</v>
       </c>
       <c r="I15" t="n">
-        <v>8049</v>
+        <v>8081</v>
       </c>
       <c r="J15" t="n">
-        <v>97719</v>
+        <v>98117</v>
       </c>
       <c r="K15" t="n">
-        <v>37996</v>
+        <v>38028</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>273707</v>
+        <v>291483</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>255309</v>
+        <v>273085</v>
       </c>
       <c r="I16" t="n">
-        <v>41136</v>
+        <v>41534</v>
       </c>
       <c r="J16" t="n">
-        <v>214173</v>
+        <v>231551</v>
       </c>
       <c r="K16" t="n">
-        <v>44261</v>
+        <v>46241</v>
       </c>
     </row>
     <row r="17">
@@ -1133,11 +1133,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>501582.69</v>
+        <v>532407.6900000001</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1145,20 +1145,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>413149.29</v>
+        <v>443974.29</v>
       </c>
       <c r="I17" t="n">
-        <v>42911</v>
+        <v>43338</v>
       </c>
       <c r="J17" t="n">
-        <v>301408</v>
+        <v>331806</v>
       </c>
       <c r="K17" t="n">
-        <v>104150</v>
+        <v>104179</v>
       </c>
     </row>
     <row r="18">
@@ -1176,11 +1176,11 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>925448.6800000001</v>
+        <v>981599.99</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1188,20 +1188,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>825953.6800000001</v>
+        <v>882104.99</v>
       </c>
       <c r="I18" t="n">
-        <v>226862</v>
+        <v>237298</v>
       </c>
       <c r="J18" t="n">
-        <v>598241</v>
+        <v>643956</v>
       </c>
       <c r="K18" t="n">
-        <v>497161</v>
+        <v>542914</v>
       </c>
     </row>
     <row r="19">
@@ -1219,11 +1219,11 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>325448.53</v>
+        <v>386469</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>325102.53</v>
+        <v>386123</v>
       </c>
       <c r="I19" t="n">
         <v>42018</v>
       </c>
       <c r="J19" t="n">
-        <v>258680</v>
+        <v>286180</v>
       </c>
       <c r="K19" t="n">
-        <v>95242</v>
+        <v>128763</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>366769.9</v>
+        <v>389753.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>54328</v>
+        <v>56427</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>312441.9</v>
+        <v>333326.9</v>
       </c>
       <c r="I20" t="n">
-        <v>81128</v>
+        <v>82613</v>
       </c>
       <c r="J20" t="n">
-        <v>231313</v>
+        <v>250713</v>
       </c>
       <c r="K20" t="n">
-        <v>35091</v>
+        <v>34776</v>
       </c>
     </row>
     <row r="21">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>541467.21</v>
+        <v>311994</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>150423.16</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>391044.0499999999</v>
+        <v>311994</v>
       </c>
       <c r="I2" t="n">
-        <v>380411</v>
+        <v>310870</v>
       </c>
       <c r="J2" t="n">
-        <v>10633</v>
+        <v>1124</v>
       </c>
       <c r="K2" t="n">
-        <v>399656</v>
+        <v>301596</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>2019</v>
+        <v>2000</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -539,24 +539,24 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>14980</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>742.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-12961</v>
+        <v>2000</v>
       </c>
       <c r="I3" t="n">
-        <v>-13096</v>
+        <v>1865</v>
       </c>
       <c r="J3" t="n">
         <v>135</v>
       </c>
       <c r="K3" t="n">
-        <v>-2961</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>626869.3699999999</v>
+        <v>447037.84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>152073.8</v>
+        <v>0</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>474795.5699999999</v>
+        <v>447037.84</v>
       </c>
       <c r="I4" t="n">
-        <v>465572</v>
+        <v>421007</v>
       </c>
       <c r="J4" t="n">
-        <v>9223</v>
+        <v>26029</v>
       </c>
       <c r="K4" t="n">
-        <v>456611</v>
+        <v>390251</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>230425</v>
+        <v>176054</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>239927.9</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>104.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-9502.899999999994</v>
+        <v>176054</v>
       </c>
       <c r="I5" t="n">
-        <v>-14690</v>
+        <v>132666</v>
       </c>
       <c r="J5" t="n">
-        <v>5188</v>
+        <v>43388</v>
       </c>
       <c r="K5" t="n">
-        <v>-121662</v>
+        <v>98414</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>588342.45</v>
+        <v>377840.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>69645.89999999999</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>518696.5499999999</v>
+        <v>377840.45</v>
       </c>
       <c r="I6" t="n">
-        <v>511770</v>
+        <v>370875</v>
       </c>
       <c r="J6" t="n">
-        <v>6926</v>
+        <v>6964</v>
       </c>
       <c r="K6" t="n">
-        <v>430535</v>
+        <v>310048</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>390130.89</v>
+        <v>276079.99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>76.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>92083</v>
+        <v>0</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>298047.89</v>
+        <v>276079.99</v>
       </c>
       <c r="I7" t="n">
-        <v>296329</v>
+        <v>244580</v>
       </c>
       <c r="J7" t="n">
-        <v>1718</v>
+        <v>31499</v>
       </c>
       <c r="K7" t="n">
-        <v>175755</v>
+        <v>161865</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>423881.04</v>
+        <v>302771.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>49.5%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>106828</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>317053.04</v>
+        <v>302771.62</v>
       </c>
       <c r="I8" t="n">
-        <v>335457</v>
+        <v>291538</v>
       </c>
       <c r="J8" t="n">
-        <v>-18404</v>
+        <v>11233</v>
       </c>
       <c r="K8" t="n">
-        <v>275859</v>
+        <v>259577</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>843371.8300000001</v>
+        <v>910887.8300000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>315500</v>
+        <v>377900</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>527871.8300000001</v>
+        <v>532987.8300000001</v>
       </c>
       <c r="I9" t="n">
-        <v>390233</v>
+        <v>395349</v>
       </c>
       <c r="J9" t="n">
         <v>137638</v>
       </c>
       <c r="K9" t="n">
-        <v>317461</v>
+        <v>269761</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1503391.43</v>
+        <v>1540234.13</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -844,20 +844,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1473583.43</v>
+        <v>1510426.13</v>
       </c>
       <c r="I10" t="n">
-        <v>555301</v>
+        <v>560593</v>
       </c>
       <c r="J10" t="n">
-        <v>918281</v>
+        <v>949832</v>
       </c>
       <c r="K10" t="n">
-        <v>1429297</v>
+        <v>1466140</v>
       </c>
     </row>
     <row r="11">
@@ -875,7 +875,7 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>239150.1</v>
+        <v>239169.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>202750.12</v>
+        <v>202769.12</v>
       </c>
       <c r="I11" t="n">
-        <v>51744</v>
+        <v>51763</v>
       </c>
       <c r="J11" t="n">
         <v>150781</v>
       </c>
       <c r="K11" t="n">
-        <v>87402</v>
+        <v>87421</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>375683</v>
+        <v>386380</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>89.1%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>345607</v>
+        <v>356304</v>
       </c>
       <c r="I12" t="n">
-        <v>69552</v>
+        <v>69851</v>
       </c>
       <c r="J12" t="n">
-        <v>276055</v>
+        <v>286453</v>
       </c>
       <c r="K12" t="n">
-        <v>41609</v>
+        <v>41908</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>527733.37</v>
+        <v>559255.27</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>482719.7</v>
+        <v>514241.6</v>
       </c>
       <c r="I13" t="n">
-        <v>29617</v>
+        <v>29646</v>
       </c>
       <c r="J13" t="n">
-        <v>421887</v>
+        <v>452902</v>
       </c>
       <c r="K13" t="n">
-        <v>105377</v>
+        <v>106103</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>263537.9</v>
+        <v>265862.95</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>248671.9</v>
+        <v>250996.95</v>
       </c>
       <c r="I14" t="n">
-        <v>41724</v>
+        <v>42322</v>
       </c>
       <c r="J14" t="n">
-        <v>187870</v>
+        <v>188268</v>
       </c>
       <c r="K14" t="n">
-        <v>75123</v>
+        <v>76452</v>
       </c>
     </row>
     <row r="15">
@@ -1090,29 +1090,29 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>291483</v>
+        <v>311483</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>18398</v>
+        <v>48398</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>273085</v>
+        <v>263085</v>
       </c>
       <c r="I16" t="n">
-        <v>41534</v>
+        <v>21534</v>
       </c>
       <c r="J16" t="n">
-        <v>231551</v>
+        <v>241551</v>
       </c>
       <c r="K16" t="n">
         <v>46241</v>
@@ -1133,32 +1133,32 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>532407.6900000001</v>
+        <v>534173.05</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>88433.39999999999</v>
+        <v>105631.4</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>443974.29</v>
+        <v>428541.65</v>
       </c>
       <c r="I17" t="n">
-        <v>43338</v>
+        <v>43538</v>
       </c>
       <c r="J17" t="n">
-        <v>331806</v>
+        <v>315604</v>
       </c>
       <c r="K17" t="n">
-        <v>104179</v>
+        <v>87949</v>
       </c>
     </row>
     <row r="18">
@@ -1176,32 +1176,32 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>981599.99</v>
+        <v>999752.99</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>99495</v>
+        <v>108845</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>882104.99</v>
+        <v>890907.99</v>
       </c>
       <c r="I18" t="n">
-        <v>237298</v>
+        <v>228297</v>
       </c>
       <c r="J18" t="n">
-        <v>643956</v>
+        <v>661760</v>
       </c>
       <c r="K18" t="n">
-        <v>542914</v>
+        <v>536921</v>
       </c>
     </row>
     <row r="19">
@@ -1219,32 +1219,32 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>386469</v>
+        <v>411284</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>346</v>
+        <v>30346</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>386123</v>
+        <v>380938</v>
       </c>
       <c r="I19" t="n">
-        <v>42018</v>
+        <v>42416</v>
       </c>
       <c r="J19" t="n">
-        <v>286180</v>
+        <v>280597</v>
       </c>
       <c r="K19" t="n">
-        <v>128763</v>
+        <v>128782</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>389753.9</v>
+        <v>401887.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>56427</v>
+        <v>56436</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>333326.9</v>
+        <v>345451.9</v>
       </c>
       <c r="I20" t="n">
-        <v>82613</v>
+        <v>83058</v>
       </c>
       <c r="J20" t="n">
-        <v>250713</v>
+        <v>262393</v>
       </c>
       <c r="K20" t="n">
-        <v>34776</v>
+        <v>36503</v>
       </c>
     </row>
     <row r="21">
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>14920</v>
+        <v>1110892.89</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1313,24 +1313,24 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>18111</v>
+        <v>802687.66</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>121.4%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>-3191</v>
+        <v>308205.2299999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-16391</v>
+        <v>376721</v>
       </c>
       <c r="J21" t="n">
-        <v>13200</v>
+        <v>-68516</v>
       </c>
       <c r="K21" t="n">
-        <v>-770</v>
+        <v>266673</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>311994</v>
+        <v>559704</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>123625.16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>311994</v>
+        <v>436078.84</v>
       </c>
       <c r="I2" t="n">
-        <v>310870</v>
+        <v>426734</v>
       </c>
       <c r="J2" t="n">
-        <v>1124</v>
+        <v>9344</v>
       </c>
       <c r="K2" t="n">
-        <v>301596</v>
+        <v>444690</v>
       </c>
     </row>
     <row r="3">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>447037.84</v>
+        <v>622555.84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>103159</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>447037.84</v>
+        <v>519396.84</v>
       </c>
       <c r="I4" t="n">
-        <v>421007</v>
+        <v>505366</v>
       </c>
       <c r="J4" t="n">
-        <v>26029</v>
+        <v>14029</v>
       </c>
       <c r="K4" t="n">
-        <v>390251</v>
+        <v>486212</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>176054</v>
+        <v>234954</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>157581</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>176054</v>
+        <v>77373</v>
       </c>
       <c r="I5" t="n">
-        <v>132666</v>
+        <v>72185</v>
       </c>
       <c r="J5" t="n">
-        <v>43388</v>
+        <v>5188</v>
       </c>
       <c r="K5" t="n">
-        <v>98414</v>
+        <v>-34787</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>377840.45</v>
+        <v>627658.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>44360</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>377840.45</v>
+        <v>583298.45</v>
       </c>
       <c r="I6" t="n">
-        <v>370875</v>
+        <v>576333</v>
       </c>
       <c r="J6" t="n">
         <v>6964</v>
       </c>
       <c r="K6" t="n">
-        <v>310048</v>
+        <v>472308</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>276079.99</v>
+        <v>386795.99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.7%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>89097</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>276079.99</v>
+        <v>297698.99</v>
       </c>
       <c r="I7" t="n">
-        <v>244580</v>
+        <v>298479</v>
       </c>
       <c r="J7" t="n">
-        <v>31499</v>
+        <v>-781</v>
       </c>
       <c r="K7" t="n">
-        <v>161865</v>
+        <v>175008</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>302771.62</v>
+        <v>418671.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>105733</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>302771.62</v>
+        <v>312938.62</v>
       </c>
       <c r="I8" t="n">
-        <v>291538</v>
+        <v>331505</v>
       </c>
       <c r="J8" t="n">
-        <v>11233</v>
+        <v>-18567</v>
       </c>
       <c r="K8" t="n">
-        <v>259577</v>
+        <v>271744</v>
       </c>
     </row>
     <row r="9">
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>1110892.89</v>
+        <v>152330.89</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1313,24 +1313,24 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>802687.66</v>
+        <v>179132.5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>117.6%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>308205.2299999999</v>
+        <v>-26801.60999999996</v>
       </c>
       <c r="I21" t="n">
-        <v>376721</v>
+        <v>-62345</v>
       </c>
       <c r="J21" t="n">
-        <v>-68516</v>
+        <v>35543</v>
       </c>
       <c r="K21" t="n">
-        <v>266673</v>
+        <v>-26751</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,11 +488,11 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>559704</v>
+        <v>619464</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -500,20 +500,20 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>436078.84</v>
+        <v>495838.84</v>
       </c>
       <c r="I2" t="n">
-        <v>426734</v>
+        <v>486494</v>
       </c>
       <c r="J2" t="n">
         <v>9344</v>
       </c>
       <c r="K2" t="n">
-        <v>444690</v>
+        <v>504450</v>
       </c>
     </row>
     <row r="3">
@@ -574,11 +574,11 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>622555.84</v>
+        <v>632913.84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -586,20 +586,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>519396.84</v>
+        <v>529754.84</v>
       </c>
       <c r="I4" t="n">
-        <v>505366</v>
+        <v>515724</v>
       </c>
       <c r="J4" t="n">
         <v>14029</v>
       </c>
       <c r="K4" t="n">
-        <v>486212</v>
+        <v>496172</v>
       </c>
     </row>
     <row r="5">
@@ -617,11 +617,11 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>234954</v>
+        <v>241974</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -629,20 +629,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>77373</v>
+        <v>84393</v>
       </c>
       <c r="I5" t="n">
-        <v>72185</v>
+        <v>79205</v>
       </c>
       <c r="J5" t="n">
         <v>5188</v>
       </c>
       <c r="K5" t="n">
-        <v>-34787</v>
+        <v>-39767</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>627658.45</v>
+        <v>688414.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>107.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>44360</v>
+        <v>46360</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>583298.45</v>
+        <v>642054.45</v>
       </c>
       <c r="I6" t="n">
-        <v>576333</v>
+        <v>635089</v>
       </c>
       <c r="J6" t="n">
         <v>6964</v>
       </c>
       <c r="K6" t="n">
-        <v>472308</v>
+        <v>530068</v>
       </c>
     </row>
     <row r="7">
@@ -703,11 +703,11 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>386795.99</v>
+        <v>433553.99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -715,20 +715,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>297698.99</v>
+        <v>344456.99</v>
       </c>
       <c r="I7" t="n">
-        <v>298479</v>
+        <v>345237</v>
       </c>
       <c r="J7" t="n">
         <v>-781</v>
       </c>
       <c r="K7" t="n">
-        <v>175008</v>
+        <v>209868</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>418671.62</v>
+        <v>421147.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>105733</v>
+        <v>109433</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>312938.62</v>
+        <v>311714.62</v>
       </c>
       <c r="I8" t="n">
-        <v>331505</v>
+        <v>330281</v>
       </c>
       <c r="J8" t="n">
         <v>-18567</v>
       </c>
       <c r="K8" t="n">
-        <v>271744</v>
+        <v>269724</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>910887.8300000001</v>
+        <v>927927.8300000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>377900</v>
+        <v>388060</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>532987.8300000001</v>
+        <v>539867.8300000001</v>
       </c>
       <c r="I9" t="n">
-        <v>395349</v>
+        <v>402229</v>
       </c>
       <c r="J9" t="n">
         <v>137638</v>
       </c>
       <c r="K9" t="n">
-        <v>269761</v>
+        <v>276243</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1540234.13</v>
+        <v>1771164.350000001</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>29808</v>
+        <v>47508</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1510426.13</v>
+        <v>1723656.350000001</v>
       </c>
       <c r="I10" t="n">
-        <v>560593</v>
+        <v>712253</v>
       </c>
       <c r="J10" t="n">
-        <v>949832</v>
+        <v>1011402</v>
       </c>
       <c r="K10" t="n">
-        <v>1466140</v>
+        <v>1691672</v>
       </c>
     </row>
     <row r="11">
@@ -875,32 +875,32 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>239169.1</v>
+        <v>256386.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>36399.98</v>
+        <v>37233.35</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>202769.12</v>
+        <v>219152.75</v>
       </c>
       <c r="I11" t="n">
-        <v>51763</v>
+        <v>51347</v>
       </c>
       <c r="J11" t="n">
-        <v>150781</v>
+        <v>167581</v>
       </c>
       <c r="K11" t="n">
-        <v>87421</v>
+        <v>104240</v>
       </c>
     </row>
     <row r="12">
@@ -918,32 +918,32 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>386380</v>
+        <v>410398</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>89.1%</t>
+          <t>95.1%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30076</v>
+        <v>30095</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>356304</v>
+        <v>380303</v>
       </c>
       <c r="I12" t="n">
-        <v>69851</v>
+        <v>65260</v>
       </c>
       <c r="J12" t="n">
-        <v>286453</v>
+        <v>315043</v>
       </c>
       <c r="K12" t="n">
-        <v>41908</v>
+        <v>41927</v>
       </c>
     </row>
     <row r="13">
@@ -961,32 +961,32 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>559255.27</v>
+        <v>566324.15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>45013.67</v>
+        <v>50513.67</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>514241.6</v>
+        <v>515810.48</v>
       </c>
       <c r="I13" t="n">
-        <v>29646</v>
+        <v>30480</v>
       </c>
       <c r="J13" t="n">
-        <v>452902</v>
+        <v>453602</v>
       </c>
       <c r="K13" t="n">
-        <v>106103</v>
+        <v>106176</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>265862.95</v>
+        <v>296518.55</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>250996.95</v>
+        <v>281652.55</v>
       </c>
       <c r="I14" t="n">
-        <v>42322</v>
+        <v>52739</v>
       </c>
       <c r="J14" t="n">
-        <v>188268</v>
+        <v>208268</v>
       </c>
       <c r="K14" t="n">
-        <v>76452</v>
+        <v>76710</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>122055</v>
+        <v>141912</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>106198</v>
+        <v>126055</v>
       </c>
       <c r="I15" t="n">
-        <v>8081</v>
+        <v>8119</v>
       </c>
       <c r="J15" t="n">
-        <v>98117</v>
+        <v>117936</v>
       </c>
       <c r="K15" t="n">
-        <v>38028</v>
+        <v>38085</v>
       </c>
     </row>
     <row r="16">
@@ -1090,32 +1090,32 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>311483</v>
+        <v>320679</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>48398</v>
+        <v>68917</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>263085</v>
+        <v>251762</v>
       </c>
       <c r="I16" t="n">
-        <v>21534</v>
+        <v>12711</v>
       </c>
       <c r="J16" t="n">
-        <v>241551</v>
+        <v>239051</v>
       </c>
       <c r="K16" t="n">
-        <v>46241</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="17">
@@ -1133,11 +1133,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>534173.05</v>
+        <v>580567.05</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1145,20 +1145,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>428541.65</v>
+        <v>474935.65</v>
       </c>
       <c r="I17" t="n">
         <v>43538</v>
       </c>
       <c r="J17" t="n">
-        <v>315604</v>
+        <v>361998</v>
       </c>
       <c r="K17" t="n">
-        <v>87949</v>
+        <v>105549</v>
       </c>
     </row>
     <row r="18">
@@ -1176,32 +1176,32 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>999752.99</v>
+        <v>1046375.97</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>103.2%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>108845</v>
+        <v>117874</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>890907.99</v>
+        <v>928501.97</v>
       </c>
       <c r="I18" t="n">
-        <v>228297</v>
+        <v>229083</v>
       </c>
       <c r="J18" t="n">
-        <v>661760</v>
+        <v>698568</v>
       </c>
       <c r="K18" t="n">
-        <v>536921</v>
+        <v>546719</v>
       </c>
     </row>
     <row r="19">
@@ -1219,11 +1219,11 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>411284</v>
+        <v>493397.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1231,20 +1231,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>380938</v>
+        <v>463051.3</v>
       </c>
       <c r="I19" t="n">
-        <v>42416</v>
+        <v>77753</v>
       </c>
       <c r="J19" t="n">
-        <v>280597</v>
+        <v>325497</v>
       </c>
       <c r="K19" t="n">
-        <v>128782</v>
+        <v>135597</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>401887.9</v>
+        <v>413230.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>56436</v>
+        <v>99955</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>345451.9</v>
+        <v>313275.9</v>
       </c>
       <c r="I20" t="n">
-        <v>83058</v>
+        <v>58688</v>
       </c>
       <c r="J20" t="n">
-        <v>262393</v>
+        <v>254587</v>
       </c>
       <c r="K20" t="n">
-        <v>36503</v>
+        <v>41633</v>
       </c>
     </row>
     <row r="21">
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>152330.89</v>
+        <v>179276.74</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1313,24 +1313,24 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>179132.5</v>
+        <v>182489.5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>117.6%</t>
+          <t>101.8%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>-26801.60999999996</v>
+        <v>-3212.75999999998</v>
       </c>
       <c r="I21" t="n">
-        <v>-62345</v>
+        <v>-39050</v>
       </c>
       <c r="J21" t="n">
-        <v>35543</v>
+        <v>35837</v>
       </c>
       <c r="K21" t="n">
-        <v>-26751</v>
+        <v>-3162</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -664,28 +664,28 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>107.0%</t>
+          <t>105.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>46360</v>
+        <v>54490</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>642054.45</v>
+        <v>633924.45</v>
       </c>
       <c r="I6" t="n">
-        <v>635089</v>
+        <v>626959</v>
       </c>
       <c r="J6" t="n">
         <v>6964</v>
       </c>
       <c r="K6" t="n">
-        <v>530068</v>
+        <v>521938</v>
       </c>
     </row>
     <row r="7">
@@ -1313,24 +1313,24 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>182489.5</v>
+        <v>174359.5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>101.8%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>-3212.75999999998</v>
+        <v>4917.239999999991</v>
       </c>
       <c r="I21" t="n">
-        <v>-39050</v>
+        <v>-30920</v>
       </c>
       <c r="J21" t="n">
         <v>35837</v>
       </c>
       <c r="K21" t="n">
-        <v>-3162</v>
+        <v>4967</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,11 +488,11 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>619464</v>
+        <v>619862</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -500,14 +500,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>495838.84</v>
+        <v>496236.84</v>
       </c>
       <c r="I2" t="n">
-        <v>486494</v>
+        <v>486892</v>
       </c>
       <c r="J2" t="n">
         <v>9344</v>
@@ -574,11 +574,11 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>632913.84</v>
+        <v>639573.84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -586,20 +586,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>529754.84</v>
+        <v>536414.84</v>
       </c>
       <c r="I4" t="n">
-        <v>515724</v>
+        <v>520704</v>
       </c>
       <c r="J4" t="n">
-        <v>14029</v>
+        <v>15709</v>
       </c>
       <c r="K4" t="n">
-        <v>496172</v>
+        <v>502832</v>
       </c>
     </row>
     <row r="5">
@@ -617,11 +617,11 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>241974</v>
+        <v>243954</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -629,20 +629,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>84393</v>
+        <v>86373</v>
       </c>
       <c r="I5" t="n">
-        <v>79205</v>
+        <v>81185</v>
       </c>
       <c r="J5" t="n">
         <v>5188</v>
       </c>
       <c r="K5" t="n">
-        <v>-39767</v>
+        <v>-37787</v>
       </c>
     </row>
     <row r="6">
@@ -660,11 +660,11 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>688414.45</v>
+        <v>695014.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>105.7%</t>
+          <t>106.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -672,20 +672,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>633924.45</v>
+        <v>640524.45</v>
       </c>
       <c r="I6" t="n">
-        <v>626959</v>
+        <v>633559</v>
       </c>
       <c r="J6" t="n">
         <v>6964</v>
       </c>
       <c r="K6" t="n">
-        <v>521938</v>
+        <v>528538</v>
       </c>
     </row>
     <row r="7">
@@ -703,11 +703,11 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>433553.99</v>
+        <v>438533.99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -715,20 +715,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>344456.99</v>
+        <v>349436.99</v>
       </c>
       <c r="I7" t="n">
-        <v>345237</v>
+        <v>350217</v>
       </c>
       <c r="J7" t="n">
         <v>-781</v>
       </c>
       <c r="K7" t="n">
-        <v>209868</v>
+        <v>214848</v>
       </c>
     </row>
     <row r="8">
@@ -789,11 +789,11 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>927927.8300000001</v>
+        <v>934527.8300000001</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>539867.8300000001</v>
+        <v>546467.8300000001</v>
       </c>
       <c r="I9" t="n">
-        <v>402229</v>
+        <v>408829</v>
       </c>
       <c r="J9" t="n">
         <v>137638</v>
       </c>
       <c r="K9" t="n">
-        <v>276243</v>
+        <v>282843</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1771164.350000001</v>
+        <v>1890333.67</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>92.1%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -844,20 +844,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1723656.350000001</v>
+        <v>1842825.67</v>
       </c>
       <c r="I10" t="n">
-        <v>712253</v>
+        <v>775873</v>
       </c>
       <c r="J10" t="n">
-        <v>1011402</v>
+        <v>1066952</v>
       </c>
       <c r="K10" t="n">
-        <v>1691672</v>
+        <v>1810841</v>
       </c>
     </row>
     <row r="11">
@@ -875,7 +875,7 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>256386.1</v>
+        <v>256605.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>219152.75</v>
+        <v>219371.75</v>
       </c>
       <c r="I11" t="n">
-        <v>51347</v>
+        <v>51366</v>
       </c>
       <c r="J11" t="n">
-        <v>167581</v>
+        <v>167781</v>
       </c>
       <c r="K11" t="n">
-        <v>104240</v>
+        <v>104459</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>410398</v>
+        <v>431592</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>95.1%</t>
+          <t>100.4%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,17 +930,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>380303</v>
+        <v>401497</v>
       </c>
       <c r="I12" t="n">
-        <v>65260</v>
+        <v>65658</v>
       </c>
       <c r="J12" t="n">
-        <v>315043</v>
+        <v>335839</v>
       </c>
       <c r="K12" t="n">
         <v>41927</v>
@@ -961,29 +961,29 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>566324.15</v>
+        <v>596939.15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50513.67</v>
+        <v>50532.67</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>515810.48</v>
+        <v>546406.48</v>
       </c>
       <c r="I13" t="n">
         <v>30480</v>
       </c>
       <c r="J13" t="n">
-        <v>453602</v>
+        <v>484198</v>
       </c>
       <c r="K13" t="n">
         <v>106176</v>
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>296518.55</v>
+        <v>312840.65</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>281652.55</v>
+        <v>297974.65</v>
       </c>
       <c r="I14" t="n">
         <v>52739</v>
       </c>
       <c r="J14" t="n">
-        <v>208268</v>
+        <v>218268</v>
       </c>
       <c r="K14" t="n">
-        <v>76710</v>
+        <v>83032</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>141912</v>
+        <v>142310</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,14 +1059,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>126055</v>
+        <v>126453</v>
       </c>
       <c r="I15" t="n">
-        <v>8119</v>
+        <v>8517</v>
       </c>
       <c r="J15" t="n">
         <v>117936</v>
@@ -1090,11 +1090,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>320679</v>
+        <v>323355</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>251762</v>
+        <v>254438</v>
       </c>
       <c r="I16" t="n">
-        <v>12711</v>
+        <v>5109</v>
       </c>
       <c r="J16" t="n">
-        <v>239051</v>
+        <v>249329</v>
       </c>
       <c r="K16" t="n">
-        <v>46222</v>
+        <v>47902</v>
       </c>
     </row>
     <row r="17">
@@ -1176,11 +1176,11 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>1046375.97</v>
+        <v>1067536.97</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>103.2%</t>
+          <t>105.5%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1188,20 +1188,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>928501.97</v>
+        <v>949662.97</v>
       </c>
       <c r="I18" t="n">
-        <v>229083</v>
+        <v>230864</v>
       </c>
       <c r="J18" t="n">
-        <v>698568</v>
+        <v>711548</v>
       </c>
       <c r="K18" t="n">
-        <v>546719</v>
+        <v>556880</v>
       </c>
     </row>
     <row r="19">
@@ -1219,11 +1219,11 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>493397.3</v>
+        <v>510447.64</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1231,20 +1231,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>463051.3</v>
+        <v>480101.64</v>
       </c>
       <c r="I19" t="n">
-        <v>77753</v>
+        <v>85253</v>
       </c>
       <c r="J19" t="n">
-        <v>325497</v>
+        <v>333797</v>
       </c>
       <c r="K19" t="n">
-        <v>135597</v>
+        <v>136847</v>
       </c>
     </row>
     <row r="20">
@@ -1262,11 +1262,11 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>413230.9</v>
+        <v>450256.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>313275.9</v>
+        <v>350301.9</v>
       </c>
       <c r="I20" t="n">
-        <v>58688</v>
+        <v>65316</v>
       </c>
       <c r="J20" t="n">
-        <v>254587</v>
+        <v>284985</v>
       </c>
       <c r="K20" t="n">
-        <v>41633</v>
+        <v>48261</v>
       </c>
     </row>
     <row r="21">
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>179276.74</v>
+        <v>182907.74</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1313,24 +1313,24 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>174359.5</v>
+        <v>177578.5</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>4917.239999999991</v>
+        <v>5329.239999999991</v>
       </c>
       <c r="I21" t="n">
-        <v>-30920</v>
+        <v>-30508</v>
       </c>
       <c r="J21" t="n">
         <v>35837</v>
       </c>
       <c r="K21" t="n">
-        <v>4967</v>
+        <v>5379</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>619862</v>
+        <v>632101</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>123625.16</v>
+        <v>129095.16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>496236.84</v>
+        <v>503005.84</v>
       </c>
       <c r="I2" t="n">
-        <v>486892</v>
+        <v>493661</v>
       </c>
       <c r="J2" t="n">
         <v>9344</v>
       </c>
       <c r="K2" t="n">
-        <v>504450</v>
+        <v>511219</v>
       </c>
     </row>
     <row r="3">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>639573.84</v>
+        <v>724153.84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>103159</v>
+        <v>128972.4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>536414.84</v>
+        <v>595181.4399999999</v>
       </c>
       <c r="I4" t="n">
-        <v>520704</v>
+        <v>579471</v>
       </c>
       <c r="J4" t="n">
         <v>15709</v>
       </c>
       <c r="K4" t="n">
-        <v>502832</v>
+        <v>561599</v>
       </c>
     </row>
     <row r="5">
@@ -617,11 +617,11 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>243954</v>
+        <v>245934</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -629,20 +629,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>86373</v>
+        <v>88353</v>
       </c>
       <c r="I5" t="n">
-        <v>81185</v>
+        <v>83165</v>
       </c>
       <c r="J5" t="n">
         <v>5188</v>
       </c>
       <c r="K5" t="n">
-        <v>-37787</v>
+        <v>-35807</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>695014.45</v>
+        <v>725312.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>106.8%</t>
+          <t>110.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>54490</v>
+        <v>64470</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>640524.45</v>
+        <v>660842.45</v>
       </c>
       <c r="I6" t="n">
-        <v>633559</v>
+        <v>653877</v>
       </c>
       <c r="J6" t="n">
         <v>6964</v>
       </c>
       <c r="K6" t="n">
-        <v>528538</v>
+        <v>553458</v>
       </c>
     </row>
     <row r="7">
@@ -703,11 +703,11 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>438533.99</v>
+        <v>446633.99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -715,20 +715,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>349436.99</v>
+        <v>357536.99</v>
       </c>
       <c r="I7" t="n">
-        <v>350217</v>
+        <v>358317</v>
       </c>
       <c r="J7" t="n">
         <v>-781</v>
       </c>
       <c r="K7" t="n">
-        <v>214848</v>
+        <v>221448</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>421147.62</v>
+        <v>482607.6200000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>109433</v>
+        <v>135030</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>311714.62</v>
+        <v>347577.6200000001</v>
       </c>
       <c r="I8" t="n">
-        <v>330281</v>
+        <v>366144</v>
       </c>
       <c r="J8" t="n">
         <v>-18567</v>
       </c>
       <c r="K8" t="n">
-        <v>269724</v>
+        <v>285587</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>934527.8300000001</v>
+        <v>1007327.83</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>388060</v>
+        <v>419460</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>546467.8300000001</v>
+        <v>587867.83</v>
       </c>
       <c r="I9" t="n">
-        <v>408829</v>
+        <v>456829</v>
       </c>
       <c r="J9" t="n">
-        <v>137638</v>
+        <v>131038</v>
       </c>
       <c r="K9" t="n">
-        <v>282843</v>
+        <v>324243</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1890333.67</v>
+        <v>1924782.67</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1842825.67</v>
+        <v>1877274.67</v>
       </c>
       <c r="I10" t="n">
         <v>775873</v>
       </c>
       <c r="J10" t="n">
-        <v>1066952</v>
+        <v>1101401</v>
       </c>
       <c r="K10" t="n">
-        <v>1810841</v>
+        <v>1845290</v>
       </c>
     </row>
     <row r="11">
@@ -875,7 +875,7 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>256605.1</v>
+        <v>256615.45</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>219371.75</v>
+        <v>219382.1</v>
       </c>
       <c r="I11" t="n">
         <v>51366</v>
@@ -900,7 +900,7 @@
         <v>167781</v>
       </c>
       <c r="K11" t="n">
-        <v>104459</v>
+        <v>104469</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>431592</v>
+        <v>453582</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>100.4%</t>
+          <t>105.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,17 +930,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>401497</v>
+        <v>423487</v>
       </c>
       <c r="I12" t="n">
-        <v>65658</v>
+        <v>66852</v>
       </c>
       <c r="J12" t="n">
-        <v>335839</v>
+        <v>356635</v>
       </c>
       <c r="K12" t="n">
         <v>41927</v>
@@ -961,32 +961,32 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>596939.15</v>
+        <v>617720.15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>50532.67</v>
+        <v>68261.67</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>546406.48</v>
+        <v>549458.48</v>
       </c>
       <c r="I13" t="n">
-        <v>30480</v>
+        <v>37951</v>
       </c>
       <c r="J13" t="n">
-        <v>484198</v>
+        <v>479779</v>
       </c>
       <c r="K13" t="n">
-        <v>106176</v>
+        <v>106128</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>312840.65</v>
+        <v>323238.65</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,17 +1016,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>297974.65</v>
+        <v>308372.65</v>
       </c>
       <c r="I14" t="n">
-        <v>52739</v>
+        <v>53137</v>
       </c>
       <c r="J14" t="n">
-        <v>218268</v>
+        <v>228268</v>
       </c>
       <c r="K14" t="n">
         <v>83032</v>
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>142310</v>
+        <v>148328</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>126453</v>
+        <v>132471</v>
       </c>
       <c r="I15" t="n">
-        <v>8517</v>
+        <v>8555</v>
       </c>
       <c r="J15" t="n">
-        <v>117936</v>
+        <v>123916</v>
       </c>
       <c r="K15" t="n">
-        <v>38085</v>
+        <v>39123</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>323355</v>
+        <v>354151</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,17 +1102,17 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>254438</v>
+        <v>285234</v>
       </c>
       <c r="I16" t="n">
-        <v>5109</v>
+        <v>17507</v>
       </c>
       <c r="J16" t="n">
-        <v>249329</v>
+        <v>267727</v>
       </c>
       <c r="K16" t="n">
         <v>47902</v>
@@ -1133,11 +1133,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>580567.05</v>
+        <v>619530.29</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1145,20 +1145,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>474935.65</v>
+        <v>513898.89</v>
       </c>
       <c r="I17" t="n">
-        <v>43538</v>
+        <v>44534</v>
       </c>
       <c r="J17" t="n">
-        <v>361998</v>
+        <v>399896</v>
       </c>
       <c r="K17" t="n">
-        <v>105549</v>
+        <v>141618</v>
       </c>
     </row>
     <row r="18">
@@ -1176,32 +1176,32 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>1067536.97</v>
+        <v>1082655.59</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>105.5%</t>
+          <t>104.4%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>117874</v>
+        <v>142696.24</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>949662.97</v>
+        <v>939959.3500000001</v>
       </c>
       <c r="I18" t="n">
-        <v>230864</v>
+        <v>229968</v>
       </c>
       <c r="J18" t="n">
-        <v>711548</v>
+        <v>702741</v>
       </c>
       <c r="K18" t="n">
-        <v>556880</v>
+        <v>552807</v>
       </c>
     </row>
     <row r="19">
@@ -1219,32 +1219,32 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>510447.64</v>
+        <v>541587.87</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>30346</v>
+        <v>86946</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>480101.64</v>
+        <v>454641.87</v>
       </c>
       <c r="I19" t="n">
-        <v>85253</v>
+        <v>69553</v>
       </c>
       <c r="J19" t="n">
-        <v>333797</v>
+        <v>323897</v>
       </c>
       <c r="K19" t="n">
-        <v>136847</v>
+        <v>136987</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>450256.9</v>
+        <v>468751.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>99955</v>
+        <v>105502</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>350301.9</v>
+        <v>363249.9</v>
       </c>
       <c r="I20" t="n">
-        <v>65316</v>
+        <v>60364</v>
       </c>
       <c r="J20" t="n">
-        <v>284985</v>
+        <v>302885</v>
       </c>
       <c r="K20" t="n">
-        <v>48261</v>
+        <v>66709</v>
       </c>
     </row>
     <row r="21">
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>182907.74</v>
+        <v>213094.74</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1313,24 +1313,24 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>177578.5</v>
+        <v>184809.52</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5329.239999999991</v>
+        <v>28285.22</v>
       </c>
       <c r="I21" t="n">
-        <v>-30508</v>
+        <v>-14171</v>
       </c>
       <c r="J21" t="n">
-        <v>35837</v>
+        <v>42456</v>
       </c>
       <c r="K21" t="n">
-        <v>5379</v>
+        <v>31733</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -492,22 +492,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>129095.16</v>
+        <v>132095.16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>503005.84</v>
+        <v>500005.84</v>
       </c>
       <c r="I2" t="n">
-        <v>493661</v>
+        <v>490661</v>
       </c>
       <c r="J2" t="n">
         <v>9344</v>
@@ -1313,18 +1313,18 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>184809.52</v>
+        <v>181809.52</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>85.3%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>28285.22</v>
+        <v>31285.22</v>
       </c>
       <c r="I21" t="n">
-        <v>-14171</v>
+        <v>-11171</v>
       </c>
       <c r="J21" t="n">
         <v>42456</v>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,11 +488,11 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>632101</v>
+        <v>665361</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -500,20 +500,20 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>500005.84</v>
+        <v>533265.84</v>
       </c>
       <c r="I2" t="n">
-        <v>490661</v>
+        <v>523921</v>
       </c>
       <c r="J2" t="n">
         <v>9344</v>
       </c>
       <c r="K2" t="n">
-        <v>511219</v>
+        <v>544479</v>
       </c>
     </row>
     <row r="3">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>724153.84</v>
+        <v>753933.84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>80.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>128972.4</v>
+        <v>138932.4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>595181.4399999999</v>
+        <v>615001.4399999999</v>
       </c>
       <c r="I4" t="n">
-        <v>579471</v>
+        <v>599291</v>
       </c>
       <c r="J4" t="n">
         <v>15709</v>
       </c>
       <c r="K4" t="n">
-        <v>561599</v>
+        <v>581419</v>
       </c>
     </row>
     <row r="5">
@@ -617,11 +617,11 @@
         <v>520000</v>
       </c>
       <c r="D5" t="n">
-        <v>245934</v>
+        <v>247834</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -629,20 +629,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>88353</v>
+        <v>90253</v>
       </c>
       <c r="I5" t="n">
-        <v>83165</v>
+        <v>85065</v>
       </c>
       <c r="J5" t="n">
         <v>5188</v>
       </c>
       <c r="K5" t="n">
-        <v>-35807</v>
+        <v>-33907</v>
       </c>
     </row>
     <row r="6">
@@ -660,11 +660,11 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>725312.45</v>
+        <v>740292.45</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>110.1%</t>
+          <t>112.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -672,20 +672,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>660842.45</v>
+        <v>675822.45</v>
       </c>
       <c r="I6" t="n">
-        <v>653877</v>
+        <v>668857</v>
       </c>
       <c r="J6" t="n">
         <v>6964</v>
       </c>
       <c r="K6" t="n">
-        <v>553458</v>
+        <v>558438</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>446633.99</v>
+        <v>461633.99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>89097</v>
+        <v>94077</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>357536.99</v>
+        <v>367556.99</v>
       </c>
       <c r="I7" t="n">
-        <v>358317</v>
+        <v>368337</v>
       </c>
       <c r="J7" t="n">
         <v>-781</v>
       </c>
       <c r="K7" t="n">
-        <v>221448</v>
+        <v>216468</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>482607.6200000001</v>
+        <v>417947.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>135030</v>
+        <v>52608</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>347577.6200000001</v>
+        <v>365339.62</v>
       </c>
       <c r="I8" t="n">
-        <v>366144</v>
+        <v>354106</v>
       </c>
       <c r="J8" t="n">
-        <v>-18567</v>
+        <v>11233</v>
       </c>
       <c r="K8" t="n">
-        <v>285587</v>
+        <v>311349</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>1007327.83</v>
+        <v>1034247.83</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>587867.83</v>
+        <v>614787.83</v>
       </c>
       <c r="I9" t="n">
-        <v>456829</v>
+        <v>483749</v>
       </c>
       <c r="J9" t="n">
         <v>131038</v>
       </c>
       <c r="K9" t="n">
-        <v>324243</v>
+        <v>319941</v>
       </c>
     </row>
     <row r="10">
@@ -832,15 +832,15 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1924782.67</v>
+        <v>1949381.67</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>47508</v>
+        <v>49508</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1877274.67</v>
+        <v>1899873.67</v>
       </c>
       <c r="I10" t="n">
-        <v>775873</v>
+        <v>799867</v>
       </c>
       <c r="J10" t="n">
-        <v>1101401</v>
+        <v>1100006</v>
       </c>
       <c r="K10" t="n">
-        <v>1845290</v>
+        <v>1869093</v>
       </c>
     </row>
     <row r="11">
@@ -875,7 +875,7 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>256615.45</v>
+        <v>273503.45</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -883,24 +883,24 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>37233.35</v>
+        <v>54233.35000000001</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>219382.1</v>
+        <v>219270.1</v>
       </c>
       <c r="I11" t="n">
-        <v>51366</v>
+        <v>63964</v>
       </c>
       <c r="J11" t="n">
-        <v>167781</v>
+        <v>155071</v>
       </c>
       <c r="K11" t="n">
-        <v>104469</v>
+        <v>108759</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>453582</v>
+        <v>490978</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>105.9%</t>
+          <t>115.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>423487</v>
+        <v>460883</v>
       </c>
       <c r="I12" t="n">
-        <v>66852</v>
+        <v>67250</v>
       </c>
       <c r="J12" t="n">
-        <v>356635</v>
+        <v>393633</v>
       </c>
       <c r="K12" t="n">
-        <v>41927</v>
+        <v>48527</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>617720.15</v>
+        <v>669312.15</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,17 +973,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>549458.48</v>
+        <v>601050.48</v>
       </c>
       <c r="I13" t="n">
-        <v>37951</v>
+        <v>48747</v>
       </c>
       <c r="J13" t="n">
-        <v>479779</v>
+        <v>520575</v>
       </c>
       <c r="K13" t="n">
         <v>106128</v>
@@ -1004,11 +1004,11 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>323238.65</v>
+        <v>325009.45</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1020,16 +1020,16 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>308372.65</v>
+        <v>310143.45</v>
       </c>
       <c r="I14" t="n">
-        <v>53137</v>
+        <v>53535</v>
       </c>
       <c r="J14" t="n">
-        <v>228268</v>
+        <v>228685</v>
       </c>
       <c r="K14" t="n">
-        <v>83032</v>
+        <v>84007</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>148328</v>
+        <v>143367</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>132471</v>
+        <v>127510</v>
       </c>
       <c r="I15" t="n">
-        <v>8555</v>
+        <v>8574</v>
       </c>
       <c r="J15" t="n">
-        <v>123916</v>
+        <v>118936</v>
       </c>
       <c r="K15" t="n">
-        <v>39123</v>
+        <v>39142</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>354151</v>
+        <v>349171</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,14 +1102,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>285234</v>
+        <v>280254</v>
       </c>
       <c r="I16" t="n">
-        <v>17507</v>
+        <v>12527</v>
       </c>
       <c r="J16" t="n">
         <v>267727</v>
@@ -1133,11 +1133,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>619530.29</v>
+        <v>621730.29</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1145,20 +1145,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>513898.89</v>
+        <v>516098.89</v>
       </c>
       <c r="I17" t="n">
         <v>44534</v>
       </c>
       <c r="J17" t="n">
-        <v>399896</v>
+        <v>402096</v>
       </c>
       <c r="K17" t="n">
-        <v>141618</v>
+        <v>143818</v>
       </c>
     </row>
     <row r="18">
@@ -1176,11 +1176,11 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>1082655.59</v>
+        <v>1123652.59</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>104.4%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1188,20 +1188,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>939959.3500000001</v>
+        <v>980956.3499999999</v>
       </c>
       <c r="I18" t="n">
-        <v>229968</v>
+        <v>230267</v>
       </c>
       <c r="J18" t="n">
-        <v>702741</v>
+        <v>743439</v>
       </c>
       <c r="K18" t="n">
-        <v>552807</v>
+        <v>553406</v>
       </c>
     </row>
     <row r="19">
@@ -1219,11 +1219,11 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>541587.87</v>
+        <v>549122.58</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1231,20 +1231,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>454641.87</v>
+        <v>462176.58</v>
       </c>
       <c r="I19" t="n">
         <v>69553</v>
       </c>
       <c r="J19" t="n">
-        <v>323897</v>
+        <v>331397</v>
       </c>
       <c r="K19" t="n">
-        <v>136987</v>
+        <v>137022</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>468751.9</v>
+        <v>498149.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>105502</v>
+        <v>115483</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>363249.9</v>
+        <v>382666.9</v>
       </c>
       <c r="I20" t="n">
-        <v>60364</v>
+        <v>50981</v>
       </c>
       <c r="J20" t="n">
-        <v>302885</v>
+        <v>331685</v>
       </c>
       <c r="K20" t="n">
-        <v>66709</v>
+        <v>83528</v>
       </c>
     </row>
     <row r="21">
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>213094.74</v>
+        <v>311960.09</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1313,24 +1313,24 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>181809.52</v>
+        <v>265235.08</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>31285.22</v>
+        <v>46725.01000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-11171</v>
+        <v>31736</v>
       </c>
       <c r="J21" t="n">
-        <v>42456</v>
+        <v>14988</v>
       </c>
       <c r="K21" t="n">
-        <v>31733</v>
+        <v>31173</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,11 +488,11 @@
         <v>760000</v>
       </c>
       <c r="D2" t="n">
-        <v>665361</v>
+        <v>724921</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -500,20 +500,20 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>533265.84</v>
+        <v>592825.84</v>
       </c>
       <c r="I2" t="n">
-        <v>523921</v>
+        <v>583481</v>
       </c>
       <c r="J2" t="n">
         <v>9344</v>
       </c>
       <c r="K2" t="n">
-        <v>544479</v>
+        <v>604039</v>
       </c>
     </row>
     <row r="3">
@@ -574,32 +574,32 @@
         <v>760000</v>
       </c>
       <c r="D4" t="n">
-        <v>753933.84</v>
+        <v>819273.84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80.9%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>138932.4</v>
+        <v>143912.4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>615001.4399999999</v>
+        <v>675361.4399999999</v>
       </c>
       <c r="I4" t="n">
-        <v>599291</v>
+        <v>659651</v>
       </c>
       <c r="J4" t="n">
         <v>15709</v>
       </c>
       <c r="K4" t="n">
-        <v>581419</v>
+        <v>626959</v>
       </c>
     </row>
     <row r="5">
@@ -660,11 +660,11 @@
         <v>600000</v>
       </c>
       <c r="D6" t="n">
-        <v>740292.45</v>
+        <v>779833.4500000001</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>112.6%</t>
+          <t>119.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -672,20 +672,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>675822.45</v>
+        <v>715363.4500000001</v>
       </c>
       <c r="I6" t="n">
-        <v>668857</v>
+        <v>708398</v>
       </c>
       <c r="J6" t="n">
         <v>6964</v>
       </c>
       <c r="K6" t="n">
-        <v>558438</v>
+        <v>597979</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>360000</v>
       </c>
       <c r="D7" t="n">
-        <v>461633.99</v>
+        <v>486533.99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>100.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>94077</v>
+        <v>123857</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>367556.99</v>
+        <v>362676.99</v>
       </c>
       <c r="I7" t="n">
-        <v>368337</v>
+        <v>363457</v>
       </c>
       <c r="J7" t="n">
         <v>-781</v>
       </c>
       <c r="K7" t="n">
-        <v>216468</v>
+        <v>211588</v>
       </c>
     </row>
     <row r="8">
@@ -746,11 +746,11 @@
         <v>640000</v>
       </c>
       <c r="D8" t="n">
-        <v>417947.62</v>
+        <v>437927.62</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -758,20 +758,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>365339.62</v>
+        <v>385319.62</v>
       </c>
       <c r="I8" t="n">
-        <v>354106</v>
+        <v>374086</v>
       </c>
       <c r="J8" t="n">
         <v>11233</v>
       </c>
       <c r="K8" t="n">
-        <v>311349</v>
+        <v>321329</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1120000</v>
       </c>
       <c r="D9" t="n">
-        <v>1034247.83</v>
+        <v>1235647.83</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>419460</v>
+        <v>444276</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>614787.83</v>
+        <v>791371.8300000001</v>
       </c>
       <c r="I9" t="n">
-        <v>483749</v>
+        <v>660333</v>
       </c>
       <c r="J9" t="n">
         <v>131038</v>
       </c>
       <c r="K9" t="n">
-        <v>319941</v>
+        <v>496525</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>2000000</v>
       </c>
       <c r="D10" t="n">
-        <v>1949381.67</v>
+        <v>1998284.67</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -848,16 +848,16 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1899873.67</v>
+        <v>1948776.67</v>
       </c>
       <c r="I10" t="n">
-        <v>799867</v>
+        <v>809724</v>
       </c>
       <c r="J10" t="n">
-        <v>1100006</v>
+        <v>1139052</v>
       </c>
       <c r="K10" t="n">
-        <v>1869093</v>
+        <v>1917996</v>
       </c>
     </row>
     <row r="11">
@@ -875,7 +875,7 @@
         <v>380000</v>
       </c>
       <c r="D11" t="n">
-        <v>273503.45</v>
+        <v>273522.45</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>219270.1</v>
+        <v>219289.1</v>
       </c>
       <c r="I11" t="n">
-        <v>63964</v>
+        <v>63983</v>
       </c>
       <c r="J11" t="n">
         <v>155071</v>
       </c>
       <c r="K11" t="n">
-        <v>108759</v>
+        <v>108778</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>490978</v>
+        <v>511376</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>115.2%</t>
+          <t>120.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,17 +930,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>460883</v>
+        <v>481281</v>
       </c>
       <c r="I12" t="n">
         <v>67250</v>
       </c>
       <c r="J12" t="n">
-        <v>393633</v>
+        <v>414031</v>
       </c>
       <c r="K12" t="n">
         <v>48527</v>
@@ -961,32 +961,32 @@
         <v>800000</v>
       </c>
       <c r="D13" t="n">
-        <v>669312.15</v>
+        <v>704876.55</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>68261.67</v>
+        <v>79280.67</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>601050.48</v>
+        <v>625595.88</v>
       </c>
       <c r="I13" t="n">
-        <v>48747</v>
+        <v>48728</v>
       </c>
       <c r="J13" t="n">
-        <v>520575</v>
+        <v>544575</v>
       </c>
       <c r="K13" t="n">
-        <v>106128</v>
+        <v>106673</v>
       </c>
     </row>
     <row r="14">
@@ -1004,32 +1004,32 @@
         <v>800000</v>
       </c>
       <c r="D14" t="n">
-        <v>325009.45</v>
+        <v>336057.75</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>14866</v>
+        <v>22866</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>310143.45</v>
+        <v>313191.75</v>
       </c>
       <c r="I14" t="n">
-        <v>53535</v>
+        <v>56133</v>
       </c>
       <c r="J14" t="n">
         <v>228685</v>
       </c>
       <c r="K14" t="n">
-        <v>84007</v>
+        <v>84457</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>260000</v>
       </c>
       <c r="D15" t="n">
-        <v>143367</v>
+        <v>143784.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>127510</v>
+        <v>127927.9</v>
       </c>
       <c r="I15" t="n">
-        <v>8574</v>
+        <v>8991</v>
       </c>
       <c r="J15" t="n">
         <v>118936</v>
       </c>
       <c r="K15" t="n">
-        <v>39142</v>
+        <v>39161</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>400000</v>
       </c>
       <c r="D16" t="n">
-        <v>349171</v>
+        <v>349967</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>280254</v>
+        <v>281050</v>
       </c>
       <c r="I16" t="n">
-        <v>12527</v>
+        <v>13323</v>
       </c>
       <c r="J16" t="n">
         <v>267727</v>
@@ -1133,11 +1133,11 @@
         <v>700000</v>
       </c>
       <c r="D17" t="n">
-        <v>621730.29</v>
+        <v>625926.29</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1145,17 +1145,17 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>516098.89</v>
+        <v>520294.89</v>
       </c>
       <c r="I17" t="n">
-        <v>44534</v>
+        <v>45132</v>
       </c>
       <c r="J17" t="n">
-        <v>402096</v>
+        <v>405694</v>
       </c>
       <c r="K17" t="n">
         <v>143818</v>
@@ -1176,32 +1176,32 @@
         <v>900000</v>
       </c>
       <c r="D18" t="n">
-        <v>1123652.59</v>
+        <v>1147250.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>142696.24</v>
+        <v>162496.24</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>980956.3499999999</v>
+        <v>984754.3600000001</v>
       </c>
       <c r="I18" t="n">
-        <v>230267</v>
+        <v>247265</v>
       </c>
       <c r="J18" t="n">
-        <v>743439</v>
+        <v>730239</v>
       </c>
       <c r="K18" t="n">
-        <v>553406</v>
+        <v>566606</v>
       </c>
     </row>
     <row r="19">
@@ -1219,7 +1219,7 @@
         <v>900000</v>
       </c>
       <c r="D19" t="n">
-        <v>549122.58</v>
+        <v>549922.58</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>86946</v>
+        <v>86965</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1235,16 +1235,16 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>462176.58</v>
+        <v>462957.58</v>
       </c>
       <c r="I19" t="n">
-        <v>69553</v>
+        <v>70334</v>
       </c>
       <c r="J19" t="n">
         <v>331397</v>
       </c>
       <c r="K19" t="n">
-        <v>137022</v>
+        <v>137003</v>
       </c>
     </row>
     <row r="20">
@@ -1262,32 +1262,32 @@
         <v>700000</v>
       </c>
       <c r="D20" t="n">
-        <v>498149.9</v>
+        <v>526498.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>115483</v>
+        <v>133502</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>382666.9</v>
+        <v>392996.9</v>
       </c>
       <c r="I20" t="n">
-        <v>50981</v>
+        <v>52104</v>
       </c>
       <c r="J20" t="n">
-        <v>331685</v>
+        <v>340892</v>
       </c>
       <c r="K20" t="n">
-        <v>83528</v>
+        <v>100664</v>
       </c>
     </row>
     <row r="21">
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>311960.09</v>
+        <v>317608.08</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1313,24 +1313,24 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>265235.08</v>
+        <v>286208.08</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>46725.01000000001</v>
+        <v>31400.00000000006</v>
       </c>
       <c r="I21" t="n">
-        <v>31736</v>
+        <v>19911</v>
       </c>
       <c r="J21" t="n">
-        <v>14988</v>
+        <v>11488</v>
       </c>
       <c r="K21" t="n">
-        <v>31173</v>
+        <v>29948</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>课程1组</t>
+          <t>观行组</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -485,41 +485,41 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>760000</v>
+        <v>1400000</v>
       </c>
       <c r="D2" t="n">
-        <v>724921</v>
+        <v>32222.88</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>132095.16</v>
+        <v>845</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>592825.84</v>
+        <v>31377.88</v>
       </c>
       <c r="I2" t="n">
-        <v>583481</v>
+        <v>30550</v>
       </c>
       <c r="J2" t="n">
-        <v>9344</v>
+        <v>826</v>
       </c>
       <c r="K2" t="n">
-        <v>604039</v>
+        <v>29583</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>课程2组</t>
+          <t>观懋组</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -528,41 +528,41 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>2000</v>
+        <v>7862.99</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>46334</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>589.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>2000</v>
+        <v>-38471.01</v>
       </c>
       <c r="I3" t="n">
-        <v>1865</v>
+        <v>-38789</v>
       </c>
       <c r="J3" t="n">
-        <v>135</v>
+        <v>318</v>
       </c>
       <c r="K3" t="n">
-        <v>2000</v>
+        <v>-38471</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>课程3组</t>
+          <t>初心组</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -571,41 +571,41 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>760000</v>
+        <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>819273.84</v>
+        <v>48586</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>143912.4</v>
+        <v>1714</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>675361.4399999999</v>
+        <v>46872</v>
       </c>
       <c r="I4" t="n">
-        <v>659651</v>
+        <v>46872</v>
       </c>
       <c r="J4" t="n">
-        <v>15709</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>626959</v>
+        <v>26674</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>课程4组</t>
+          <t>观鼎组</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,213 +614,213 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>520000</v>
+        <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>247834</v>
+        <v>156757.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>157581</v>
+        <v>67</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>90253</v>
+        <v>156690.36</v>
       </c>
       <c r="I5" t="n">
-        <v>85065</v>
+        <v>156690</v>
       </c>
       <c r="J5" t="n">
-        <v>5188</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-33907</v>
+        <v>71272</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>课程5组</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>门店</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>600000</v>
+        <v>2000000</v>
       </c>
       <c r="D6" t="n">
-        <v>779833.4500000001</v>
+        <v>195696</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>119.2%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>64470</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>715363.4500000001</v>
+        <v>195696</v>
       </c>
       <c r="I6" t="n">
-        <v>708398</v>
+        <v>75335</v>
       </c>
       <c r="J6" t="n">
-        <v>6964</v>
+        <v>120361</v>
       </c>
       <c r="K6" t="n">
-        <v>597979</v>
+        <v>185298</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>课程6组</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>门店</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>360000</v>
+        <v>380000</v>
       </c>
       <c r="D7" t="n">
-        <v>486533.99</v>
+        <v>24628</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>100.7%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>123857</v>
+        <v>19</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>362676.99</v>
+        <v>24609</v>
       </c>
       <c r="I7" t="n">
-        <v>363457</v>
+        <v>14590</v>
       </c>
       <c r="J7" t="n">
-        <v>-781</v>
+        <v>10019</v>
       </c>
       <c r="K7" t="n">
-        <v>211588</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>课程7组</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>门店</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>640000</v>
+        <v>400000</v>
       </c>
       <c r="D8" t="n">
-        <v>437927.62</v>
+        <v>101194</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>52608</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>385319.62</v>
+        <v>101194</v>
       </c>
       <c r="I8" t="n">
-        <v>374086</v>
+        <v>21194</v>
       </c>
       <c r="J8" t="n">
-        <v>11233</v>
+        <v>80000</v>
       </c>
       <c r="K8" t="n">
-        <v>321329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>门店</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1120000</v>
+        <v>800000</v>
       </c>
       <c r="D9" t="n">
-        <v>1235647.83</v>
+        <v>70893.23</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>444276</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>791371.8300000001</v>
+        <v>70893.23</v>
       </c>
       <c r="I9" t="n">
-        <v>660333</v>
+        <v>8694</v>
       </c>
       <c r="J9" t="n">
-        <v>131038</v>
+        <v>56816</v>
       </c>
       <c r="K9" t="n">
-        <v>496525</v>
+        <v>12699</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -829,41 +829,41 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2000000</v>
+        <v>800000</v>
       </c>
       <c r="D10" t="n">
-        <v>1998284.67</v>
+        <v>34101.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>49508</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1948776.67</v>
+        <v>34101.1</v>
       </c>
       <c r="I10" t="n">
-        <v>809724</v>
+        <v>9</v>
       </c>
       <c r="J10" t="n">
-        <v>1139052</v>
+        <v>32598</v>
       </c>
       <c r="K10" t="n">
-        <v>1917996</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -872,41 +872,41 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>380000</v>
+        <v>260000</v>
       </c>
       <c r="D11" t="n">
-        <v>273522.45</v>
+        <v>6053</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>54233.35000000001</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>219289.1</v>
+        <v>6053</v>
       </c>
       <c r="I11" t="n">
-        <v>63983</v>
+        <v>57</v>
       </c>
       <c r="J11" t="n">
-        <v>155071</v>
+        <v>5996</v>
       </c>
       <c r="K11" t="n">
-        <v>108778</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -918,38 +918,38 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>511376</v>
+        <v>46811</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>120.3%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>30095</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>481281</v>
+        <v>46811</v>
       </c>
       <c r="I12" t="n">
-        <v>67250</v>
+        <v>6015</v>
       </c>
       <c r="J12" t="n">
-        <v>414031</v>
+        <v>40796</v>
       </c>
       <c r="K12" t="n">
-        <v>48527</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -958,41 +958,41 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>800000</v>
+        <v>700000</v>
       </c>
       <c r="D13" t="n">
-        <v>704876.55</v>
+        <v>19334.88</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>79280.67</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>625595.88</v>
+        <v>19334.88</v>
       </c>
       <c r="I13" t="n">
-        <v>48728</v>
+        <v>417</v>
       </c>
       <c r="J13" t="n">
-        <v>544575</v>
+        <v>16692</v>
       </c>
       <c r="K13" t="n">
-        <v>106673</v>
+        <v>8844</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1001,41 +1001,41 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>800000</v>
+        <v>900000</v>
       </c>
       <c r="D14" t="n">
-        <v>336057.75</v>
+        <v>101937</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>22866</v>
+        <v>47</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>313191.75</v>
+        <v>101890</v>
       </c>
       <c r="I14" t="n">
-        <v>56133</v>
+        <v>14293</v>
       </c>
       <c r="J14" t="n">
-        <v>228685</v>
+        <v>87597</v>
       </c>
       <c r="K14" t="n">
-        <v>84457</v>
+        <v>50284</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1044,41 +1044,41 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>260000</v>
+        <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>143784.9</v>
+        <v>65824.82000000001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>15857</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>127927.9</v>
+        <v>65824.82000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>8991</v>
+        <v>27594</v>
       </c>
       <c r="J15" t="n">
-        <v>118936</v>
+        <v>32396</v>
       </c>
       <c r="K15" t="n">
-        <v>39161</v>
+        <v>5834</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1087,41 +1087,41 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>400000</v>
+        <v>700000</v>
       </c>
       <c r="D16" t="n">
-        <v>349967</v>
+        <v>38194</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>68917</v>
+        <v>0</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>281050</v>
+        <v>38194</v>
       </c>
       <c r="I16" t="n">
-        <v>13323</v>
+        <v>10898</v>
       </c>
       <c r="J16" t="n">
-        <v>267727</v>
+        <v>27296</v>
       </c>
       <c r="K16" t="n">
-        <v>47902</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>未映射</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1130,207 +1130,35 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>625926.29</v>
+        <v>0</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>105631.4</v>
+        <v>0</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>520294.89</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>45132</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>405694</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>143818</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>南京</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>门店</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>900000</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1147250.6</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>109.4%</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>162496.24</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>14.2%</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>984754.3600000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>247265</v>
-      </c>
-      <c r="J18" t="n">
-        <v>730239</v>
-      </c>
-      <c r="K18" t="n">
-        <v>566606</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>武汉</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>门店</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>900000</v>
-      </c>
-      <c r="D19" t="n">
-        <v>549922.58</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>51.4%</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>86965</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>15.8%</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>462957.58</v>
-      </c>
-      <c r="I19" t="n">
-        <v>70334</v>
-      </c>
-      <c r="J19" t="n">
-        <v>331397</v>
-      </c>
-      <c r="K19" t="n">
-        <v>137003</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>徐汇</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>门店</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>700000</v>
-      </c>
-      <c r="D20" t="n">
-        <v>526498.9</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>56.1%</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>133502</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>25.4%</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>392996.9</v>
-      </c>
-      <c r="I20" t="n">
-        <v>52104</v>
-      </c>
-      <c r="J20" t="n">
-        <v>340892</v>
-      </c>
-      <c r="K20" t="n">
-        <v>100664</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>未映射</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>门店</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>317608.08</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>286208.08</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>90.1%</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>31400.00000000006</v>
-      </c>
-      <c r="I21" t="n">
-        <v>19911</v>
-      </c>
-      <c r="J21" t="n">
-        <v>11488</v>
-      </c>
-      <c r="K21" t="n">
-        <v>29948</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1400000</v>
       </c>
       <c r="D2" t="n">
-        <v>32222.88</v>
+        <v>70914.87999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>845</v>
+        <v>11584</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>31377.88</v>
+        <v>59330.87999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>30550</v>
+        <v>58503</v>
       </c>
       <c r="J2" t="n">
         <v>826</v>
       </c>
       <c r="K2" t="n">
-        <v>29583</v>
+        <v>57138</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>7862.99</v>
+        <v>52936.99</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>46334</v>
+        <v>98928</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>589.3%</t>
+          <t>186.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-38471.01</v>
+        <v>-45991.01</v>
       </c>
       <c r="I3" t="n">
-        <v>-38789</v>
+        <v>-46309</v>
       </c>
       <c r="J3" t="n">
         <v>318</v>
       </c>
       <c r="K3" t="n">
-        <v>-38471</v>
+        <v>-46987</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>48586</v>
+        <v>139026.99</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1714</v>
+        <v>28253</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>46872</v>
+        <v>110773.99</v>
       </c>
       <c r="I4" t="n">
-        <v>46872</v>
+        <v>110754</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>26674</v>
+        <v>89779</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>156757.36</v>
+        <v>184107.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>13038</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>156690.36</v>
+        <v>171069.36</v>
       </c>
       <c r="I5" t="n">
-        <v>156690</v>
+        <v>152469</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>18600</v>
       </c>
       <c r="K5" t="n">
-        <v>71272</v>
+        <v>86651</v>
       </c>
     </row>
     <row r="6">
@@ -660,11 +660,11 @@
         <v>2000000</v>
       </c>
       <c r="D6" t="n">
-        <v>195696</v>
+        <v>215005</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -676,16 +676,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>195696</v>
+        <v>215005</v>
       </c>
       <c r="I6" t="n">
-        <v>75335</v>
+        <v>85731</v>
       </c>
       <c r="J6" t="n">
-        <v>120361</v>
+        <v>129274</v>
       </c>
       <c r="K6" t="n">
-        <v>185298</v>
+        <v>204607</v>
       </c>
     </row>
     <row r="7">
@@ -703,11 +703,11 @@
         <v>380000</v>
       </c>
       <c r="D7" t="n">
-        <v>24628</v>
+        <v>26225</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>24609</v>
+        <v>26206</v>
       </c>
       <c r="I7" t="n">
-        <v>14590</v>
+        <v>16187</v>
       </c>
       <c r="J7" t="n">
         <v>10019</v>
       </c>
       <c r="K7" t="n">
-        <v>19</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="8">
@@ -746,11 +746,11 @@
         <v>400000</v>
       </c>
       <c r="D8" t="n">
-        <v>101194</v>
+        <v>167988</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -762,16 +762,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>101194</v>
+        <v>167988</v>
       </c>
       <c r="I8" t="n">
-        <v>21194</v>
+        <v>21592</v>
       </c>
       <c r="J8" t="n">
-        <v>80000</v>
+        <v>146396</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>45600</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>800000</v>
       </c>
       <c r="D9" t="n">
-        <v>70893.23</v>
+        <v>100768.73</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -805,16 +805,16 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>70893.23</v>
+        <v>100768.73</v>
       </c>
       <c r="I9" t="n">
-        <v>8694</v>
+        <v>10129</v>
       </c>
       <c r="J9" t="n">
-        <v>56816</v>
+        <v>84616</v>
       </c>
       <c r="K9" t="n">
-        <v>12699</v>
+        <v>14576</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>800000</v>
       </c>
       <c r="D10" t="n">
-        <v>34101.1</v>
+        <v>34130.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>42780</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>125.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>34101.1</v>
+        <v>-8649.900000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>9</v>
+        <v>-35542</v>
       </c>
       <c r="J10" t="n">
-        <v>32598</v>
+        <v>25398</v>
       </c>
       <c r="K10" t="n">
-        <v>1503</v>
+        <v>-34047</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>260000</v>
       </c>
       <c r="D11" t="n">
-        <v>6053</v>
+        <v>14053</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -891,13 +891,13 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>6053</v>
+        <v>14053</v>
       </c>
       <c r="I11" t="n">
         <v>57</v>
       </c>
       <c r="J11" t="n">
-        <v>5996</v>
+        <v>13996</v>
       </c>
       <c r="K11" t="n">
         <v>57</v>
@@ -918,32 +918,32 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>46811</v>
+        <v>54407</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>9200</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>46811</v>
+        <v>45207</v>
       </c>
       <c r="I12" t="n">
-        <v>6015</v>
+        <v>6613</v>
       </c>
       <c r="J12" t="n">
-        <v>40796</v>
+        <v>38594</v>
       </c>
       <c r="K12" t="n">
-        <v>19</v>
+        <v>6619</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>700000</v>
       </c>
       <c r="D13" t="n">
-        <v>19334.88</v>
+        <v>33617.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>19334.88</v>
+        <v>33617.2</v>
       </c>
       <c r="I13" t="n">
-        <v>417</v>
+        <v>2209</v>
       </c>
       <c r="J13" t="n">
-        <v>16692</v>
+        <v>29090</v>
       </c>
       <c r="K13" t="n">
-        <v>8844</v>
+        <v>8937</v>
       </c>
     </row>
     <row r="14">
@@ -1004,32 +1004,32 @@
         <v>900000</v>
       </c>
       <c r="D14" t="n">
-        <v>101937</v>
+        <v>113750</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>58847</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>101890</v>
+        <v>54903</v>
       </c>
       <c r="I14" t="n">
-        <v>14293</v>
+        <v>-30909</v>
       </c>
       <c r="J14" t="n">
-        <v>87597</v>
+        <v>85812</v>
       </c>
       <c r="K14" t="n">
-        <v>50284</v>
+        <v>5303</v>
       </c>
     </row>
     <row r="15">
@@ -1047,29 +1047,29 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>65824.82000000001</v>
+        <v>85824.82000000001</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>65824.82000000001</v>
+        <v>77824.82000000001</v>
       </c>
       <c r="I15" t="n">
         <v>27594</v>
       </c>
       <c r="J15" t="n">
-        <v>32396</v>
+        <v>44396</v>
       </c>
       <c r="K15" t="n">
         <v>5834</v>
@@ -1090,11 +1090,11 @@
         <v>700000</v>
       </c>
       <c r="D16" t="n">
-        <v>38194</v>
+        <v>38990</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>38194</v>
+        <v>38990</v>
       </c>
       <c r="I16" t="n">
-        <v>10898</v>
+        <v>11296</v>
       </c>
       <c r="J16" t="n">
-        <v>27296</v>
+        <v>27694</v>
       </c>
       <c r="K16" t="n">
         <v>102</v>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1400000</v>
       </c>
       <c r="D2" t="n">
-        <v>70914.87999999999</v>
+        <v>164047.88</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>11584</v>
+        <v>43904.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>59330.87999999999</v>
+        <v>120143.18</v>
       </c>
       <c r="I2" t="n">
-        <v>58503</v>
+        <v>123316</v>
       </c>
       <c r="J2" t="n">
-        <v>826</v>
+        <v>-3173</v>
       </c>
       <c r="K2" t="n">
-        <v>57138</v>
+        <v>77951</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>52936.99</v>
+        <v>80447.99000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>98928</v>
+        <v>102329.67</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>186.9%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-45991.01</v>
+        <v>-21881.67999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-46309</v>
+        <v>-22199</v>
       </c>
       <c r="J3" t="n">
         <v>318</v>
       </c>
       <c r="K3" t="n">
-        <v>-46987</v>
+        <v>-23275</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>139026.99</v>
+        <v>187338.89</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>28253</v>
+        <v>35581.67</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>110773.99</v>
+        <v>151757.22</v>
       </c>
       <c r="I4" t="n">
-        <v>110754</v>
+        <v>141738</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>10019</v>
       </c>
       <c r="K4" t="n">
-        <v>89779</v>
+        <v>112365</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>184107.36</v>
+        <v>255954.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>13038</v>
+        <v>18037</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>171069.36</v>
+        <v>237917.36</v>
       </c>
       <c r="I5" t="n">
-        <v>152469</v>
+        <v>212717</v>
       </c>
       <c r="J5" t="n">
-        <v>18600</v>
+        <v>25200</v>
       </c>
       <c r="K5" t="n">
-        <v>86651</v>
+        <v>121699</v>
       </c>
     </row>
     <row r="6">
@@ -660,11 +660,11 @@
         <v>2000000</v>
       </c>
       <c r="D6" t="n">
-        <v>215005</v>
+        <v>290096.92</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -676,16 +676,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>215005</v>
+        <v>290096.92</v>
       </c>
       <c r="I6" t="n">
-        <v>85731</v>
+        <v>130403</v>
       </c>
       <c r="J6" t="n">
-        <v>129274</v>
+        <v>159693</v>
       </c>
       <c r="K6" t="n">
-        <v>204607</v>
+        <v>279698</v>
       </c>
     </row>
     <row r="7">
@@ -703,11 +703,11 @@
         <v>380000</v>
       </c>
       <c r="D7" t="n">
-        <v>26225</v>
+        <v>56438</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -715,20 +715,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>26206</v>
+        <v>56419</v>
       </c>
       <c r="I7" t="n">
-        <v>16187</v>
+        <v>45604</v>
       </c>
       <c r="J7" t="n">
-        <v>10019</v>
+        <v>10815</v>
       </c>
       <c r="K7" t="n">
-        <v>1218</v>
+        <v>18037</v>
       </c>
     </row>
     <row r="8">
@@ -746,11 +746,11 @@
         <v>400000</v>
       </c>
       <c r="D8" t="n">
-        <v>167988</v>
+        <v>178784</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -762,13 +762,13 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>167988</v>
+        <v>178784</v>
       </c>
       <c r="I8" t="n">
-        <v>21592</v>
+        <v>22388</v>
       </c>
       <c r="J8" t="n">
-        <v>146396</v>
+        <v>156396</v>
       </c>
       <c r="K8" t="n">
         <v>45600</v>
@@ -789,32 +789,32 @@
         <v>800000</v>
       </c>
       <c r="D9" t="n">
-        <v>100768.73</v>
+        <v>131087.73</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>25500</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>100768.73</v>
+        <v>105587.73</v>
       </c>
       <c r="I9" t="n">
-        <v>10129</v>
+        <v>15629</v>
       </c>
       <c r="J9" t="n">
-        <v>84616</v>
+        <v>83935</v>
       </c>
       <c r="K9" t="n">
-        <v>14576</v>
+        <v>14795</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>800000</v>
       </c>
       <c r="D10" t="n">
-        <v>34130.1</v>
+        <v>45155.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -844,20 +844,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>125.3%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-8649.900000000001</v>
+        <v>2375.099999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-35542</v>
+        <v>-34915</v>
       </c>
       <c r="J10" t="n">
-        <v>25398</v>
+        <v>35796</v>
       </c>
       <c r="K10" t="n">
-        <v>-34047</v>
+        <v>-34018</v>
       </c>
     </row>
     <row r="11">
@@ -875,32 +875,32 @@
         <v>260000</v>
       </c>
       <c r="D11" t="n">
-        <v>14053</v>
+        <v>15733</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>14053</v>
+        <v>15714</v>
       </c>
       <c r="I11" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="J11" t="n">
-        <v>13996</v>
+        <v>15676</v>
       </c>
       <c r="K11" t="n">
-        <v>57</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="12">
@@ -961,11 +961,11 @@
         <v>700000</v>
       </c>
       <c r="D13" t="n">
-        <v>33617.2</v>
+        <v>64413.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>33617.2</v>
+        <v>64413.2</v>
       </c>
       <c r="I13" t="n">
-        <v>2209</v>
+        <v>2607</v>
       </c>
       <c r="J13" t="n">
-        <v>29090</v>
+        <v>49488</v>
       </c>
       <c r="K13" t="n">
-        <v>8937</v>
+        <v>18937</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>900000</v>
       </c>
       <c r="D14" t="n">
-        <v>113750</v>
+        <v>120748</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>54903</v>
+        <v>61901</v>
       </c>
       <c r="I14" t="n">
-        <v>-30909</v>
+        <v>-30511</v>
       </c>
       <c r="J14" t="n">
-        <v>85812</v>
+        <v>92412</v>
       </c>
       <c r="K14" t="n">
-        <v>5303</v>
+        <v>11903</v>
       </c>
     </row>
     <row r="15">
@@ -1047,32 +1047,32 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>85824.82000000001</v>
+        <v>107777.21</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>8000</v>
+        <v>8009</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>77824.82000000001</v>
+        <v>99768.20999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>27594</v>
+        <v>28792</v>
       </c>
       <c r="J15" t="n">
-        <v>44396</v>
+        <v>54396</v>
       </c>
       <c r="K15" t="n">
-        <v>5834</v>
+        <v>16580</v>
       </c>
     </row>
     <row r="16">
@@ -1090,7 +1090,7 @@
         <v>700000</v>
       </c>
       <c r="D16" t="n">
-        <v>38990</v>
+        <v>39388</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>38990</v>
+        <v>39388</v>
       </c>
       <c r="I16" t="n">
-        <v>11296</v>
+        <v>11694</v>
       </c>
       <c r="J16" t="n">
         <v>27694</v>
@@ -1141,7 +1141,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-6500</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-6500</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1400000</v>
       </c>
       <c r="D2" t="n">
-        <v>164047.88</v>
+        <v>242887.83</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>43904.7</v>
+        <v>49677.7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>120143.18</v>
+        <v>193210.13</v>
       </c>
       <c r="I2" t="n">
-        <v>123316</v>
+        <v>176383</v>
       </c>
       <c r="J2" t="n">
-        <v>-3173</v>
+        <v>16826</v>
       </c>
       <c r="K2" t="n">
-        <v>77951</v>
+        <v>140222</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>80447.99000000001</v>
+        <v>91390.99000000001</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>102329.67</v>
+        <v>121123.67</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>127.2%</t>
+          <t>132.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-21881.67999999999</v>
+        <v>-29732.67999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-22199</v>
+        <v>-30050</v>
       </c>
       <c r="J3" t="n">
         <v>318</v>
       </c>
       <c r="K3" t="n">
-        <v>-23275</v>
+        <v>-12626</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>187338.89</v>
+        <v>242601.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>35581.67</v>
+        <v>36360.67</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>151757.22</v>
+        <v>206241.21</v>
       </c>
       <c r="I4" t="n">
-        <v>141738</v>
+        <v>196222</v>
       </c>
       <c r="J4" t="n">
         <v>10019</v>
       </c>
       <c r="K4" t="n">
-        <v>112365</v>
+        <v>146451</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>255954.36</v>
+        <v>316457.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>18037</v>
+        <v>84030</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>237917.36</v>
+        <v>232427.36</v>
       </c>
       <c r="I5" t="n">
-        <v>212717</v>
+        <v>194027</v>
       </c>
       <c r="J5" t="n">
-        <v>25200</v>
+        <v>38400</v>
       </c>
       <c r="K5" t="n">
-        <v>121699</v>
+        <v>122631</v>
       </c>
     </row>
     <row r="6">
@@ -660,11 +660,11 @@
         <v>2000000</v>
       </c>
       <c r="D6" t="n">
-        <v>290096.92</v>
+        <v>590420.1699999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -676,16 +676,16 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>290096.92</v>
+        <v>590420.1699999999</v>
       </c>
       <c r="I6" t="n">
-        <v>130403</v>
+        <v>30417</v>
       </c>
       <c r="J6" t="n">
-        <v>159693</v>
+        <v>560003</v>
       </c>
       <c r="K6" t="n">
-        <v>279698</v>
+        <v>549624</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>380000</v>
       </c>
       <c r="D7" t="n">
-        <v>56438</v>
+        <v>57135</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>3419</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>56419</v>
+        <v>53716</v>
       </c>
       <c r="I7" t="n">
-        <v>45604</v>
+        <v>45903</v>
       </c>
       <c r="J7" t="n">
-        <v>10815</v>
+        <v>7813</v>
       </c>
       <c r="K7" t="n">
-        <v>18037</v>
+        <v>18336</v>
       </c>
     </row>
     <row r="8">
@@ -746,11 +746,11 @@
         <v>400000</v>
       </c>
       <c r="D8" t="n">
-        <v>178784</v>
+        <v>236801</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -762,16 +762,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>178784</v>
+        <v>236801</v>
       </c>
       <c r="I8" t="n">
-        <v>22388</v>
+        <v>29007</v>
       </c>
       <c r="J8" t="n">
-        <v>156396</v>
+        <v>207794</v>
       </c>
       <c r="K8" t="n">
-        <v>45600</v>
+        <v>52219</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>800000</v>
       </c>
       <c r="D9" t="n">
-        <v>131087.73</v>
+        <v>193702.33</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>25500</v>
+        <v>33000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>17.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>105587.73</v>
+        <v>160702.33</v>
       </c>
       <c r="I9" t="n">
-        <v>15629</v>
+        <v>31425</v>
       </c>
       <c r="J9" t="n">
-        <v>83935</v>
+        <v>122433</v>
       </c>
       <c r="K9" t="n">
-        <v>14795</v>
+        <v>15616</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>800000</v>
       </c>
       <c r="D10" t="n">
-        <v>45155.1</v>
+        <v>51228.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>42780</v>
+        <v>73809</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>144.1%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2375.099999999999</v>
+        <v>-22580.1</v>
       </c>
       <c r="I10" t="n">
-        <v>-34915</v>
+        <v>-35527</v>
       </c>
       <c r="J10" t="n">
-        <v>35796</v>
+        <v>6592</v>
       </c>
       <c r="K10" t="n">
-        <v>-34018</v>
+        <v>-30168</v>
       </c>
     </row>
     <row r="11">
@@ -875,32 +875,32 @@
         <v>260000</v>
       </c>
       <c r="D11" t="n">
-        <v>15733</v>
+        <v>16952</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>7102.33</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>15714</v>
+        <v>9849.67</v>
       </c>
       <c r="I11" t="n">
-        <v>38</v>
+        <v>-7026</v>
       </c>
       <c r="J11" t="n">
-        <v>15676</v>
+        <v>16876</v>
       </c>
       <c r="K11" t="n">
-        <v>1718</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>54407</v>
+        <v>150397</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>45207</v>
+        <v>141197</v>
       </c>
       <c r="I12" t="n">
-        <v>6613</v>
+        <v>7807</v>
       </c>
       <c r="J12" t="n">
-        <v>38594</v>
+        <v>133390</v>
       </c>
       <c r="K12" t="n">
-        <v>6619</v>
+        <v>26619</v>
       </c>
     </row>
     <row r="13">
@@ -961,32 +961,32 @@
         <v>700000</v>
       </c>
       <c r="D13" t="n">
-        <v>64413.2</v>
+        <v>87201.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>10796</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>64413.2</v>
+        <v>76405.2</v>
       </c>
       <c r="I13" t="n">
-        <v>2607</v>
+        <v>14201</v>
       </c>
       <c r="J13" t="n">
-        <v>49488</v>
+        <v>49886</v>
       </c>
       <c r="K13" t="n">
-        <v>18937</v>
+        <v>18141</v>
       </c>
     </row>
     <row r="14">
@@ -1004,32 +1004,32 @@
         <v>900000</v>
       </c>
       <c r="D14" t="n">
-        <v>120748</v>
+        <v>478417.99</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>58847</v>
+        <v>60447</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>61901</v>
+        <v>417970.99</v>
       </c>
       <c r="I14" t="n">
-        <v>-30511</v>
+        <v>57128</v>
       </c>
       <c r="J14" t="n">
-        <v>92412</v>
+        <v>339642</v>
       </c>
       <c r="K14" t="n">
-        <v>11903</v>
+        <v>105194</v>
       </c>
     </row>
     <row r="15">
@@ -1047,32 +1047,32 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>107777.21</v>
+        <v>166831.25</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>8009</v>
+        <v>30609</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>99768.20999999999</v>
+        <v>136222.25</v>
       </c>
       <c r="I15" t="n">
-        <v>28792</v>
+        <v>31586</v>
       </c>
       <c r="J15" t="n">
-        <v>54396</v>
+        <v>66396</v>
       </c>
       <c r="K15" t="n">
-        <v>16580</v>
+        <v>38240</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>700000</v>
       </c>
       <c r="D16" t="n">
-        <v>39388</v>
+        <v>41715</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1106,16 +1106,16 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>39388</v>
+        <v>41715</v>
       </c>
       <c r="I16" t="n">
-        <v>11694</v>
+        <v>12429</v>
       </c>
       <c r="J16" t="n">
-        <v>27694</v>
+        <v>29286</v>
       </c>
       <c r="K16" t="n">
-        <v>102</v>
+        <v>439</v>
       </c>
     </row>
     <row r="17">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -485,14 +485,14 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1400000</v>
+        <v>1450000</v>
       </c>
       <c r="D2" t="n">
         <v>242887.83</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -829,14 +829,14 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>800000</v>
+        <v>1030000</v>
       </c>
       <c r="D10" t="n">
         <v>51228.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -958,14 +958,14 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>700000</v>
+        <v>1600000</v>
       </c>
       <c r="D13" t="n">
         <v>87201.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="F13" t="n">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -657,14 +657,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2000000</v>
+        <v>2500000</v>
       </c>
       <c r="D6" t="n">
         <v>590420.1699999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -700,14 +700,14 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>380000</v>
+        <v>500000</v>
       </c>
       <c r="D7" t="n">
         <v>57135</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -743,14 +743,14 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="D8" t="n">
         <v>236801</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -786,14 +786,14 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>800000</v>
+        <v>1000000</v>
       </c>
       <c r="D9" t="n">
         <v>193702.33</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -829,14 +829,14 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1030000</v>
+        <v>1100000</v>
       </c>
       <c r="D10" t="n">
         <v>51228.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -872,14 +872,14 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>260000</v>
+        <v>400000</v>
       </c>
       <c r="D11" t="n">
         <v>16952</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -915,14 +915,14 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="D12" t="n">
         <v>150397</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -958,14 +958,14 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1600000</v>
+        <v>1900000</v>
       </c>
       <c r="D13" t="n">
         <v>87201.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1001,14 +1001,14 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="D14" t="n">
         <v>478417.99</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1087,14 +1087,14 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>700000</v>
+        <v>900000</v>
       </c>
       <c r="D16" t="n">
         <v>41715</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="F16" t="n">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1121,43 +1121,86 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>望京</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>门店</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>未映射</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>门店</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" t="n">
         <v>6500</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="H18" t="n">
         <v>-6500</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>-6500</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
         <v>0</v>
       </c>
     </row>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1300000</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>242887.83</v>
+        <v>283216.83</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>49677.7</v>
+        <v>50850.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>193210.13</v>
+        <v>232366.38</v>
       </c>
       <c r="I2" t="n">
-        <v>176383</v>
+        <v>215539</v>
       </c>
       <c r="J2" t="n">
         <v>16826</v>
       </c>
       <c r="K2" t="n">
-        <v>140222</v>
+        <v>178382</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>91390.99000000001</v>
+        <v>112656.99</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>121123.67</v>
+        <v>131544.67</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>132.5%</t>
+          <t>116.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-29732.67999999999</v>
+        <v>-18887.67999999998</v>
       </c>
       <c r="I3" t="n">
-        <v>-30050</v>
+        <v>-19505</v>
       </c>
       <c r="J3" t="n">
-        <v>318</v>
+        <v>618</v>
       </c>
       <c r="K3" t="n">
-        <v>-12626</v>
+        <v>-1781</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>242601.88</v>
+        <v>309516.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>36360.67</v>
+        <v>46894.67</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>206241.21</v>
+        <v>262622.21</v>
       </c>
       <c r="I4" t="n">
-        <v>196222</v>
+        <v>252603</v>
       </c>
       <c r="J4" t="n">
         <v>10019</v>
       </c>
       <c r="K4" t="n">
-        <v>146451</v>
+        <v>202832</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>316457.36</v>
+        <v>358903.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>84030</v>
+        <v>152664</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>232427.36</v>
+        <v>206239.36</v>
       </c>
       <c r="I5" t="n">
-        <v>194027</v>
+        <v>169819</v>
       </c>
       <c r="J5" t="n">
-        <v>38400</v>
+        <v>36420</v>
       </c>
       <c r="K5" t="n">
-        <v>122631</v>
+        <v>89263</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>2500000</v>
       </c>
       <c r="D6" t="n">
-        <v>590420.1699999999</v>
+        <v>596299.6299999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>36800</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>590420.1699999999</v>
+        <v>559499.6299999999</v>
       </c>
       <c r="I6" t="n">
-        <v>30417</v>
+        <v>208473</v>
       </c>
       <c r="J6" t="n">
-        <v>560003</v>
+        <v>351026</v>
       </c>
       <c r="K6" t="n">
-        <v>549624</v>
+        <v>518703</v>
       </c>
     </row>
     <row r="7">
@@ -746,32 +746,32 @@
         <v>600000</v>
       </c>
       <c r="D8" t="n">
-        <v>236801</v>
+        <v>257597</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>236801</v>
+        <v>256597</v>
       </c>
       <c r="I8" t="n">
-        <v>29007</v>
+        <v>29405</v>
       </c>
       <c r="J8" t="n">
-        <v>207794</v>
+        <v>227192</v>
       </c>
       <c r="K8" t="n">
-        <v>52219</v>
+        <v>52419</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>1000000</v>
       </c>
       <c r="D9" t="n">
-        <v>193702.33</v>
+        <v>205080.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>17.0%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>160702.33</v>
+        <v>172080.9</v>
       </c>
       <c r="I9" t="n">
-        <v>31425</v>
+        <v>42322</v>
       </c>
       <c r="J9" t="n">
-        <v>122433</v>
+        <v>122831</v>
       </c>
       <c r="K9" t="n">
-        <v>15616</v>
+        <v>16198</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>1100000</v>
       </c>
       <c r="D10" t="n">
-        <v>51228.9</v>
+        <v>62024.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>73809</v>
+        <v>75789</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>144.1%</t>
+          <t>122.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-22580.1</v>
+        <v>-13764.1</v>
       </c>
       <c r="I10" t="n">
         <v>-35527</v>
       </c>
       <c r="J10" t="n">
-        <v>6592</v>
+        <v>15408</v>
       </c>
       <c r="K10" t="n">
-        <v>-30168</v>
+        <v>-32148</v>
       </c>
     </row>
     <row r="11">
@@ -875,32 +875,32 @@
         <v>400000</v>
       </c>
       <c r="D11" t="n">
-        <v>16952</v>
+        <v>18651</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>7102.33</v>
+        <v>7121.33</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>9849.67</v>
+        <v>11529.67</v>
       </c>
       <c r="I11" t="n">
         <v>-7026</v>
       </c>
       <c r="J11" t="n">
-        <v>16876</v>
+        <v>18556</v>
       </c>
       <c r="K11" t="n">
-        <v>1737</v>
+        <v>3417</v>
       </c>
     </row>
     <row r="12">
@@ -918,32 +918,32 @@
         <v>500000</v>
       </c>
       <c r="D12" t="n">
-        <v>150397</v>
+        <v>220245</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9200</v>
+        <v>9219</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>141197</v>
+        <v>211026</v>
       </c>
       <c r="I12" t="n">
-        <v>7807</v>
+        <v>52636</v>
       </c>
       <c r="J12" t="n">
-        <v>133390</v>
+        <v>158390</v>
       </c>
       <c r="K12" t="n">
-        <v>26619</v>
+        <v>91448</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>1900000</v>
       </c>
       <c r="D13" t="n">
-        <v>87201.2</v>
+        <v>105001.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>76405.2</v>
+        <v>94205.2</v>
       </c>
       <c r="I13" t="n">
-        <v>14201</v>
+        <v>13603</v>
       </c>
       <c r="J13" t="n">
-        <v>49886</v>
+        <v>68284</v>
       </c>
       <c r="K13" t="n">
-        <v>18141</v>
+        <v>24741</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>1000000</v>
       </c>
       <c r="D14" t="n">
-        <v>478417.99</v>
+        <v>529416.99</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>417970.99</v>
+        <v>468969.99</v>
       </c>
       <c r="I14" t="n">
-        <v>57128</v>
+        <v>77727</v>
       </c>
       <c r="J14" t="n">
-        <v>339642</v>
+        <v>370042</v>
       </c>
       <c r="K14" t="n">
-        <v>105194</v>
+        <v>166593</v>
       </c>
     </row>
     <row r="15">
@@ -1047,32 +1047,32 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>166831.25</v>
+        <v>174531.25</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>30609</v>
+        <v>33609</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>136222.25</v>
+        <v>140922.25</v>
       </c>
       <c r="I15" t="n">
         <v>31586</v>
       </c>
       <c r="J15" t="n">
-        <v>66396</v>
+        <v>70896</v>
       </c>
       <c r="K15" t="n">
-        <v>38240</v>
+        <v>38440</v>
       </c>
     </row>
     <row r="16">
@@ -1090,32 +1090,32 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>41715</v>
+        <v>48671</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>41715</v>
+        <v>48073</v>
       </c>
       <c r="I16" t="n">
-        <v>12429</v>
+        <v>19366</v>
       </c>
       <c r="J16" t="n">
-        <v>29286</v>
+        <v>28707</v>
       </c>
       <c r="K16" t="n">
-        <v>439</v>
+        <v>7395</v>
       </c>
     </row>
     <row r="17">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,11 +488,11 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>283216.83</v>
+        <v>232366.38</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -531,11 +531,11 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>112656.99</v>
+        <v>-18887.67999999998</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -574,11 +574,11 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>309516.88</v>
+        <v>262622.21</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -617,11 +617,11 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>358903.36</v>
+        <v>206239.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -657,14 +657,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2500000</v>
+        <v>2000000</v>
       </c>
       <c r="D6" t="n">
-        <v>596299.6299999999</v>
+        <v>559499.6299999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -700,14 +700,14 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>500000</v>
+        <v>380000</v>
       </c>
       <c r="D7" t="n">
-        <v>57135</v>
+        <v>53716</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -743,14 +743,14 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>600000</v>
+        <v>400000</v>
       </c>
       <c r="D8" t="n">
-        <v>257597</v>
+        <v>256597</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -786,14 +786,14 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1000000</v>
+        <v>800000</v>
       </c>
       <c r="D9" t="n">
-        <v>205080.9</v>
+        <v>172080.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -829,14 +829,14 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1100000</v>
+        <v>1030000</v>
       </c>
       <c r="D10" t="n">
-        <v>62024.9</v>
+        <v>-13764.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -872,14 +872,14 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>400000</v>
+        <v>260000</v>
       </c>
       <c r="D11" t="n">
-        <v>18651</v>
+        <v>11529.67</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -915,14 +915,14 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>500000</v>
+        <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>220245</v>
+        <v>211026</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -958,14 +958,14 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1900000</v>
+        <v>1600000</v>
       </c>
       <c r="D13" t="n">
-        <v>105001.2</v>
+        <v>94205.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1001,14 +1001,14 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1000000</v>
+        <v>900000</v>
       </c>
       <c r="D14" t="n">
-        <v>529416.99</v>
+        <v>468969.99</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1047,11 +1047,11 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>174531.25</v>
+        <v>140922.25</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1087,14 +1087,14 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>900000</v>
+        <v>700000</v>
       </c>
       <c r="D16" t="n">
-        <v>48671</v>
+        <v>48073</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1300000</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>-6500</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -657,14 +657,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2000000</v>
+        <v>2500000</v>
       </c>
       <c r="D6" t="n">
         <v>559499.6299999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -700,14 +700,14 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>380000</v>
+        <v>500000</v>
       </c>
       <c r="D7" t="n">
         <v>53716</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -743,14 +743,14 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="D8" t="n">
         <v>256597</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -786,14 +786,14 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>800000</v>
+        <v>1000000</v>
       </c>
       <c r="D9" t="n">
         <v>172080.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1030000</v>
+        <v>1100000</v>
       </c>
       <c r="D10" t="n">
         <v>-13764.1</v>
@@ -872,14 +872,14 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>260000</v>
+        <v>400000</v>
       </c>
       <c r="D11" t="n">
         <v>11529.67</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -915,14 +915,14 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="D12" t="n">
         <v>211026</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -958,14 +958,14 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1600000</v>
+        <v>1900000</v>
       </c>
       <c r="D13" t="n">
         <v>94205.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1001,14 +1001,14 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="D14" t="n">
         <v>468969.99</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1087,14 +1087,14 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>700000</v>
+        <v>900000</v>
       </c>
       <c r="D16" t="n">
         <v>48073</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1300000</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,11 +488,11 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>232366.38</v>
+        <v>283216.83</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -531,11 +531,11 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>-18887.67999999998</v>
+        <v>112656.99</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -574,11 +574,11 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>262622.21</v>
+        <v>309516.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -617,11 +617,11 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>206239.36</v>
+        <v>358903.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -660,11 +660,11 @@
         <v>2500000</v>
       </c>
       <c r="D6" t="n">
-        <v>559499.6299999999</v>
+        <v>596299.6299999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -703,11 +703,11 @@
         <v>500000</v>
       </c>
       <c r="D7" t="n">
-        <v>53716</v>
+        <v>57135</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -746,11 +746,11 @@
         <v>600000</v>
       </c>
       <c r="D8" t="n">
-        <v>256597</v>
+        <v>257597</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -789,11 +789,11 @@
         <v>1000000</v>
       </c>
       <c r="D9" t="n">
-        <v>172080.9</v>
+        <v>205080.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -832,11 +832,11 @@
         <v>1100000</v>
       </c>
       <c r="D10" t="n">
-        <v>-13764.1</v>
+        <v>62024.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -875,11 +875,11 @@
         <v>400000</v>
       </c>
       <c r="D11" t="n">
-        <v>11529.67</v>
+        <v>18651</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -918,11 +918,11 @@
         <v>500000</v>
       </c>
       <c r="D12" t="n">
-        <v>211026</v>
+        <v>220245</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -961,11 +961,11 @@
         <v>1900000</v>
       </c>
       <c r="D13" t="n">
-        <v>94205.2</v>
+        <v>105001.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1004,11 +1004,11 @@
         <v>1000000</v>
       </c>
       <c r="D14" t="n">
-        <v>468969.99</v>
+        <v>529416.99</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1047,11 +1047,11 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>140922.25</v>
+        <v>174531.25</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1090,11 +1090,11 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>48073</v>
+        <v>48671</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1130,7 +1130,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1300000</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>-6500</v>
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>一阶</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -524,7 +524,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>一阶</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -567,7 +567,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>一阶</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -610,7 +610,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>二阶</t>
         </is>
       </c>
       <c r="C5" t="n">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>283216.83</v>
+        <v>302065.7999999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>50850.45</v>
+        <v>61855.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>232366.38</v>
+        <v>240210.3499999999</v>
       </c>
       <c r="I2" t="n">
-        <v>215539</v>
+        <v>222528</v>
       </c>
       <c r="J2" t="n">
-        <v>16826</v>
+        <v>17681</v>
       </c>
       <c r="K2" t="n">
-        <v>178382</v>
+        <v>185828</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>112656.99</v>
+        <v>123694.99</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>131544.67</v>
+        <v>139091.67</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>116.8%</t>
+          <t>112.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-18887.67999999998</v>
+        <v>-15396.67999999998</v>
       </c>
       <c r="I3" t="n">
-        <v>-19505</v>
+        <v>-16014</v>
       </c>
       <c r="J3" t="n">
         <v>618</v>
       </c>
       <c r="K3" t="n">
-        <v>-1781</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>309516.88</v>
+        <v>335420.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>46894.67</v>
+        <v>82495.67</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>262622.21</v>
+        <v>252925.21</v>
       </c>
       <c r="I4" t="n">
-        <v>252603</v>
+        <v>242906</v>
       </c>
       <c r="J4" t="n">
         <v>10019</v>
       </c>
       <c r="K4" t="n">
-        <v>202832</v>
+        <v>203135</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>358903.36</v>
+        <v>396147.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>152664</v>
+        <v>184916.88</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>206239.36</v>
+        <v>211230.48</v>
       </c>
       <c r="I5" t="n">
-        <v>169819</v>
+        <v>164810</v>
       </c>
       <c r="J5" t="n">
-        <v>36420</v>
+        <v>46420</v>
       </c>
       <c r="K5" t="n">
-        <v>89263</v>
+        <v>83458</v>
       </c>
     </row>
     <row r="6">
@@ -660,11 +660,11 @@
         <v>2500000</v>
       </c>
       <c r="D6" t="n">
-        <v>596299.6299999999</v>
+        <v>623807.9199999998</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -672,20 +672,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>559499.6299999999</v>
+        <v>587007.9199999998</v>
       </c>
       <c r="I6" t="n">
-        <v>208473</v>
+        <v>228667</v>
       </c>
       <c r="J6" t="n">
-        <v>351026</v>
+        <v>358340</v>
       </c>
       <c r="K6" t="n">
-        <v>518703</v>
+        <v>546211</v>
       </c>
     </row>
     <row r="7">
@@ -703,29 +703,29 @@
         <v>500000</v>
       </c>
       <c r="D7" t="n">
-        <v>57135</v>
+        <v>58154</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3419</v>
+        <v>3438</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>53716</v>
+        <v>54716</v>
       </c>
       <c r="I7" t="n">
         <v>45903</v>
       </c>
       <c r="J7" t="n">
-        <v>7813</v>
+        <v>8813</v>
       </c>
       <c r="K7" t="n">
         <v>18336</v>
@@ -746,11 +746,11 @@
         <v>600000</v>
       </c>
       <c r="D8" t="n">
-        <v>257597</v>
+        <v>268393</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -762,16 +762,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>256597</v>
+        <v>267393</v>
       </c>
       <c r="I8" t="n">
-        <v>29405</v>
+        <v>29803</v>
       </c>
       <c r="J8" t="n">
-        <v>227192</v>
+        <v>237590</v>
       </c>
       <c r="K8" t="n">
-        <v>52419</v>
+        <v>52817</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>1000000</v>
       </c>
       <c r="D9" t="n">
-        <v>205080.9</v>
+        <v>227628.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>172080.9</v>
+        <v>194628.9</v>
       </c>
       <c r="I9" t="n">
-        <v>42322</v>
+        <v>53520</v>
       </c>
       <c r="J9" t="n">
-        <v>122831</v>
+        <v>126031</v>
       </c>
       <c r="K9" t="n">
-        <v>16198</v>
+        <v>25948</v>
       </c>
     </row>
     <row r="10">
@@ -832,7 +832,7 @@
         <v>1100000</v>
       </c>
       <c r="D10" t="n">
-        <v>62024.9</v>
+        <v>62082.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -840,24 +840,24 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>75789</v>
+        <v>87789</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>141.4%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-13764.1</v>
+        <v>-25706.1</v>
       </c>
       <c r="I10" t="n">
-        <v>-35527</v>
+        <v>-47469</v>
       </c>
       <c r="J10" t="n">
         <v>15408</v>
       </c>
       <c r="K10" t="n">
-        <v>-32148</v>
+        <v>-32090</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>400000</v>
       </c>
       <c r="D11" t="n">
-        <v>18651</v>
+        <v>19068</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>11529.67</v>
+        <v>11946.67</v>
       </c>
       <c r="I11" t="n">
-        <v>-7026</v>
+        <v>-7007</v>
       </c>
       <c r="J11" t="n">
-        <v>18556</v>
+        <v>18954</v>
       </c>
       <c r="K11" t="n">
-        <v>3417</v>
+        <v>3436</v>
       </c>
     </row>
     <row r="12">
@@ -918,32 +918,32 @@
         <v>500000</v>
       </c>
       <c r="D12" t="n">
-        <v>220245</v>
+        <v>231060</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>9219</v>
+        <v>10419</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>211026</v>
+        <v>220641</v>
       </c>
       <c r="I12" t="n">
-        <v>52636</v>
+        <v>53451</v>
       </c>
       <c r="J12" t="n">
-        <v>158390</v>
+        <v>167190</v>
       </c>
       <c r="K12" t="n">
-        <v>91448</v>
+        <v>91467</v>
       </c>
     </row>
     <row r="13">
@@ -961,32 +961,32 @@
         <v>1900000</v>
       </c>
       <c r="D13" t="n">
-        <v>105001.2</v>
+        <v>105466.36</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>10796</v>
+        <v>11194</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>94205.2</v>
+        <v>94272.36</v>
       </c>
       <c r="I13" t="n">
-        <v>13603</v>
+        <v>13205</v>
       </c>
       <c r="J13" t="n">
-        <v>68284</v>
+        <v>68682</v>
       </c>
       <c r="K13" t="n">
-        <v>24741</v>
+        <v>24410</v>
       </c>
     </row>
     <row r="14">
@@ -1004,32 +1004,32 @@
         <v>1000000</v>
       </c>
       <c r="D14" t="n">
-        <v>529416.99</v>
+        <v>625443.51</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>60447</v>
+        <v>67947</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>468969.99</v>
+        <v>557496.51</v>
       </c>
       <c r="I14" t="n">
-        <v>77727</v>
+        <v>117973</v>
       </c>
       <c r="J14" t="n">
-        <v>370042</v>
+        <v>418322</v>
       </c>
       <c r="K14" t="n">
-        <v>166593</v>
+        <v>202024</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>174531.25</v>
+        <v>196472.65</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>140922.25</v>
+        <v>162863.65</v>
       </c>
       <c r="I15" t="n">
-        <v>31586</v>
+        <v>51586</v>
       </c>
       <c r="J15" t="n">
-        <v>70896</v>
+        <v>72492</v>
       </c>
       <c r="K15" t="n">
-        <v>38440</v>
+        <v>39183</v>
       </c>
     </row>
     <row r="16">
@@ -1090,32 +1090,32 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>48671</v>
+        <v>81488</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>598</v>
+        <v>2676</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>48073</v>
+        <v>78812</v>
       </c>
       <c r="I16" t="n">
-        <v>19366</v>
+        <v>29385</v>
       </c>
       <c r="J16" t="n">
-        <v>28707</v>
+        <v>49427</v>
       </c>
       <c r="K16" t="n">
-        <v>7395</v>
+        <v>7134</v>
       </c>
     </row>
     <row r="17">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>302065.7999999999</v>
+        <v>340226.01</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>61855.45</v>
+        <v>67842.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>240210.3499999999</v>
+        <v>272383.56</v>
       </c>
       <c r="I2" t="n">
-        <v>222528</v>
+        <v>249038</v>
       </c>
       <c r="J2" t="n">
-        <v>17681</v>
+        <v>23344</v>
       </c>
       <c r="K2" t="n">
-        <v>185828</v>
+        <v>218001</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>123694.99</v>
+        <v>138329.99</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>139091.67</v>
+        <v>162419.37</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>112.4%</t>
+          <t>117.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-15396.67999999998</v>
+        <v>-24089.38</v>
       </c>
       <c r="I3" t="n">
-        <v>-16014</v>
+        <v>-24707</v>
       </c>
       <c r="J3" t="n">
         <v>618</v>
       </c>
       <c r="K3" t="n">
-        <v>1709</v>
+        <v>-6983</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>335420.88</v>
+        <v>390107.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>82495.67</v>
+        <v>84676.97</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>252925.21</v>
+        <v>305430.91</v>
       </c>
       <c r="I4" t="n">
-        <v>242906</v>
+        <v>305411</v>
       </c>
       <c r="J4" t="n">
-        <v>10019</v>
+        <v>19</v>
       </c>
       <c r="K4" t="n">
-        <v>203135</v>
+        <v>216820</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>396147.36</v>
+        <v>484621.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>184916.88</v>
+        <v>204996.88</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>211230.48</v>
+        <v>279624.48</v>
       </c>
       <c r="I5" t="n">
-        <v>164810</v>
+        <v>226604</v>
       </c>
       <c r="J5" t="n">
-        <v>46420</v>
+        <v>53020</v>
       </c>
       <c r="K5" t="n">
-        <v>83458</v>
+        <v>128954</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>2500000</v>
       </c>
       <c r="D6" t="n">
-        <v>623807.9199999998</v>
+        <v>742474.9199999998</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>36800</v>
+        <v>47800</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>587007.9199999998</v>
+        <v>694674.9199999998</v>
       </c>
       <c r="I6" t="n">
-        <v>228667</v>
+        <v>273665</v>
       </c>
       <c r="J6" t="n">
-        <v>358340</v>
+        <v>421009</v>
       </c>
       <c r="K6" t="n">
-        <v>546211</v>
+        <v>664878</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>500000</v>
       </c>
       <c r="D7" t="n">
-        <v>58154</v>
+        <v>79027.84</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3438</v>
+        <v>5438</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>54716</v>
+        <v>73589.84</v>
       </c>
       <c r="I7" t="n">
-        <v>45903</v>
+        <v>56388</v>
       </c>
       <c r="J7" t="n">
-        <v>8813</v>
+        <v>17201</v>
       </c>
       <c r="K7" t="n">
-        <v>18336</v>
+        <v>18811</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>600000</v>
       </c>
       <c r="D8" t="n">
-        <v>268393</v>
+        <v>278412</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1000</v>
+        <v>2680</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>267393</v>
+        <v>275732</v>
       </c>
       <c r="I8" t="n">
-        <v>29803</v>
+        <v>28142</v>
       </c>
       <c r="J8" t="n">
-        <v>237590</v>
+        <v>247590</v>
       </c>
       <c r="K8" t="n">
-        <v>52817</v>
+        <v>51156</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>1000000</v>
       </c>
       <c r="D9" t="n">
-        <v>227628.9</v>
+        <v>231626.72</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>194628.9</v>
+        <v>198626.72</v>
       </c>
       <c r="I9" t="n">
-        <v>53520</v>
+        <v>53937</v>
       </c>
       <c r="J9" t="n">
         <v>126031</v>
       </c>
       <c r="K9" t="n">
-        <v>25948</v>
+        <v>29548</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>1100000</v>
       </c>
       <c r="D10" t="n">
-        <v>62082.9</v>
+        <v>62519.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>87789</v>
+        <v>97789</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>141.4%</t>
+          <t>156.4%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-25706.1</v>
+        <v>-35269.1</v>
       </c>
       <c r="I10" t="n">
-        <v>-47469</v>
+        <v>-57430</v>
       </c>
       <c r="J10" t="n">
-        <v>15408</v>
+        <v>15806</v>
       </c>
       <c r="K10" t="n">
-        <v>-32090</v>
+        <v>-31653</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>400000</v>
       </c>
       <c r="D11" t="n">
-        <v>19068</v>
+        <v>34466</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,17 +887,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>11946.67</v>
+        <v>27344.67</v>
       </c>
       <c r="I11" t="n">
-        <v>-7007</v>
+        <v>-6609</v>
       </c>
       <c r="J11" t="n">
-        <v>18954</v>
+        <v>33954</v>
       </c>
       <c r="K11" t="n">
         <v>3436</v>
@@ -918,7 +918,7 @@
         <v>500000</v>
       </c>
       <c r="D12" t="n">
-        <v>231060</v>
+        <v>231031</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>220641</v>
+        <v>220612</v>
       </c>
       <c r="I12" t="n">
-        <v>53451</v>
+        <v>53422</v>
       </c>
       <c r="J12" t="n">
         <v>167190</v>
       </c>
       <c r="K12" t="n">
-        <v>91467</v>
+        <v>91438</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>1900000</v>
       </c>
       <c r="D13" t="n">
-        <v>105466.36</v>
+        <v>129014.36</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>94272.36</v>
+        <v>117820.36</v>
       </c>
       <c r="I13" t="n">
         <v>13205</v>
       </c>
       <c r="J13" t="n">
-        <v>68682</v>
+        <v>82230</v>
       </c>
       <c r="K13" t="n">
-        <v>24410</v>
+        <v>39360</v>
       </c>
     </row>
     <row r="14">
@@ -1004,32 +1004,32 @@
         <v>1000000</v>
       </c>
       <c r="D14" t="n">
-        <v>625443.51</v>
+        <v>715177.51</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>67947</v>
+        <v>93547</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>557496.51</v>
+        <v>621630.51</v>
       </c>
       <c r="I14" t="n">
-        <v>117973</v>
+        <v>95411</v>
       </c>
       <c r="J14" t="n">
-        <v>418322</v>
+        <v>505018</v>
       </c>
       <c r="K14" t="n">
-        <v>202024</v>
+        <v>259158</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>196472.65</v>
+        <v>214768.65</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>162863.65</v>
+        <v>181159.65</v>
       </c>
       <c r="I15" t="n">
         <v>51586</v>
       </c>
       <c r="J15" t="n">
-        <v>72492</v>
+        <v>90788</v>
       </c>
       <c r="K15" t="n">
-        <v>39183</v>
+        <v>39581</v>
       </c>
     </row>
     <row r="16">
@@ -1090,32 +1090,32 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>81488</v>
+        <v>83487</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2676</v>
+        <v>6276</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>78812</v>
+        <v>77211</v>
       </c>
       <c r="I16" t="n">
-        <v>29385</v>
+        <v>31384</v>
       </c>
       <c r="J16" t="n">
-        <v>49427</v>
+        <v>45827</v>
       </c>
       <c r="K16" t="n">
-        <v>7134</v>
+        <v>8533</v>
       </c>
     </row>
     <row r="17">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>340226.01</v>
+        <v>412127.01</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>67842.45</v>
+        <v>76095.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>272383.56</v>
+        <v>336031.56</v>
       </c>
       <c r="I2" t="n">
-        <v>249038</v>
+        <v>310848</v>
       </c>
       <c r="J2" t="n">
-        <v>23344</v>
+        <v>25182</v>
       </c>
       <c r="K2" t="n">
-        <v>218001</v>
+        <v>289457</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>138329.99</v>
+        <v>151024.99</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>162419.37</v>
+        <v>177472.37</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>117.4%</t>
+          <t>117.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-24089.38</v>
+        <v>-26447.38</v>
       </c>
       <c r="I3" t="n">
-        <v>-24707</v>
+        <v>-22085</v>
       </c>
       <c r="J3" t="n">
-        <v>618</v>
+        <v>-4362</v>
       </c>
       <c r="K3" t="n">
-        <v>-6983</v>
+        <v>-9341</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>390107.88</v>
+        <v>447425.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>84676.97</v>
+        <v>94628.97</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>305430.91</v>
+        <v>352796.91</v>
       </c>
       <c r="I4" t="n">
-        <v>305411</v>
+        <v>352758</v>
       </c>
       <c r="J4" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="K4" t="n">
-        <v>216820</v>
+        <v>264186</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>484621.36</v>
+        <v>623184.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>204996.88</v>
+        <v>235696.88</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>279624.48</v>
+        <v>387487.48</v>
       </c>
       <c r="I5" t="n">
-        <v>226604</v>
+        <v>294867</v>
       </c>
       <c r="J5" t="n">
-        <v>53020</v>
+        <v>92620</v>
       </c>
       <c r="K5" t="n">
-        <v>128954</v>
+        <v>182257</v>
       </c>
     </row>
     <row r="6">
@@ -660,11 +660,11 @@
         <v>2500000</v>
       </c>
       <c r="D6" t="n">
-        <v>742474.9199999998</v>
+        <v>790099.92</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -672,20 +672,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>694674.9199999998</v>
+        <v>742299.92</v>
       </c>
       <c r="I6" t="n">
-        <v>273665</v>
+        <v>316232</v>
       </c>
       <c r="J6" t="n">
-        <v>421009</v>
+        <v>426067</v>
       </c>
       <c r="K6" t="n">
-        <v>664878</v>
+        <v>712503</v>
       </c>
     </row>
     <row r="7">
@@ -703,15 +703,15 @@
         <v>500000</v>
       </c>
       <c r="D7" t="n">
-        <v>79027.84</v>
+        <v>79501.84</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.8%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5438</v>
+        <v>5457</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>73589.84</v>
+        <v>74044.84</v>
       </c>
       <c r="I7" t="n">
-        <v>56388</v>
+        <v>56843</v>
       </c>
       <c r="J7" t="n">
         <v>17201</v>
       </c>
       <c r="K7" t="n">
-        <v>18811</v>
+        <v>18868</v>
       </c>
     </row>
     <row r="8">
@@ -746,11 +746,11 @@
         <v>600000</v>
       </c>
       <c r="D8" t="n">
-        <v>278412</v>
+        <v>308810</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -758,17 +758,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>275732</v>
+        <v>306130</v>
       </c>
       <c r="I8" t="n">
-        <v>28142</v>
+        <v>28540</v>
       </c>
       <c r="J8" t="n">
-        <v>247590</v>
+        <v>277590</v>
       </c>
       <c r="K8" t="n">
         <v>51156</v>
@@ -789,11 +789,11 @@
         <v>1000000</v>
       </c>
       <c r="D9" t="n">
-        <v>231626.72</v>
+        <v>251387.93</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>14.2%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>198626.72</v>
+        <v>218387.93</v>
       </c>
       <c r="I9" t="n">
-        <v>53937</v>
+        <v>54335</v>
       </c>
       <c r="J9" t="n">
-        <v>126031</v>
+        <v>143936</v>
       </c>
       <c r="K9" t="n">
-        <v>29548</v>
+        <v>31411</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>1100000</v>
       </c>
       <c r="D10" t="n">
-        <v>62519.9</v>
+        <v>69335.91</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>97789</v>
+        <v>111788</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>156.4%</t>
+          <t>161.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-35269.1</v>
+        <v>-42452.09</v>
       </c>
       <c r="I10" t="n">
-        <v>-57430</v>
+        <v>-51212</v>
       </c>
       <c r="J10" t="n">
-        <v>15806</v>
+        <v>2405</v>
       </c>
       <c r="K10" t="n">
-        <v>-31653</v>
+        <v>-31634</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>400000</v>
       </c>
       <c r="D11" t="n">
-        <v>34466</v>
+        <v>45281</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>27344.67</v>
+        <v>38159.67</v>
       </c>
       <c r="I11" t="n">
-        <v>-6609</v>
+        <v>-5794</v>
       </c>
       <c r="J11" t="n">
-        <v>33954</v>
+        <v>43954</v>
       </c>
       <c r="K11" t="n">
-        <v>3436</v>
+        <v>3455</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>500000</v>
       </c>
       <c r="D12" t="n">
-        <v>231031</v>
+        <v>241031</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,17 +930,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>220612</v>
+        <v>230612</v>
       </c>
       <c r="I12" t="n">
         <v>53422</v>
       </c>
       <c r="J12" t="n">
-        <v>167190</v>
+        <v>177190</v>
       </c>
       <c r="K12" t="n">
         <v>91438</v>
@@ -961,11 +961,11 @@
         <v>1900000</v>
       </c>
       <c r="D13" t="n">
-        <v>129014.36</v>
+        <v>131164.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>117820.36</v>
+        <v>119970.8</v>
       </c>
       <c r="I13" t="n">
-        <v>13205</v>
+        <v>14424</v>
       </c>
       <c r="J13" t="n">
-        <v>82230</v>
+        <v>82628</v>
       </c>
       <c r="K13" t="n">
-        <v>39360</v>
+        <v>39912</v>
       </c>
     </row>
     <row r="14">
@@ -1004,32 +1004,32 @@
         <v>1000000</v>
       </c>
       <c r="D14" t="n">
-        <v>715177.51</v>
+        <v>742790.51</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>93547</v>
+        <v>98347</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>621630.51</v>
+        <v>644443.51</v>
       </c>
       <c r="I14" t="n">
-        <v>95411</v>
+        <v>76426</v>
       </c>
       <c r="J14" t="n">
-        <v>505018</v>
+        <v>546816</v>
       </c>
       <c r="K14" t="n">
-        <v>259158</v>
+        <v>285975</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>214768.65</v>
+        <v>265685.65</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>181159.65</v>
+        <v>232076.65</v>
       </c>
       <c r="I15" t="n">
-        <v>51586</v>
+        <v>59105</v>
       </c>
       <c r="J15" t="n">
-        <v>90788</v>
+        <v>134186</v>
       </c>
       <c r="K15" t="n">
-        <v>39581</v>
+        <v>40498</v>
       </c>
     </row>
     <row r="16">
@@ -1090,32 +1090,32 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>83487</v>
+        <v>85190</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6276</v>
+        <v>6295</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>77211</v>
+        <v>78895</v>
       </c>
       <c r="I16" t="n">
-        <v>31384</v>
+        <v>32072</v>
       </c>
       <c r="J16" t="n">
-        <v>45827</v>
+        <v>46823</v>
       </c>
       <c r="K16" t="n">
-        <v>8533</v>
+        <v>9221</v>
       </c>
     </row>
     <row r="17">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>412127.01</v>
+        <v>5330</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>76095.45</v>
+        <v>1313</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>336031.56</v>
+        <v>4017</v>
       </c>
       <c r="I2" t="n">
-        <v>310848</v>
+        <v>4017</v>
       </c>
       <c r="J2" t="n">
-        <v>25182</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>289457</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>151024.99</v>
+        <v>1915</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>177472.37</v>
+        <v>248</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>117.5%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-26447.38</v>
+        <v>1667</v>
       </c>
       <c r="I3" t="n">
-        <v>-22085</v>
+        <v>1667</v>
       </c>
       <c r="J3" t="n">
-        <v>-4362</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-9341</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>447425.88</v>
+        <v>4837</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>94628.97</v>
+        <v>524</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>352796.91</v>
+        <v>4313</v>
       </c>
       <c r="I4" t="n">
-        <v>352758</v>
+        <v>4313</v>
       </c>
       <c r="J4" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>264186</v>
+        <v>4313</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>623184.36</v>
+        <v>732</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>235696.88</v>
+        <v>299</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>387487.48</v>
+        <v>433</v>
       </c>
       <c r="I5" t="n">
-        <v>294867</v>
+        <v>433</v>
       </c>
       <c r="J5" t="n">
-        <v>92620</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>182257</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>2500000</v>
       </c>
       <c r="D6" t="n">
-        <v>790099.92</v>
+        <v>752468.0199999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>47800</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>742299.92</v>
+        <v>752468.0199999999</v>
       </c>
       <c r="I6" t="n">
-        <v>316232</v>
+        <v>287059</v>
       </c>
       <c r="J6" t="n">
-        <v>426067</v>
+        <v>465408</v>
       </c>
       <c r="K6" t="n">
-        <v>712503</v>
+        <v>752468</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>500000</v>
       </c>
       <c r="D7" t="n">
-        <v>79501.84</v>
+        <v>38</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5457</v>
+        <v>19</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>74044.84</v>
+        <v>19</v>
       </c>
       <c r="I7" t="n">
-        <v>56843</v>
+        <v>19</v>
       </c>
       <c r="J7" t="n">
-        <v>17201</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>18868</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>600000</v>
       </c>
       <c r="D8" t="n">
-        <v>308810</v>
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2680</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>306130</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>28540</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>277590</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>51156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -789,32 +789,32 @@
         <v>1000000</v>
       </c>
       <c r="D9" t="n">
-        <v>251387.93</v>
+        <v>22337.55</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>2.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>33000</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>218387.93</v>
+        <v>22337.55</v>
       </c>
       <c r="I9" t="n">
-        <v>54335</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>143936</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>31411</v>
+        <v>22337</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>1100000</v>
       </c>
       <c r="D10" t="n">
-        <v>69335.91</v>
+        <v>6383.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>111788</v>
+        <v>0</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>161.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-42452.09</v>
+        <v>6383.9</v>
       </c>
       <c r="I10" t="n">
-        <v>-51212</v>
+        <v>29</v>
       </c>
       <c r="J10" t="n">
-        <v>2405</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-31634</v>
+        <v>6383</v>
       </c>
     </row>
     <row r="11">
@@ -875,32 +875,32 @@
         <v>400000</v>
       </c>
       <c r="D11" t="n">
-        <v>45281</v>
+        <v>19</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>7121.33</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>38159.67</v>
+        <v>19</v>
       </c>
       <c r="I11" t="n">
-        <v>-5794</v>
+        <v>19</v>
       </c>
       <c r="J11" t="n">
-        <v>43954</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>3455</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -918,32 +918,32 @@
         <v>500000</v>
       </c>
       <c r="D12" t="n">
-        <v>241031</v>
+        <v>0</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10419</v>
+        <v>0</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>230612</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>53422</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>177190</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>91438</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -961,32 +961,32 @@
         <v>1900000</v>
       </c>
       <c r="D13" t="n">
-        <v>131164.8</v>
+        <v>22918.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>11194</v>
+        <v>0</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>119970.8</v>
+        <v>22918.8</v>
       </c>
       <c r="I13" t="n">
-        <v>14424</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>82628</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>39912</v>
+        <v>22918</v>
       </c>
     </row>
     <row r="14">
@@ -1004,32 +1004,32 @@
         <v>1000000</v>
       </c>
       <c r="D14" t="n">
-        <v>742790.51</v>
+        <v>22868.59</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>98347</v>
+        <v>1341.59</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>644443.51</v>
+        <v>21527</v>
       </c>
       <c r="I14" t="n">
-        <v>76426</v>
+        <v>327</v>
       </c>
       <c r="J14" t="n">
-        <v>546816</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>285975</v>
+        <v>21527</v>
       </c>
     </row>
     <row r="15">
@@ -1047,32 +1047,32 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>265685.65</v>
+        <v>39430.85</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>33609</v>
+        <v>0</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>232076.65</v>
+        <v>39430.85</v>
       </c>
       <c r="I15" t="n">
-        <v>59105</v>
+        <v>9</v>
       </c>
       <c r="J15" t="n">
-        <v>134186</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>40498</v>
+        <v>39430</v>
       </c>
     </row>
     <row r="16">
@@ -1090,32 +1090,32 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>85190</v>
+        <v>638</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6295</v>
+        <v>38</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>78895</v>
+        <v>600</v>
       </c>
       <c r="I16" t="n">
-        <v>32072</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>46823</v>
+        <v>600</v>
       </c>
       <c r="K16" t="n">
-        <v>9221</v>
+        <v>600</v>
       </c>
     </row>
     <row r="17">
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>-6500</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-6500</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -496,24 +496,24 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1313</v>
+        <v>77275.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>1449.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>4017</v>
+        <v>-71945.45</v>
       </c>
       <c r="I2" t="n">
-        <v>4017</v>
+        <v>-67945</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-4000</v>
       </c>
       <c r="K2" t="n">
-        <v>4017</v>
+        <v>-60137</v>
       </c>
     </row>
     <row r="3">
@@ -539,24 +539,24 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>248</v>
+        <v>177625.37</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>9275.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1667</v>
+        <v>-175710.37</v>
       </c>
       <c r="I3" t="n">
-        <v>1667</v>
+        <v>-170730</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-4980</v>
       </c>
       <c r="K3" t="n">
-        <v>1667</v>
+        <v>-157210</v>
       </c>
     </row>
     <row r="4">
@@ -582,24 +582,24 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>524</v>
+        <v>94904.97</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>1962.1%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4313</v>
+        <v>-90067.97</v>
       </c>
       <c r="I4" t="n">
-        <v>4313</v>
+        <v>-90067</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>4313</v>
+        <v>-68067</v>
       </c>
     </row>
     <row r="5">
@@ -625,24 +625,24 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>299</v>
+        <v>235995.88</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>32239.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>433</v>
+        <v>-235263.88</v>
       </c>
       <c r="I5" t="n">
-        <v>433</v>
+        <v>-233283</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>-1980</v>
       </c>
       <c r="K5" t="n">
-        <v>433</v>
+        <v>-165223</v>
       </c>
     </row>
     <row r="6">
@@ -668,24 +668,24 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>47800</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>752468.0199999999</v>
+        <v>704668.0199999999</v>
       </c>
       <c r="I6" t="n">
         <v>287059</v>
       </c>
       <c r="J6" t="n">
-        <v>465408</v>
+        <v>417608</v>
       </c>
       <c r="K6" t="n">
-        <v>752468</v>
+        <v>715668</v>
       </c>
     </row>
     <row r="7">
@@ -711,24 +711,24 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>5457</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>14360.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>19</v>
+        <v>-5419</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>-19</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-5400</v>
       </c>
       <c r="K7" t="n">
-        <v>19</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="8">
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2680</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -762,16 +762,16 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-2680</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-1680</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-1680</v>
       </c>
     </row>
     <row r="9">
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>33000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>147.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>22337.55</v>
+        <v>-10662.45</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-17000</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-16000</v>
       </c>
       <c r="K9" t="n">
         <v>22337</v>
@@ -840,24 +840,24 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>111788</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1751.1%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>6383.9</v>
+        <v>-105404.1</v>
       </c>
       <c r="I10" t="n">
-        <v>29</v>
+        <v>-58580</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-53179</v>
       </c>
       <c r="K10" t="n">
-        <v>6383</v>
+        <v>-37204</v>
       </c>
     </row>
     <row r="11">
@@ -883,24 +883,24 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>7121.33</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>37480.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19</v>
+        <v>-7102.33</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>-7102</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>19</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="12">
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>10419</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-10419</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-10400</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="13">
@@ -969,24 +969,24 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>11194</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>22918.8</v>
+        <v>11724.8</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-796</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-10398</v>
       </c>
       <c r="K13" t="n">
-        <v>22918</v>
+        <v>21724</v>
       </c>
     </row>
     <row r="14">
@@ -1012,24 +1012,24 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1341.59</v>
+        <v>99688.59</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>435.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>21527</v>
+        <v>-76820</v>
       </c>
       <c r="I14" t="n">
-        <v>327</v>
+        <v>-67920</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-30100</v>
       </c>
       <c r="K14" t="n">
-        <v>21527</v>
+        <v>-46720</v>
       </c>
     </row>
     <row r="15">
@@ -1055,24 +1055,24 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>33609</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>39430.85</v>
+        <v>5821.849999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-33600</v>
       </c>
       <c r="K15" t="n">
-        <v>39430</v>
+        <v>39421</v>
       </c>
     </row>
     <row r="16">
@@ -1098,24 +1098,24 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>38</v>
+        <v>6314</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>989.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>600</v>
+        <v>-5676</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>600</v>
+        <v>-5676</v>
       </c>
       <c r="K16" t="n">
-        <v>600</v>
+        <v>-1680</v>
       </c>
     </row>
     <row r="17">
@@ -1184,7 +1184,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>6500</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-6500</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-6500</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,11 +488,11 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>5330</v>
+        <v>412222.01</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -500,20 +500,20 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1449.8%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-71945.45</v>
+        <v>334946.56</v>
       </c>
       <c r="I2" t="n">
-        <v>-67945</v>
+        <v>309763</v>
       </c>
       <c r="J2" t="n">
-        <v>-4000</v>
+        <v>25182</v>
       </c>
       <c r="K2" t="n">
-        <v>-60137</v>
+        <v>288372</v>
       </c>
     </row>
     <row r="3">
@@ -531,11 +531,11 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>1915</v>
+        <v>151062.99</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -543,20 +543,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9275.5%</t>
+          <t>117.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-175710.37</v>
+        <v>-26562.38</v>
       </c>
       <c r="I3" t="n">
-        <v>-170730</v>
+        <v>-22200</v>
       </c>
       <c r="J3" t="n">
-        <v>-4980</v>
+        <v>-4362</v>
       </c>
       <c r="K3" t="n">
-        <v>-157210</v>
+        <v>-9456</v>
       </c>
     </row>
     <row r="4">
@@ -574,11 +574,11 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>4837</v>
+        <v>447587.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -586,20 +586,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1962.1%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-90067.97</v>
+        <v>352682.91</v>
       </c>
       <c r="I4" t="n">
-        <v>-90067</v>
+        <v>352644</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K4" t="n">
-        <v>-68067</v>
+        <v>264072</v>
       </c>
     </row>
     <row r="5">
@@ -617,11 +617,11 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>732</v>
+        <v>623184.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -629,20 +629,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>32239.9%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-235263.88</v>
+        <v>387188.48</v>
       </c>
       <c r="I5" t="n">
-        <v>-233283</v>
+        <v>294568</v>
       </c>
       <c r="J5" t="n">
-        <v>-1980</v>
+        <v>92620</v>
       </c>
       <c r="K5" t="n">
-        <v>-165223</v>
+        <v>181958</v>
       </c>
     </row>
     <row r="6">
@@ -660,11 +660,11 @@
         <v>2500000</v>
       </c>
       <c r="D6" t="n">
-        <v>752468.0199999999</v>
+        <v>799979.9199999999</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -672,20 +672,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>704668.0199999999</v>
+        <v>752179.9199999999</v>
       </c>
       <c r="I6" t="n">
-        <v>287059</v>
+        <v>317573</v>
       </c>
       <c r="J6" t="n">
-        <v>417608</v>
+        <v>434606</v>
       </c>
       <c r="K6" t="n">
-        <v>715668</v>
+        <v>722383</v>
       </c>
     </row>
     <row r="7">
@@ -703,11 +703,11 @@
         <v>500000</v>
       </c>
       <c r="D7" t="n">
-        <v>38</v>
+        <v>79501.84</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -715,20 +715,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>14360.5%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>-5419</v>
+        <v>74044.84</v>
       </c>
       <c r="I7" t="n">
-        <v>-19</v>
+        <v>56843</v>
       </c>
       <c r="J7" t="n">
-        <v>-5400</v>
+        <v>17201</v>
       </c>
       <c r="K7" t="n">
-        <v>-19</v>
+        <v>18868</v>
       </c>
     </row>
     <row r="8">
@@ -746,11 +746,11 @@
         <v>600000</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>308810</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -758,20 +758,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-2680</v>
+        <v>306130</v>
       </c>
       <c r="I8" t="n">
-        <v>-1680</v>
+        <v>28540</v>
       </c>
       <c r="J8" t="n">
-        <v>-1000</v>
+        <v>277590</v>
       </c>
       <c r="K8" t="n">
-        <v>-1680</v>
+        <v>51156</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>1000000</v>
       </c>
       <c r="D9" t="n">
-        <v>22337.55</v>
+        <v>253609.03</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>147.7%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-10662.45</v>
+        <v>220609.03</v>
       </c>
       <c r="I9" t="n">
-        <v>-17000</v>
+        <v>54335</v>
       </c>
       <c r="J9" t="n">
-        <v>-16000</v>
+        <v>143936</v>
       </c>
       <c r="K9" t="n">
-        <v>22337</v>
+        <v>33633</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>1100000</v>
       </c>
       <c r="D10" t="n">
-        <v>6383.9</v>
+        <v>69335.91</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -844,20 +844,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1751.1%</t>
+          <t>161.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-105404.1</v>
+        <v>-42452.09</v>
       </c>
       <c r="I10" t="n">
-        <v>-58580</v>
+        <v>-51212</v>
       </c>
       <c r="J10" t="n">
-        <v>-53179</v>
+        <v>2405</v>
       </c>
       <c r="K10" t="n">
-        <v>-37204</v>
+        <v>-31634</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>400000</v>
       </c>
       <c r="D11" t="n">
-        <v>19</v>
+        <v>45281</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>37480.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-7102.33</v>
+        <v>38159.67</v>
       </c>
       <c r="I11" t="n">
-        <v>-7102</v>
+        <v>-5794</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>43954</v>
       </c>
       <c r="K11" t="n">
-        <v>-19</v>
+        <v>3455</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>500000</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>241031</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-10419</v>
+        <v>230612</v>
       </c>
       <c r="I12" t="n">
-        <v>-19</v>
+        <v>53422</v>
       </c>
       <c r="J12" t="n">
-        <v>-10400</v>
+        <v>177190</v>
       </c>
       <c r="K12" t="n">
-        <v>-19</v>
+        <v>91438</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>1900000</v>
       </c>
       <c r="D13" t="n">
-        <v>22918.8</v>
+        <v>131164.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>11724.8</v>
+        <v>119970.8</v>
       </c>
       <c r="I13" t="n">
-        <v>-796</v>
+        <v>14424</v>
       </c>
       <c r="J13" t="n">
-        <v>-10398</v>
+        <v>82628</v>
       </c>
       <c r="K13" t="n">
-        <v>21724</v>
+        <v>39912</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>1000000</v>
       </c>
       <c r="D14" t="n">
-        <v>22868.59</v>
+        <v>744132.1000000001</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>435.9%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-76820</v>
+        <v>644443.5100000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-67920</v>
+        <v>76426</v>
       </c>
       <c r="J14" t="n">
-        <v>-30100</v>
+        <v>546816</v>
       </c>
       <c r="K14" t="n">
-        <v>-46720</v>
+        <v>285975</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>39430.85</v>
+        <v>266321.85</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5821.849999999999</v>
+        <v>232712.85</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>59105</v>
       </c>
       <c r="J15" t="n">
-        <v>-33600</v>
+        <v>134186</v>
       </c>
       <c r="K15" t="n">
-        <v>39421</v>
+        <v>41134</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>638</v>
+        <v>85190</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>989.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-5676</v>
+        <v>78876</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>32053</v>
       </c>
       <c r="J16" t="n">
-        <v>-5676</v>
+        <v>46823</v>
       </c>
       <c r="K16" t="n">
-        <v>-1680</v>
+        <v>9202</v>
       </c>
     </row>
     <row r="17">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>412222.01</v>
+        <v>518692.01</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>77275.45</v>
+        <v>77934.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>334946.56</v>
+        <v>440757.56</v>
       </c>
       <c r="I2" t="n">
-        <v>309763</v>
+        <v>415555</v>
       </c>
       <c r="J2" t="n">
-        <v>25182</v>
+        <v>25201</v>
       </c>
       <c r="K2" t="n">
-        <v>288372</v>
+        <v>392989</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>151062.99</v>
+        <v>191734.13</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>177625.37</v>
+        <v>179454.37</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>117.6%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-26562.38</v>
+        <v>12279.76000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-22200</v>
+        <v>-3369</v>
       </c>
       <c r="J3" t="n">
-        <v>-4362</v>
+        <v>15649</v>
       </c>
       <c r="K3" t="n">
-        <v>-9456</v>
+        <v>28787</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>447587.88</v>
+        <v>558937.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>94904.97</v>
+        <v>99419.97</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>352682.91</v>
+        <v>459517.91</v>
       </c>
       <c r="I4" t="n">
-        <v>352644</v>
+        <v>459460</v>
       </c>
       <c r="J4" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="K4" t="n">
-        <v>264072</v>
+        <v>306709</v>
       </c>
     </row>
     <row r="5">
@@ -617,11 +617,11 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>623184.36</v>
+        <v>1075132.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -629,20 +629,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>387188.48</v>
+        <v>839136.4799999999</v>
       </c>
       <c r="I5" t="n">
-        <v>294568</v>
+        <v>661205</v>
       </c>
       <c r="J5" t="n">
-        <v>92620</v>
+        <v>177931</v>
       </c>
       <c r="K5" t="n">
-        <v>181958</v>
+        <v>582106</v>
       </c>
     </row>
     <row r="6">
@@ -660,11 +660,11 @@
         <v>2500000</v>
       </c>
       <c r="D6" t="n">
-        <v>799979.9199999999</v>
+        <v>976484.92</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -672,20 +672,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>752179.9199999999</v>
+        <v>928684.92</v>
       </c>
       <c r="I6" t="n">
-        <v>317573</v>
+        <v>377437</v>
       </c>
       <c r="J6" t="n">
-        <v>434606</v>
+        <v>551247</v>
       </c>
       <c r="K6" t="n">
-        <v>722383</v>
+        <v>888490</v>
       </c>
     </row>
     <row r="7">
@@ -703,11 +703,11 @@
         <v>500000</v>
       </c>
       <c r="D7" t="n">
-        <v>79501.84</v>
+        <v>81817.84</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -715,20 +715,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>74044.84</v>
+        <v>76360.84</v>
       </c>
       <c r="I7" t="n">
-        <v>56843</v>
+        <v>57279</v>
       </c>
       <c r="J7" t="n">
-        <v>17201</v>
+        <v>18881</v>
       </c>
       <c r="K7" t="n">
-        <v>18868</v>
+        <v>20786</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>600000</v>
       </c>
       <c r="D8" t="n">
-        <v>308810</v>
+        <v>368998</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2680</v>
+        <v>9280</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>306130</v>
+        <v>359718</v>
       </c>
       <c r="I8" t="n">
-        <v>28540</v>
+        <v>24328</v>
       </c>
       <c r="J8" t="n">
-        <v>277590</v>
+        <v>335390</v>
       </c>
       <c r="K8" t="n">
-        <v>51156</v>
+        <v>69356</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>1000000</v>
       </c>
       <c r="D9" t="n">
-        <v>253609.03</v>
+        <v>346401.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>220609.03</v>
+        <v>313401.9</v>
       </c>
       <c r="I9" t="n">
-        <v>54335</v>
+        <v>55558</v>
       </c>
       <c r="J9" t="n">
-        <v>143936</v>
+        <v>234431</v>
       </c>
       <c r="K9" t="n">
-        <v>33633</v>
+        <v>35035</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>1100000</v>
       </c>
       <c r="D10" t="n">
-        <v>69335.91</v>
+        <v>98784.10999999999</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>111788</v>
+        <v>129788</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>161.2%</t>
+          <t>131.4%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-42452.09</v>
+        <v>-31003.89000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-51212</v>
+        <v>-68614</v>
       </c>
       <c r="J10" t="n">
-        <v>2405</v>
+        <v>25401</v>
       </c>
       <c r="K10" t="n">
-        <v>-31634</v>
+        <v>-25381</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>400000</v>
       </c>
       <c r="D11" t="n">
-        <v>45281</v>
+        <v>62033.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>38159.67</v>
+        <v>54912.47</v>
       </c>
       <c r="I11" t="n">
-        <v>-5794</v>
+        <v>-4960</v>
       </c>
       <c r="J11" t="n">
-        <v>43954</v>
+        <v>59872</v>
       </c>
       <c r="K11" t="n">
-        <v>3455</v>
+        <v>10217</v>
       </c>
     </row>
     <row r="12">
@@ -918,29 +918,29 @@
         <v>500000</v>
       </c>
       <c r="D12" t="n">
-        <v>241031</v>
+        <v>260642</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>10419</v>
+        <v>15838</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>230612</v>
+        <v>244804</v>
       </c>
       <c r="I12" t="n">
-        <v>53422</v>
+        <v>55014</v>
       </c>
       <c r="J12" t="n">
-        <v>177190</v>
+        <v>189790</v>
       </c>
       <c r="K12" t="n">
         <v>91438</v>
@@ -961,11 +961,11 @@
         <v>1900000</v>
       </c>
       <c r="D13" t="n">
-        <v>131164.8</v>
+        <v>151554.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>119970.8</v>
+        <v>140360.8</v>
       </c>
       <c r="I13" t="n">
-        <v>14424</v>
+        <v>15220</v>
       </c>
       <c r="J13" t="n">
-        <v>82628</v>
+        <v>94222</v>
       </c>
       <c r="K13" t="n">
-        <v>39912</v>
+        <v>47912</v>
       </c>
     </row>
     <row r="14">
@@ -1004,32 +1004,32 @@
         <v>1000000</v>
       </c>
       <c r="D14" t="n">
-        <v>744132.1000000001</v>
+        <v>869279.14</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>99688.59</v>
+        <v>103647.59</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>644443.5100000001</v>
+        <v>765631.55</v>
       </c>
       <c r="I14" t="n">
-        <v>76426</v>
+        <v>109381</v>
       </c>
       <c r="J14" t="n">
-        <v>546816</v>
+        <v>634749</v>
       </c>
       <c r="K14" t="n">
-        <v>285975</v>
+        <v>354371</v>
       </c>
     </row>
     <row r="15">
@@ -1047,32 +1047,32 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>266321.85</v>
+        <v>325728.48</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>33609</v>
+        <v>33628</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>232712.85</v>
+        <v>292100.48</v>
       </c>
       <c r="I15" t="n">
-        <v>59105</v>
+        <v>60743</v>
       </c>
       <c r="J15" t="n">
-        <v>134186</v>
+        <v>181078</v>
       </c>
       <c r="K15" t="n">
-        <v>41134</v>
+        <v>59824</v>
       </c>
     </row>
     <row r="16">
@@ -1090,32 +1090,32 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>85190</v>
+        <v>134047</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6314</v>
+        <v>12362</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>78876</v>
+        <v>121685</v>
       </c>
       <c r="I16" t="n">
-        <v>32053</v>
+        <v>26849</v>
       </c>
       <c r="J16" t="n">
-        <v>46823</v>
+        <v>94836</v>
       </c>
       <c r="K16" t="n">
-        <v>9202</v>
+        <v>26021</v>
       </c>
     </row>
     <row r="17">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>518692.01</v>
+        <v>224627</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>77934.45</v>
+        <v>80794.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>440757.56</v>
+        <v>143832.55</v>
       </c>
       <c r="I2" t="n">
-        <v>415555</v>
+        <v>145975</v>
       </c>
       <c r="J2" t="n">
-        <v>25201</v>
+        <v>-2143</v>
       </c>
       <c r="K2" t="n">
-        <v>392989</v>
+        <v>154446</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>191734.13</v>
+        <v>102457.42</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>179454.37</v>
+        <v>182952.07</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>178.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>12279.76000000001</v>
+        <v>-80494.65000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>-3369</v>
+        <v>-97792</v>
       </c>
       <c r="J3" t="n">
-        <v>15649</v>
+        <v>17297</v>
       </c>
       <c r="K3" t="n">
-        <v>28787</v>
+        <v>-62592</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>558937.88</v>
+        <v>272865</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>99419.97</v>
+        <v>110888.97</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>459517.91</v>
+        <v>161976.03</v>
       </c>
       <c r="I4" t="n">
-        <v>459460</v>
+        <v>161938</v>
       </c>
       <c r="J4" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="K4" t="n">
-        <v>306709</v>
+        <v>118982</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>1075132.36</v>
+        <v>799874</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>235995.88</v>
+        <v>262558.54</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>839136.4799999999</v>
+        <v>537315.46</v>
       </c>
       <c r="I5" t="n">
-        <v>661205</v>
+        <v>393979</v>
       </c>
       <c r="J5" t="n">
-        <v>177931</v>
+        <v>143336</v>
       </c>
       <c r="K5" t="n">
-        <v>582106</v>
+        <v>503795</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>2500000</v>
       </c>
       <c r="D6" t="n">
-        <v>976484.92</v>
+        <v>966033.92</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>47800</v>
+        <v>58819</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>928684.92</v>
+        <v>907214.92</v>
       </c>
       <c r="I6" t="n">
-        <v>377437</v>
+        <v>337218</v>
       </c>
       <c r="J6" t="n">
-        <v>551247</v>
+        <v>569996</v>
       </c>
       <c r="K6" t="n">
-        <v>888490</v>
+        <v>908816</v>
       </c>
     </row>
     <row r="7">
@@ -703,11 +703,11 @@
         <v>500000</v>
       </c>
       <c r="D7" t="n">
-        <v>81817.84</v>
+        <v>14276</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -715,20 +715,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>76360.84</v>
+        <v>8819</v>
       </c>
       <c r="I7" t="n">
-        <v>57279</v>
+        <v>11939</v>
       </c>
       <c r="J7" t="n">
-        <v>18881</v>
+        <v>-3320</v>
       </c>
       <c r="K7" t="n">
-        <v>20786</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="8">
@@ -746,11 +746,11 @@
         <v>600000</v>
       </c>
       <c r="D8" t="n">
-        <v>368998</v>
+        <v>104184</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -758,20 +758,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>359718</v>
+        <v>94904</v>
       </c>
       <c r="I8" t="n">
-        <v>24328</v>
+        <v>-5096</v>
       </c>
       <c r="J8" t="n">
-        <v>335390</v>
+        <v>100000</v>
       </c>
       <c r="K8" t="n">
-        <v>69356</v>
+        <v>29720</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>1000000</v>
       </c>
       <c r="D9" t="n">
-        <v>346401.9</v>
+        <v>156627.42</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>313401.9</v>
+        <v>123627.42</v>
       </c>
       <c r="I9" t="n">
-        <v>55558</v>
+        <v>-15379</v>
       </c>
       <c r="J9" t="n">
-        <v>234431</v>
+        <v>115594</v>
       </c>
       <c r="K9" t="n">
-        <v>35035</v>
+        <v>24145</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>1100000</v>
       </c>
       <c r="D10" t="n">
-        <v>98784.10999999999</v>
+        <v>181559.11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>129788</v>
+        <v>206844</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>131.4%</t>
+          <t>113.9%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-31003.89000000001</v>
+        <v>-25284.88999999998</v>
       </c>
       <c r="I10" t="n">
-        <v>-68614</v>
+        <v>-69237</v>
       </c>
       <c r="J10" t="n">
-        <v>25401</v>
+        <v>31405</v>
       </c>
       <c r="K10" t="n">
-        <v>-25381</v>
+        <v>-5294</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>400000</v>
       </c>
       <c r="D11" t="n">
-        <v>62033.8</v>
+        <v>29295.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>54912.47</v>
+        <v>22174.47</v>
       </c>
       <c r="I11" t="n">
-        <v>-4960</v>
+        <v>-5424</v>
       </c>
       <c r="J11" t="n">
-        <v>59872</v>
+        <v>27598</v>
       </c>
       <c r="K11" t="n">
-        <v>10217</v>
+        <v>8471</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>500000</v>
       </c>
       <c r="D12" t="n">
-        <v>260642</v>
+        <v>30407</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>244804</v>
+        <v>14569</v>
       </c>
       <c r="I12" t="n">
-        <v>55014</v>
+        <v>2369</v>
       </c>
       <c r="J12" t="n">
-        <v>189790</v>
+        <v>12200</v>
       </c>
       <c r="K12" t="n">
-        <v>91438</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="13">
@@ -961,32 +961,32 @@
         <v>1900000</v>
       </c>
       <c r="D13" t="n">
-        <v>151554.8</v>
+        <v>104245.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>11194</v>
+        <v>244098</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>234.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>140360.8</v>
+        <v>-139852.2</v>
       </c>
       <c r="I13" t="n">
-        <v>15220</v>
+        <v>-174991</v>
       </c>
       <c r="J13" t="n">
-        <v>94222</v>
+        <v>4220</v>
       </c>
       <c r="K13" t="n">
-        <v>47912</v>
+        <v>-119526</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>1000000</v>
       </c>
       <c r="D14" t="n">
-        <v>869279.14</v>
+        <v>226086.63</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>765631.55</v>
+        <v>122439.04</v>
       </c>
       <c r="I14" t="n">
-        <v>109381</v>
+        <v>-14588</v>
       </c>
       <c r="J14" t="n">
-        <v>634749</v>
+        <v>115527</v>
       </c>
       <c r="K14" t="n">
-        <v>354371</v>
+        <v>76165</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>325728.48</v>
+        <v>196528.87</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>21.8%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>17.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>292100.48</v>
+        <v>162900.87</v>
       </c>
       <c r="I15" t="n">
-        <v>60743</v>
+        <v>37966</v>
       </c>
       <c r="J15" t="n">
-        <v>181078</v>
+        <v>74588</v>
       </c>
       <c r="K15" t="n">
-        <v>59824</v>
+        <v>59086</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>134047</v>
+        <v>64187</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>121685</v>
+        <v>51825</v>
       </c>
       <c r="I16" t="n">
-        <v>26849</v>
+        <v>-4525</v>
       </c>
       <c r="J16" t="n">
-        <v>94836</v>
+        <v>56350</v>
       </c>
       <c r="K16" t="n">
-        <v>26021</v>
+        <v>28437</v>
       </c>
     </row>
     <row r="17">
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>29086</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1184,24 +1184,24 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>6500</v>
+        <v>24218</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>-6500</v>
+        <v>4868</v>
       </c>
       <c r="I18" t="n">
-        <v>-6500</v>
+        <v>5068</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>12368</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>224627</v>
+        <v>559077.01</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>80794.45</v>
+        <v>80823.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>143832.55</v>
+        <v>478253.56</v>
       </c>
       <c r="I2" t="n">
-        <v>145975</v>
+        <v>453051</v>
       </c>
       <c r="J2" t="n">
-        <v>-2143</v>
+        <v>25201</v>
       </c>
       <c r="K2" t="n">
-        <v>154446</v>
+        <v>430883</v>
       </c>
     </row>
     <row r="3">
@@ -531,11 +531,11 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>102457.42</v>
+        <v>240170.41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -543,20 +543,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>178.6%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-80494.65000000001</v>
+        <v>57218.33999999997</v>
       </c>
       <c r="I3" t="n">
-        <v>-97792</v>
+        <v>39302</v>
       </c>
       <c r="J3" t="n">
-        <v>17297</v>
+        <v>17915</v>
       </c>
       <c r="K3" t="n">
-        <v>-62592</v>
+        <v>74324</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>272865</v>
+        <v>657617.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>110888.97</v>
+        <v>110926.97</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>161976.03</v>
+        <v>546690.91</v>
       </c>
       <c r="I4" t="n">
-        <v>161938</v>
+        <v>546633</v>
       </c>
       <c r="J4" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="K4" t="n">
-        <v>118982</v>
+        <v>393086</v>
       </c>
     </row>
     <row r="5">
@@ -617,11 +617,11 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>799874</v>
+        <v>1291095.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -629,20 +629,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>537315.46</v>
+        <v>1028536.82</v>
       </c>
       <c r="I5" t="n">
-        <v>393979</v>
+        <v>830200</v>
       </c>
       <c r="J5" t="n">
-        <v>143336</v>
+        <v>198336</v>
       </c>
       <c r="K5" t="n">
-        <v>503795</v>
+        <v>780206</v>
       </c>
     </row>
     <row r="6">
@@ -660,11 +660,11 @@
         <v>2500000</v>
       </c>
       <c r="D6" t="n">
-        <v>966033.92</v>
+        <v>1013467.92</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -672,20 +672,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>907214.92</v>
+        <v>954648.92</v>
       </c>
       <c r="I6" t="n">
-        <v>337218</v>
+        <v>367654</v>
       </c>
       <c r="J6" t="n">
-        <v>569996</v>
+        <v>586994</v>
       </c>
       <c r="K6" t="n">
-        <v>908816</v>
+        <v>915454</v>
       </c>
     </row>
     <row r="7">
@@ -703,11 +703,11 @@
         <v>500000</v>
       </c>
       <c r="D7" t="n">
-        <v>14276</v>
+        <v>93303.84</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -715,20 +715,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8819</v>
+        <v>87846.84</v>
       </c>
       <c r="I7" t="n">
-        <v>11939</v>
+        <v>68365</v>
       </c>
       <c r="J7" t="n">
-        <v>-3320</v>
+        <v>19281</v>
       </c>
       <c r="K7" t="n">
-        <v>2427</v>
+        <v>21276</v>
       </c>
     </row>
     <row r="8">
@@ -746,11 +746,11 @@
         <v>600000</v>
       </c>
       <c r="D8" t="n">
-        <v>104184</v>
+        <v>382596</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -758,20 +758,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>94904</v>
+        <v>373316</v>
       </c>
       <c r="I8" t="n">
-        <v>-5096</v>
+        <v>24726</v>
       </c>
       <c r="J8" t="n">
-        <v>100000</v>
+        <v>348590</v>
       </c>
       <c r="K8" t="n">
-        <v>29720</v>
+        <v>82556</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>1000000</v>
       </c>
       <c r="D9" t="n">
-        <v>156627.42</v>
+        <v>369595.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>123627.42</v>
+        <v>336595.9</v>
       </c>
       <c r="I9" t="n">
-        <v>-15379</v>
+        <v>55558</v>
       </c>
       <c r="J9" t="n">
-        <v>115594</v>
+        <v>257625</v>
       </c>
       <c r="K9" t="n">
-        <v>24145</v>
+        <v>35035</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>1100000</v>
       </c>
       <c r="D10" t="n">
-        <v>181559.11</v>
+        <v>242704.11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -844,20 +844,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>113.9%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-25284.88999999998</v>
+        <v>35860.11000000002</v>
       </c>
       <c r="I10" t="n">
-        <v>-69237</v>
+        <v>-63078</v>
       </c>
       <c r="J10" t="n">
-        <v>31405</v>
+        <v>86391</v>
       </c>
       <c r="K10" t="n">
-        <v>-5294</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>400000</v>
       </c>
       <c r="D11" t="n">
-        <v>29295.8</v>
+        <v>63761.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>22174.47</v>
+        <v>56640.47</v>
       </c>
       <c r="I11" t="n">
-        <v>-5424</v>
+        <v>-4912</v>
       </c>
       <c r="J11" t="n">
-        <v>27598</v>
+        <v>61552</v>
       </c>
       <c r="K11" t="n">
-        <v>8471</v>
+        <v>11945</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>500000</v>
       </c>
       <c r="D12" t="n">
-        <v>30407</v>
+        <v>261438</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>14569</v>
+        <v>245600</v>
       </c>
       <c r="I12" t="n">
-        <v>2369</v>
+        <v>55810</v>
       </c>
       <c r="J12" t="n">
-        <v>12200</v>
+        <v>189790</v>
       </c>
       <c r="K12" t="n">
-        <v>-19</v>
+        <v>91438</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>1900000</v>
       </c>
       <c r="D13" t="n">
-        <v>104245.8</v>
+        <v>210874.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>234.2%</t>
+          <t>115.8%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-139852.2</v>
+        <v>-33223.20000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-174991</v>
+        <v>-160990</v>
       </c>
       <c r="J13" t="n">
-        <v>4220</v>
+        <v>96848</v>
       </c>
       <c r="K13" t="n">
-        <v>-119526</v>
+        <v>-101357</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>1000000</v>
       </c>
       <c r="D14" t="n">
-        <v>226086.63</v>
+        <v>920064.14</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>122439.04</v>
+        <v>816416.55</v>
       </c>
       <c r="I14" t="n">
-        <v>-14588</v>
+        <v>129270</v>
       </c>
       <c r="J14" t="n">
-        <v>115527</v>
+        <v>665645</v>
       </c>
       <c r="K14" t="n">
-        <v>76165</v>
+        <v>382370</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>196528.87</v>
+        <v>372511.87</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>162900.87</v>
+        <v>338883.87</v>
       </c>
       <c r="I15" t="n">
-        <v>37966</v>
+        <v>89561</v>
       </c>
       <c r="J15" t="n">
-        <v>74588</v>
+        <v>198976</v>
       </c>
       <c r="K15" t="n">
-        <v>59086</v>
+        <v>59891</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>64187</v>
+        <v>147693</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>51825</v>
+        <v>135331</v>
       </c>
       <c r="I16" t="n">
-        <v>-4525</v>
+        <v>26878</v>
       </c>
       <c r="J16" t="n">
-        <v>56350</v>
+        <v>108453</v>
       </c>
       <c r="K16" t="n">
-        <v>28437</v>
+        <v>39269</v>
       </c>
     </row>
     <row r="17">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>559077.01</v>
+        <v>564019.01</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>80823.45</v>
+        <v>97723.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>478253.56</v>
+        <v>466295.56</v>
       </c>
       <c r="I2" t="n">
-        <v>453051</v>
+        <v>441093</v>
       </c>
       <c r="J2" t="n">
         <v>25201</v>
       </c>
       <c r="K2" t="n">
-        <v>430883</v>
+        <v>418925</v>
       </c>
     </row>
     <row r="3">
@@ -539,24 +539,24 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>182952.07</v>
+        <v>188021.07</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>57218.33999999997</v>
+        <v>52149.34</v>
       </c>
       <c r="I3" t="n">
-        <v>39302</v>
+        <v>34233</v>
       </c>
       <c r="J3" t="n">
         <v>17915</v>
       </c>
       <c r="K3" t="n">
-        <v>74324</v>
+        <v>69255</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>657617.88</v>
+        <v>667558.88</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>110926.97</v>
+        <v>149341.97</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>546690.91</v>
+        <v>518216.91</v>
       </c>
       <c r="I4" t="n">
-        <v>546633</v>
+        <v>518159</v>
       </c>
       <c r="J4" t="n">
         <v>57</v>
       </c>
       <c r="K4" t="n">
-        <v>393086</v>
+        <v>396810</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>1291095.36</v>
+        <v>1261983.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>262558.54</v>
+        <v>299119.54</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1028536.82</v>
+        <v>962863.8199999998</v>
       </c>
       <c r="I5" t="n">
-        <v>830200</v>
+        <v>750539</v>
       </c>
       <c r="J5" t="n">
-        <v>198336</v>
+        <v>212324</v>
       </c>
       <c r="K5" t="n">
-        <v>780206</v>
+        <v>760333</v>
       </c>
     </row>
     <row r="6">
@@ -660,11 +660,11 @@
         <v>2500000</v>
       </c>
       <c r="D6" t="n">
-        <v>1013467.92</v>
+        <v>1041378.92</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -672,20 +672,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>954648.92</v>
+        <v>982559.92</v>
       </c>
       <c r="I6" t="n">
-        <v>367654</v>
+        <v>382386</v>
       </c>
       <c r="J6" t="n">
-        <v>586994</v>
+        <v>600173</v>
       </c>
       <c r="K6" t="n">
-        <v>915454</v>
+        <v>943365</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>500000</v>
       </c>
       <c r="D7" t="n">
-        <v>93303.84</v>
+        <v>91623.84</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5457</v>
+        <v>7857</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>87846.84</v>
+        <v>83766.84</v>
       </c>
       <c r="I7" t="n">
-        <v>68365</v>
+        <v>65965</v>
       </c>
       <c r="J7" t="n">
-        <v>19281</v>
+        <v>17601</v>
       </c>
       <c r="K7" t="n">
-        <v>21276</v>
+        <v>19596</v>
       </c>
     </row>
     <row r="8">
@@ -789,7 +789,7 @@
         <v>1000000</v>
       </c>
       <c r="D9" t="n">
-        <v>369595.9</v>
+        <v>370371.98</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -797,24 +797,24 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>33000</v>
+        <v>36519</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>336595.9</v>
+        <v>333852.98</v>
       </c>
       <c r="I9" t="n">
-        <v>55558</v>
+        <v>52039</v>
       </c>
       <c r="J9" t="n">
         <v>257625</v>
       </c>
       <c r="K9" t="n">
-        <v>35035</v>
+        <v>35792</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>1100000</v>
       </c>
       <c r="D10" t="n">
-        <v>242704.11</v>
+        <v>206497.87</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -844,20 +844,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>100.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>35860.11000000002</v>
+        <v>-346.1300000000047</v>
       </c>
       <c r="I10" t="n">
-        <v>-63078</v>
+        <v>-63505</v>
       </c>
       <c r="J10" t="n">
-        <v>86391</v>
+        <v>49393</v>
       </c>
       <c r="K10" t="n">
-        <v>266</v>
+        <v>-24944</v>
       </c>
     </row>
     <row r="11">
@@ -875,7 +875,7 @@
         <v>400000</v>
       </c>
       <c r="D11" t="n">
-        <v>63761.8</v>
+        <v>63608</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -883,24 +883,24 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>7121.33</v>
+        <v>29921.33</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>56640.47</v>
+        <v>33686.67</v>
       </c>
       <c r="I11" t="n">
-        <v>-4912</v>
+        <v>-4941</v>
       </c>
       <c r="J11" t="n">
-        <v>61552</v>
+        <v>38628</v>
       </c>
       <c r="K11" t="n">
-        <v>11945</v>
+        <v>-11008</v>
       </c>
     </row>
     <row r="12">
@@ -961,32 +961,32 @@
         <v>1900000</v>
       </c>
       <c r="D13" t="n">
-        <v>210874.8</v>
+        <v>258457.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>244098</v>
+        <v>268077</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>115.8%</t>
+          <t>103.7%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-33223.20000000001</v>
+        <v>-9619.600000000006</v>
       </c>
       <c r="I13" t="n">
-        <v>-160990</v>
+        <v>-135657</v>
       </c>
       <c r="J13" t="n">
-        <v>96848</v>
+        <v>94868</v>
       </c>
       <c r="K13" t="n">
-        <v>-101357</v>
+        <v>-77753</v>
       </c>
     </row>
     <row r="14">
@@ -1004,7 +1004,7 @@
         <v>1000000</v>
       </c>
       <c r="D14" t="n">
-        <v>920064.14</v>
+        <v>920064.1400000001</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1012,24 +1012,24 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>103647.59</v>
+        <v>110247.59</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>816416.55</v>
+        <v>809816.5500000002</v>
       </c>
       <c r="I14" t="n">
-        <v>129270</v>
+        <v>122272</v>
       </c>
       <c r="J14" t="n">
-        <v>665645</v>
+        <v>666043</v>
       </c>
       <c r="K14" t="n">
-        <v>382370</v>
+        <v>375770</v>
       </c>
     </row>
     <row r="15">
@@ -1047,32 +1047,32 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>372511.87</v>
+        <v>373364.21</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>33628</v>
+        <v>38128</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>338883.87</v>
+        <v>335236.21</v>
       </c>
       <c r="I15" t="n">
-        <v>89561</v>
+        <v>89163</v>
       </c>
       <c r="J15" t="n">
-        <v>198976</v>
+        <v>194874</v>
       </c>
       <c r="K15" t="n">
-        <v>59891</v>
+        <v>60744</v>
       </c>
     </row>
     <row r="16">
@@ -1098,24 +1098,24 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>12362</v>
+        <v>17381</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>135331</v>
+        <v>130312</v>
       </c>
       <c r="I16" t="n">
-        <v>26878</v>
+        <v>26859</v>
       </c>
       <c r="J16" t="n">
-        <v>108453</v>
+        <v>103453</v>
       </c>
       <c r="K16" t="n">
-        <v>39269</v>
+        <v>39250</v>
       </c>
     </row>
     <row r="17">
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>29086</v>
+        <v>74457</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1184,24 +1184,24 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>24218</v>
+        <v>26217</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>4868</v>
+        <v>48240</v>
       </c>
       <c r="I18" t="n">
-        <v>5068</v>
+        <v>48440</v>
       </c>
       <c r="J18" t="n">
         <v>-200</v>
       </c>
       <c r="K18" t="n">
-        <v>12368</v>
+        <v>55740</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>564019.01</v>
+        <v>651711.3100000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>97723.45</v>
+        <v>121033.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>466295.56</v>
+        <v>530677.8600000001</v>
       </c>
       <c r="I2" t="n">
-        <v>441093</v>
+        <v>499174</v>
       </c>
       <c r="J2" t="n">
-        <v>25201</v>
+        <v>31502</v>
       </c>
       <c r="K2" t="n">
-        <v>418925</v>
+        <v>469011</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>240170.41</v>
+        <v>282567.41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>188021.07</v>
+        <v>220151.07</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>78.3%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>52149.34</v>
+        <v>62416.33999999997</v>
       </c>
       <c r="I3" t="n">
-        <v>34233</v>
+        <v>43000</v>
       </c>
       <c r="J3" t="n">
-        <v>17915</v>
+        <v>19415</v>
       </c>
       <c r="K3" t="n">
-        <v>69255</v>
+        <v>76122</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>667558.88</v>
+        <v>747913.78</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>149341.97</v>
+        <v>158534.87</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>518216.91</v>
+        <v>589378.91</v>
       </c>
       <c r="I4" t="n">
-        <v>518159</v>
+        <v>589321</v>
       </c>
       <c r="J4" t="n">
         <v>57</v>
       </c>
       <c r="K4" t="n">
-        <v>396810</v>
+        <v>456608</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>1261983.36</v>
+        <v>1394627.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>299119.54</v>
+        <v>349147.54</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>962863.8199999998</v>
+        <v>1045479.82</v>
       </c>
       <c r="I5" t="n">
-        <v>750539</v>
+        <v>834656</v>
       </c>
       <c r="J5" t="n">
-        <v>212324</v>
+        <v>210823</v>
       </c>
       <c r="K5" t="n">
-        <v>760333</v>
+        <v>810251</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>2500000</v>
       </c>
       <c r="D6" t="n">
-        <v>1041378.92</v>
+        <v>1134208.92</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>58819</v>
+        <v>60819</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>982559.92</v>
+        <v>1073389.92</v>
       </c>
       <c r="I6" t="n">
-        <v>382386</v>
+        <v>28987</v>
       </c>
       <c r="J6" t="n">
-        <v>600173</v>
+        <v>1044402</v>
       </c>
       <c r="K6" t="n">
-        <v>943365</v>
+        <v>1035797</v>
       </c>
     </row>
     <row r="7">
@@ -703,11 +703,11 @@
         <v>500000</v>
       </c>
       <c r="D7" t="n">
-        <v>91623.84</v>
+        <v>139415.84</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -715,20 +715,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>83766.84</v>
+        <v>131558.84</v>
       </c>
       <c r="I7" t="n">
-        <v>65965</v>
+        <v>79159</v>
       </c>
       <c r="J7" t="n">
-        <v>17601</v>
+        <v>51999</v>
       </c>
       <c r="K7" t="n">
-        <v>19596</v>
+        <v>19796</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>600000</v>
       </c>
       <c r="D8" t="n">
-        <v>382596</v>
+        <v>405687</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>9280</v>
+        <v>11280</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>373316</v>
+        <v>394407</v>
       </c>
       <c r="I8" t="n">
-        <v>24726</v>
+        <v>25423</v>
       </c>
       <c r="J8" t="n">
-        <v>348590</v>
+        <v>368984</v>
       </c>
       <c r="K8" t="n">
-        <v>82556</v>
+        <v>84049</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>1000000</v>
       </c>
       <c r="D9" t="n">
-        <v>370371.98</v>
+        <v>441271.58</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>333852.98</v>
+        <v>404752.58</v>
       </c>
       <c r="I9" t="n">
-        <v>52039</v>
+        <v>43589</v>
       </c>
       <c r="J9" t="n">
-        <v>257625</v>
+        <v>335638</v>
       </c>
       <c r="K9" t="n">
-        <v>35792</v>
+        <v>37504</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>1100000</v>
       </c>
       <c r="D10" t="n">
-        <v>206497.87</v>
+        <v>687024.87</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>206844</v>
+        <v>259842</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>100.2%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-346.1300000000047</v>
+        <v>427182.87</v>
       </c>
       <c r="I10" t="n">
-        <v>-63505</v>
+        <v>114773</v>
       </c>
       <c r="J10" t="n">
-        <v>49393</v>
+        <v>298644</v>
       </c>
       <c r="K10" t="n">
-        <v>-24944</v>
+        <v>342608</v>
       </c>
     </row>
     <row r="11">
@@ -875,32 +875,32 @@
         <v>400000</v>
       </c>
       <c r="D11" t="n">
-        <v>63608</v>
+        <v>71780.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>29921.33</v>
+        <v>41921.33</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>33686.67</v>
+        <v>29859.47</v>
       </c>
       <c r="I11" t="n">
-        <v>-4941</v>
+        <v>-4893</v>
       </c>
       <c r="J11" t="n">
-        <v>38628</v>
+        <v>34752</v>
       </c>
       <c r="K11" t="n">
-        <v>-11008</v>
+        <v>-10835</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>500000</v>
       </c>
       <c r="D12" t="n">
-        <v>261438</v>
+        <v>262957</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>245600</v>
+        <v>247119</v>
       </c>
       <c r="I12" t="n">
-        <v>55810</v>
+        <v>55829</v>
       </c>
       <c r="J12" t="n">
-        <v>189790</v>
+        <v>191290</v>
       </c>
       <c r="K12" t="n">
-        <v>91438</v>
+        <v>91457</v>
       </c>
     </row>
     <row r="13">
@@ -961,32 +961,32 @@
         <v>1900000</v>
       </c>
       <c r="D13" t="n">
-        <v>258457.4</v>
+        <v>1463526.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>268077</v>
+        <v>285476</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>103.7%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-9619.600000000006</v>
+        <v>1178050.4</v>
       </c>
       <c r="I13" t="n">
-        <v>-135657</v>
+        <v>1015013</v>
       </c>
       <c r="J13" t="n">
-        <v>94868</v>
+        <v>131868</v>
       </c>
       <c r="K13" t="n">
-        <v>-77753</v>
+        <v>1083418</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>1000000</v>
       </c>
       <c r="D14" t="n">
-        <v>920064.1400000001</v>
+        <v>938917.14</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>809816.5500000002</v>
+        <v>828669.55</v>
       </c>
       <c r="I14" t="n">
-        <v>122272</v>
+        <v>126849</v>
       </c>
       <c r="J14" t="n">
-        <v>666043</v>
+        <v>680319</v>
       </c>
       <c r="K14" t="n">
-        <v>375770</v>
+        <v>382229</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>900000</v>
       </c>
       <c r="D15" t="n">
-        <v>373364.21</v>
+        <v>387112.21</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>335236.21</v>
+        <v>348984.21</v>
       </c>
       <c r="I15" t="n">
-        <v>89163</v>
+        <v>89211</v>
       </c>
       <c r="J15" t="n">
-        <v>194874</v>
+        <v>208574</v>
       </c>
       <c r="K15" t="n">
-        <v>60744</v>
+        <v>60792</v>
       </c>
     </row>
     <row r="16">
@@ -1090,32 +1090,32 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>147693</v>
+        <v>170797</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>17381</v>
+        <v>38831</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>130312</v>
+        <v>131966</v>
       </c>
       <c r="I16" t="n">
-        <v>26859</v>
+        <v>26868</v>
       </c>
       <c r="J16" t="n">
-        <v>103453</v>
+        <v>105098</v>
       </c>
       <c r="K16" t="n">
-        <v>39250</v>
+        <v>39558</v>
       </c>
     </row>
     <row r="17">
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>74457</v>
+        <v>570839.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1184,24 +1184,24 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>26217</v>
+        <v>58137</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>48240</v>
+        <v>512702.8</v>
       </c>
       <c r="I18" t="n">
-        <v>48440</v>
+        <v>512521</v>
       </c>
       <c r="J18" t="n">
-        <v>-200</v>
+        <v>181</v>
       </c>
       <c r="K18" t="n">
-        <v>55740</v>
+        <v>484406</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>651711.3100000001</v>
+        <v>644894.0900000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>121033.45</v>
+        <v>120995.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>530677.8600000001</v>
+        <v>523898.6400000001</v>
       </c>
       <c r="I2" t="n">
-        <v>499174</v>
+        <v>492997</v>
       </c>
       <c r="J2" t="n">
-        <v>31502</v>
+        <v>30900</v>
       </c>
       <c r="K2" t="n">
-        <v>469011</v>
+        <v>462232</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>282567.41</v>
+        <v>282211.41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -539,24 +539,24 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>220151.07</v>
+        <v>220132.07</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>77.9%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>62416.33999999997</v>
+        <v>62079.33999999997</v>
       </c>
       <c r="I3" t="n">
-        <v>43000</v>
+        <v>42663</v>
       </c>
       <c r="J3" t="n">
         <v>19415</v>
       </c>
       <c r="K3" t="n">
-        <v>76122</v>
+        <v>75785</v>
       </c>
     </row>
     <row r="4">
@@ -574,7 +574,7 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>747913.78</v>
+        <v>747666.78</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>158534.87</v>
+        <v>158420.87</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -590,16 +590,16 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>589378.91</v>
+        <v>589245.91</v>
       </c>
       <c r="I4" t="n">
-        <v>589321</v>
+        <v>589188</v>
       </c>
       <c r="J4" t="n">
         <v>57</v>
       </c>
       <c r="K4" t="n">
-        <v>456608</v>
+        <v>456475</v>
       </c>
     </row>
     <row r="5">
@@ -648,50 +648,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>普陀</t>
+          <t>观澜组</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>门店</t>
+          <t>销售</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2500000</v>
+        <v>1300000</v>
       </c>
       <c r="D6" t="n">
-        <v>1134208.92</v>
+        <v>538346</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>60819</v>
+        <v>44760</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1073389.92</v>
+        <v>493586</v>
       </c>
       <c r="I6" t="n">
-        <v>28987</v>
+        <v>493586</v>
       </c>
       <c r="J6" t="n">
-        <v>1044402</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1035797</v>
+        <v>478790</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>昆明</t>
+          <t>普陀</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -700,41 +700,41 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>500000</v>
+        <v>2500000</v>
       </c>
       <c r="D7" t="n">
-        <v>139415.84</v>
+        <v>1134208.92</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>7857</v>
+        <v>60819</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>131558.84</v>
+        <v>1073389.92</v>
       </c>
       <c r="I7" t="n">
-        <v>79159</v>
+        <v>28987</v>
       </c>
       <c r="J7" t="n">
-        <v>51999</v>
+        <v>1044402</v>
       </c>
       <c r="K7" t="n">
-        <v>19796</v>
+        <v>1035797</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>成都</t>
+          <t>昆明</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -743,41 +743,41 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="D8" t="n">
-        <v>405687</v>
+        <v>139415.84</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>11280</v>
+        <v>7857</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>394407</v>
+        <v>131558.84</v>
       </c>
       <c r="I8" t="n">
-        <v>25423</v>
+        <v>79159</v>
       </c>
       <c r="J8" t="n">
-        <v>368984</v>
+        <v>51999</v>
       </c>
       <c r="K8" t="n">
-        <v>84049</v>
+        <v>19796</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>广州</t>
+          <t>成都</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -786,41 +786,41 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1000000</v>
+        <v>600000</v>
       </c>
       <c r="D9" t="n">
-        <v>441271.58</v>
+        <v>405687</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>36519</v>
+        <v>11280</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>404752.58</v>
+        <v>394407</v>
       </c>
       <c r="I9" t="n">
-        <v>43589</v>
+        <v>25423</v>
       </c>
       <c r="J9" t="n">
-        <v>335638</v>
+        <v>368984</v>
       </c>
       <c r="K9" t="n">
-        <v>37504</v>
+        <v>84049</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>深圳</t>
+          <t>广州</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -829,41 +829,41 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1100000</v>
+        <v>1000000</v>
       </c>
       <c r="D10" t="n">
-        <v>687024.87</v>
+        <v>441271.58</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>259842</v>
+        <v>36519</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>427182.87</v>
+        <v>404752.58</v>
       </c>
       <c r="I10" t="n">
-        <v>114773</v>
+        <v>43589</v>
       </c>
       <c r="J10" t="n">
-        <v>298644</v>
+        <v>335638</v>
       </c>
       <c r="K10" t="n">
-        <v>342608</v>
+        <v>37504</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>珠海</t>
+          <t>深圳</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -872,41 +872,41 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>400000</v>
+        <v>1100000</v>
       </c>
       <c r="D11" t="n">
-        <v>71780.8</v>
+        <v>682044.87</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>41921.33</v>
+        <v>259842</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>29859.47</v>
+        <v>422202.87</v>
       </c>
       <c r="I11" t="n">
-        <v>-4893</v>
+        <v>109793</v>
       </c>
       <c r="J11" t="n">
-        <v>34752</v>
+        <v>298644</v>
       </c>
       <c r="K11" t="n">
-        <v>-10835</v>
+        <v>337628</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>福州</t>
+          <t>珠海</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -915,41 +915,41 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>500000</v>
+        <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>262957</v>
+        <v>71780.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>15838</v>
+        <v>41921.33</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>247119</v>
+        <v>29859.47</v>
       </c>
       <c r="I12" t="n">
-        <v>55829</v>
+        <v>-4893</v>
       </c>
       <c r="J12" t="n">
-        <v>191290</v>
+        <v>34752</v>
       </c>
       <c r="K12" t="n">
-        <v>91457</v>
+        <v>-10835</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>杭州</t>
+          <t>福州</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -958,41 +958,41 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1900000</v>
+        <v>500000</v>
       </c>
       <c r="D13" t="n">
-        <v>1463526.4</v>
+        <v>262957</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>285476</v>
+        <v>15838</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1178050.4</v>
+        <v>247119</v>
       </c>
       <c r="I13" t="n">
-        <v>1015013</v>
+        <v>55829</v>
       </c>
       <c r="J13" t="n">
-        <v>131868</v>
+        <v>191290</v>
       </c>
       <c r="K13" t="n">
-        <v>1083418</v>
+        <v>91457</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>南京</t>
+          <t>杭州</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1001,41 +1001,41 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1000000</v>
+        <v>1900000</v>
       </c>
       <c r="D14" t="n">
-        <v>938917.14</v>
+        <v>1463526.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>110247.59</v>
+        <v>285476</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>828669.55</v>
+        <v>1178050.4</v>
       </c>
       <c r="I14" t="n">
-        <v>126849</v>
+        <v>1015013</v>
       </c>
       <c r="J14" t="n">
-        <v>680319</v>
+        <v>131868</v>
       </c>
       <c r="K14" t="n">
-        <v>382229</v>
+        <v>1083418</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>武汉</t>
+          <t>南京</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1044,41 +1044,41 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>900000</v>
+        <v>1000000</v>
       </c>
       <c r="D15" t="n">
-        <v>387112.21</v>
+        <v>938917.14</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>38128</v>
+        <v>110247.59</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>348984.21</v>
+        <v>828669.55</v>
       </c>
       <c r="I15" t="n">
-        <v>89211</v>
+        <v>126849</v>
       </c>
       <c r="J15" t="n">
-        <v>208574</v>
+        <v>680319</v>
       </c>
       <c r="K15" t="n">
-        <v>60792</v>
+        <v>382229</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>徐汇</t>
+          <t>武汉</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1090,38 +1090,38 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>170797</v>
+        <v>387112.21</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>38831</v>
+        <v>38128</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>131966</v>
+        <v>348984.21</v>
       </c>
       <c r="I16" t="n">
-        <v>26868</v>
+        <v>89211</v>
       </c>
       <c r="J16" t="n">
-        <v>105098</v>
+        <v>208574</v>
       </c>
       <c r="K16" t="n">
-        <v>39558</v>
+        <v>60792</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>望京</t>
+          <t>徐汇</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1130,35 +1130,35 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>900000</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>170797</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>38831</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>131966</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>26868</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>105098</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>39558</v>
       </c>
     </row>
     <row r="18">
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>570839.8</v>
+        <v>32493.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1184,24 +1184,24 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>58137</v>
+        <v>13377</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>512702.8</v>
+        <v>19116.8</v>
       </c>
       <c r="I18" t="n">
-        <v>512521</v>
+        <v>18935</v>
       </c>
       <c r="J18" t="n">
         <v>181</v>
       </c>
       <c r="K18" t="n">
-        <v>484406</v>
+        <v>5616</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>644894.0900000001</v>
+        <v>14996</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>120995.45</v>
+        <v>129547.45</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>863.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>523898.6400000001</v>
+        <v>-114551.45</v>
       </c>
       <c r="I2" t="n">
-        <v>492997</v>
+        <v>-110551</v>
       </c>
       <c r="J2" t="n">
-        <v>30900</v>
+        <v>-4000</v>
       </c>
       <c r="K2" t="n">
-        <v>462232</v>
+        <v>-94243</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>282211.41</v>
+        <v>3337</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>220132.07</v>
+        <v>220402.07</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>6604.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>62079.33999999997</v>
+        <v>-217065.07</v>
       </c>
       <c r="I3" t="n">
-        <v>42663</v>
+        <v>-212085</v>
       </c>
       <c r="J3" t="n">
-        <v>19415</v>
+        <v>-4980</v>
       </c>
       <c r="K3" t="n">
-        <v>75785</v>
+        <v>-191965</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>747666.78</v>
+        <v>7514</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>158420.87</v>
+        <v>162922.87</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>2168.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>589245.91</v>
+        <v>-155408.87</v>
       </c>
       <c r="I4" t="n">
-        <v>589188</v>
+        <v>-151608</v>
       </c>
       <c r="J4" t="n">
-        <v>57</v>
+        <v>-3800</v>
       </c>
       <c r="K4" t="n">
-        <v>456475</v>
+        <v>-91180</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>1394627.36</v>
+        <v>751</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>349147.54</v>
+        <v>359147.54</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>47822.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1045479.82</v>
+        <v>-358396.54</v>
       </c>
       <c r="I5" t="n">
-        <v>834656</v>
+        <v>-352916</v>
       </c>
       <c r="J5" t="n">
-        <v>210823</v>
+        <v>-5480</v>
       </c>
       <c r="K5" t="n">
-        <v>810251</v>
+        <v>-245156</v>
       </c>
     </row>
     <row r="6">
@@ -660,11 +660,11 @@
         <v>1300000</v>
       </c>
       <c r="D6" t="n">
-        <v>538346</v>
+        <v>2260</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -672,20 +672,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>1980.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>493586</v>
+        <v>-42500</v>
       </c>
       <c r="I6" t="n">
-        <v>493586</v>
+        <v>-42500</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>478790</v>
+        <v>-41500</v>
       </c>
     </row>
     <row r="7">
@@ -703,11 +703,11 @@
         <v>2500000</v>
       </c>
       <c r="D7" t="n">
-        <v>1134208.92</v>
+        <v>1114788.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -715,20 +715,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1073389.92</v>
+        <v>1053969.1</v>
       </c>
       <c r="I7" t="n">
-        <v>28987</v>
+        <v>397219</v>
       </c>
       <c r="J7" t="n">
-        <v>1044402</v>
+        <v>656750</v>
       </c>
       <c r="K7" t="n">
-        <v>1035797</v>
+        <v>1077969</v>
       </c>
     </row>
     <row r="8">
@@ -746,11 +746,11 @@
         <v>500000</v>
       </c>
       <c r="D8" t="n">
-        <v>139415.84</v>
+        <v>438</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -758,20 +758,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>1793.8%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>131558.84</v>
+        <v>-7419</v>
       </c>
       <c r="I8" t="n">
-        <v>79159</v>
+        <v>-2419</v>
       </c>
       <c r="J8" t="n">
-        <v>51999</v>
+        <v>-5400</v>
       </c>
       <c r="K8" t="n">
-        <v>19796</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>600000</v>
       </c>
       <c r="D9" t="n">
-        <v>405687</v>
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>394407</v>
+        <v>-11280</v>
       </c>
       <c r="I9" t="n">
-        <v>25423</v>
+        <v>-8280</v>
       </c>
       <c r="J9" t="n">
-        <v>368984</v>
+        <v>-3000</v>
       </c>
       <c r="K9" t="n">
-        <v>84049</v>
+        <v>-8280</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>1000000</v>
       </c>
       <c r="D10" t="n">
-        <v>441271.58</v>
+        <v>25642.86</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -844,20 +844,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>142.4%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>404752.58</v>
+        <v>-10876.14</v>
       </c>
       <c r="I10" t="n">
-        <v>43589</v>
+        <v>-20500</v>
       </c>
       <c r="J10" t="n">
-        <v>335638</v>
+        <v>-16000</v>
       </c>
       <c r="K10" t="n">
-        <v>37504</v>
+        <v>25623</v>
       </c>
     </row>
     <row r="11">
@@ -875,32 +875,32 @@
         <v>1100000</v>
       </c>
       <c r="D11" t="n">
-        <v>682044.87</v>
+        <v>15978.86</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>259842</v>
+        <v>265441</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>1661.2%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>422202.87</v>
+        <v>-249462.14</v>
       </c>
       <c r="I11" t="n">
-        <v>109793</v>
+        <v>-187469</v>
       </c>
       <c r="J11" t="n">
-        <v>298644</v>
+        <v>-75759</v>
       </c>
       <c r="K11" t="n">
-        <v>337628</v>
+        <v>-86692</v>
       </c>
     </row>
     <row r="12">
@@ -918,32 +918,32 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>71780.8</v>
+        <v>48</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>41921.33</v>
+        <v>41950.33</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>87396.5%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>29859.47</v>
+        <v>-41902.33</v>
       </c>
       <c r="I12" t="n">
-        <v>-4893</v>
+        <v>-7102</v>
       </c>
       <c r="J12" t="n">
-        <v>34752</v>
+        <v>-34800</v>
       </c>
       <c r="K12" t="n">
-        <v>-10835</v>
+        <v>-22819</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>500000</v>
       </c>
       <c r="D13" t="n">
-        <v>262957</v>
+        <v>19</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>83357.9%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>247119</v>
+        <v>-15819</v>
       </c>
       <c r="I13" t="n">
-        <v>55829</v>
+        <v>-19</v>
       </c>
       <c r="J13" t="n">
-        <v>191290</v>
+        <v>-15800</v>
       </c>
       <c r="K13" t="n">
-        <v>91457</v>
+        <v>-19</v>
       </c>
     </row>
     <row r="14">
@@ -1004,32 +1004,32 @@
         <v>1900000</v>
       </c>
       <c r="D14" t="n">
-        <v>1463526.4</v>
+        <v>91509.39999999999</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>285476</v>
+        <v>305912</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>334.3%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1178050.4</v>
+        <v>-214402.6</v>
       </c>
       <c r="I14" t="n">
-        <v>1015013</v>
+        <v>-207794</v>
       </c>
       <c r="J14" t="n">
-        <v>131868</v>
+        <v>-37778</v>
       </c>
       <c r="K14" t="n">
-        <v>1083418</v>
+        <v>-152692</v>
       </c>
     </row>
     <row r="15">
@@ -1047,32 +1047,32 @@
         <v>1000000</v>
       </c>
       <c r="D15" t="n">
-        <v>938917.14</v>
+        <v>23187.59</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>110247.59</v>
+        <v>114266.59</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>492.8%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>828669.55</v>
+        <v>-91079</v>
       </c>
       <c r="I15" t="n">
-        <v>126849</v>
+        <v>-76499</v>
       </c>
       <c r="J15" t="n">
-        <v>680319</v>
+        <v>-36080</v>
       </c>
       <c r="K15" t="n">
-        <v>382229</v>
+        <v>-56979</v>
       </c>
     </row>
     <row r="16">
@@ -1090,32 +1090,32 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>387112.21</v>
+        <v>51246.21000000001</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>38128</v>
+        <v>66947</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>130.6%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>348984.21</v>
+        <v>-15700.78999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>89211</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>208574</v>
+        <v>-66900</v>
       </c>
       <c r="K16" t="n">
-        <v>60792</v>
+        <v>26399</v>
       </c>
     </row>
     <row r="17">
@@ -1133,32 +1133,32 @@
         <v>900000</v>
       </c>
       <c r="D17" t="n">
-        <v>170797</v>
+        <v>724</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>38831</v>
+        <v>38850</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>5366.0%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>131966</v>
+        <v>-38126</v>
       </c>
       <c r="I17" t="n">
-        <v>26868</v>
+        <v>-6000</v>
       </c>
       <c r="J17" t="n">
-        <v>105098</v>
+        <v>-32126</v>
       </c>
       <c r="K17" t="n">
-        <v>39558</v>
+        <v>-1680</v>
       </c>
     </row>
     <row r="18">
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>32493.8</v>
+        <v>5018</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1188,20 +1188,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>266.6%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>19116.8</v>
+        <v>-8359</v>
       </c>
       <c r="I18" t="n">
-        <v>18935</v>
+        <v>-8159</v>
       </c>
       <c r="J18" t="n">
-        <v>181</v>
+        <v>-200</v>
       </c>
       <c r="K18" t="n">
-        <v>5616</v>
+        <v>-1859</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,11 +488,11 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>14996</v>
+        <v>783326.16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -500,20 +500,20 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>863.9%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-114551.45</v>
+        <v>653778.7100000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-110551</v>
+        <v>621580</v>
       </c>
       <c r="J2" t="n">
-        <v>-4000</v>
+        <v>32198</v>
       </c>
       <c r="K2" t="n">
-        <v>-94243</v>
+        <v>591514</v>
       </c>
     </row>
     <row r="3">
@@ -531,11 +531,11 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>3337</v>
+        <v>325870.41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -543,20 +543,20 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>6604.8%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>-217065.07</v>
+        <v>105468.34</v>
       </c>
       <c r="I3" t="n">
-        <v>-212085</v>
+        <v>86052</v>
       </c>
       <c r="J3" t="n">
-        <v>-4980</v>
+        <v>19415</v>
       </c>
       <c r="K3" t="n">
-        <v>-191965</v>
+        <v>119174</v>
       </c>
     </row>
     <row r="4">
@@ -574,11 +574,11 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>7514</v>
+        <v>824725.78</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -586,20 +586,20 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2168.3%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>-155408.87</v>
+        <v>661802.91</v>
       </c>
       <c r="I4" t="n">
-        <v>-151608</v>
+        <v>665522</v>
       </c>
       <c r="J4" t="n">
-        <v>-3800</v>
+        <v>-3720</v>
       </c>
       <c r="K4" t="n">
-        <v>-91180</v>
+        <v>507032</v>
       </c>
     </row>
     <row r="5">
@@ -617,11 +617,11 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>751</v>
+        <v>1446274.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -629,20 +629,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>47822.6%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>-358396.54</v>
+        <v>1087126.82</v>
       </c>
       <c r="I5" t="n">
-        <v>-352916</v>
+        <v>876303</v>
       </c>
       <c r="J5" t="n">
-        <v>-5480</v>
+        <v>210823</v>
       </c>
       <c r="K5" t="n">
-        <v>-245156</v>
+        <v>837078</v>
       </c>
     </row>
     <row r="6">
@@ -660,11 +660,11 @@
         <v>1300000</v>
       </c>
       <c r="D6" t="n">
-        <v>2260</v>
+        <v>588664</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -672,20 +672,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1980.5%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>-42500</v>
+        <v>543904</v>
       </c>
       <c r="I6" t="n">
-        <v>-42500</v>
+        <v>542824</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1080</v>
       </c>
       <c r="K6" t="n">
-        <v>-41500</v>
+        <v>484910</v>
       </c>
     </row>
     <row r="7">
@@ -703,11 +703,11 @@
         <v>2500000</v>
       </c>
       <c r="D7" t="n">
-        <v>1114788.1</v>
+        <v>1184871</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -715,20 +715,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1053969.1</v>
+        <v>1124052</v>
       </c>
       <c r="I7" t="n">
-        <v>397219</v>
+        <v>428226</v>
       </c>
       <c r="J7" t="n">
-        <v>656750</v>
+        <v>695826</v>
       </c>
       <c r="K7" t="n">
-        <v>1077969</v>
+        <v>1086460</v>
       </c>
     </row>
     <row r="8">
@@ -746,11 +746,11 @@
         <v>500000</v>
       </c>
       <c r="D8" t="n">
-        <v>438</v>
+        <v>153032.84</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -758,20 +758,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1793.8%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>-7419</v>
+        <v>145175.84</v>
       </c>
       <c r="I8" t="n">
-        <v>-2419</v>
+        <v>92776</v>
       </c>
       <c r="J8" t="n">
-        <v>-5400</v>
+        <v>51999</v>
       </c>
       <c r="K8" t="n">
-        <v>381</v>
+        <v>33015</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>600000</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>413102</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>-11280</v>
+        <v>401822</v>
       </c>
       <c r="I9" t="n">
-        <v>-8280</v>
+        <v>25044</v>
       </c>
       <c r="J9" t="n">
-        <v>-3000</v>
+        <v>376778</v>
       </c>
       <c r="K9" t="n">
-        <v>-8280</v>
+        <v>91066</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>1000000</v>
       </c>
       <c r="D10" t="n">
-        <v>25642.86</v>
+        <v>471427.33</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -844,20 +844,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>142.4%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>-10876.14</v>
+        <v>434908.33</v>
       </c>
       <c r="I10" t="n">
-        <v>-20500</v>
+        <v>43646</v>
       </c>
       <c r="J10" t="n">
-        <v>-16000</v>
+        <v>365638</v>
       </c>
       <c r="K10" t="n">
-        <v>25623</v>
+        <v>37660</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>1100000</v>
       </c>
       <c r="D11" t="n">
-        <v>15978.86</v>
+        <v>684757.87</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1661.2%</t>
+          <t>38.8%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>-249462.14</v>
+        <v>419316.87</v>
       </c>
       <c r="I11" t="n">
-        <v>-187469</v>
+        <v>110109</v>
       </c>
       <c r="J11" t="n">
-        <v>-75759</v>
+        <v>295442</v>
       </c>
       <c r="K11" t="n">
-        <v>-86692</v>
+        <v>337148</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>48</v>
+        <v>80605.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>87396.5%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>-41902.33</v>
+        <v>38655.47</v>
       </c>
       <c r="I12" t="n">
-        <v>-7102</v>
+        <v>-4495</v>
       </c>
       <c r="J12" t="n">
-        <v>-34800</v>
+        <v>43150</v>
       </c>
       <c r="K12" t="n">
-        <v>-22819</v>
+        <v>-10835</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>500000</v>
       </c>
       <c r="D13" t="n">
-        <v>19</v>
+        <v>262957</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>83357.9%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>-15819</v>
+        <v>247119</v>
       </c>
       <c r="I13" t="n">
-        <v>-19</v>
+        <v>55829</v>
       </c>
       <c r="J13" t="n">
-        <v>-15800</v>
+        <v>191290</v>
       </c>
       <c r="K13" t="n">
-        <v>-19</v>
+        <v>91457</v>
       </c>
     </row>
     <row r="14">
@@ -1004,11 +1004,11 @@
         <v>1900000</v>
       </c>
       <c r="D14" t="n">
-        <v>91509.39999999999</v>
+        <v>1465620.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>334.3%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>-214402.6</v>
+        <v>1159708.4</v>
       </c>
       <c r="I14" t="n">
-        <v>-207794</v>
+        <v>1016671</v>
       </c>
       <c r="J14" t="n">
-        <v>-37778</v>
+        <v>111868</v>
       </c>
       <c r="K14" t="n">
-        <v>-152692</v>
+        <v>1085474</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>1000000</v>
       </c>
       <c r="D15" t="n">
-        <v>23187.59</v>
+        <v>966916.14</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>96.7%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>492.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-91079</v>
+        <v>852649.55</v>
       </c>
       <c r="I15" t="n">
-        <v>-76499</v>
+        <v>126849</v>
       </c>
       <c r="J15" t="n">
-        <v>-36080</v>
+        <v>704299</v>
       </c>
       <c r="K15" t="n">
-        <v>-56979</v>
+        <v>384209</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>51246.21000000001</v>
+        <v>408765.21</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>130.6%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>-15700.78999999999</v>
+        <v>341818.21</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>97128</v>
       </c>
       <c r="J16" t="n">
-        <v>-66900</v>
+        <v>193491</v>
       </c>
       <c r="K16" t="n">
-        <v>26399</v>
+        <v>36030</v>
       </c>
     </row>
     <row r="17">
@@ -1133,11 +1133,11 @@
         <v>900000</v>
       </c>
       <c r="D17" t="n">
-        <v>724</v>
+        <v>183273</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1145,20 +1145,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5366.0%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>-38126</v>
+        <v>144423</v>
       </c>
       <c r="I17" t="n">
-        <v>-6000</v>
+        <v>26849</v>
       </c>
       <c r="J17" t="n">
-        <v>-32126</v>
+        <v>117574</v>
       </c>
       <c r="K17" t="n">
-        <v>-1680</v>
+        <v>41219</v>
       </c>
     </row>
     <row r="18">
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5018</v>
+        <v>33019.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1188,20 +1188,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>266.6%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>-8359</v>
+        <v>19642.8</v>
       </c>
       <c r="I18" t="n">
-        <v>-8159</v>
+        <v>19461</v>
       </c>
       <c r="J18" t="n">
-        <v>-200</v>
+        <v>181</v>
       </c>
       <c r="K18" t="n">
-        <v>-1859</v>
+        <v>6142</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -429,12 +429,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>目标</t>
+          <t>目标(元)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>完成(元)</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
@@ -444,7 +444,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>本月退费</t>
+          <t>本月退费(元)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -454,22 +454,22 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>本月净流水</t>
+          <t>本月净流水(元)</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>新客净流水</t>
+          <t>新客净流水(元)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>老客净流水</t>
+          <t>老客净流水(元)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>非1V1及菌群净</t>
+          <t>非1V1及菌群净(元)</t>
         </is>
       </c>
     </row>
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>783326.16</v>
+        <v>881795.39</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>129547.45</v>
+        <v>134561.15</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>653778.7100000001</v>
+        <v>747234.24</v>
       </c>
       <c r="I2" t="n">
-        <v>621580</v>
+        <v>714980</v>
       </c>
       <c r="J2" t="n">
-        <v>32198</v>
+        <v>32253</v>
       </c>
       <c r="K2" t="n">
-        <v>591514</v>
+        <v>684174</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>325870.41</v>
+        <v>383448.41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>220402.07</v>
+        <v>250667.07</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>105468.34</v>
+        <v>132781.34</v>
       </c>
       <c r="I3" t="n">
-        <v>86052</v>
+        <v>93565</v>
       </c>
       <c r="J3" t="n">
-        <v>19415</v>
+        <v>39215</v>
       </c>
       <c r="K3" t="n">
-        <v>119174</v>
+        <v>146487</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>824725.78</v>
+        <v>920969.78</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>162922.87</v>
+        <v>167221.87</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>661802.91</v>
+        <v>753747.91</v>
       </c>
       <c r="I4" t="n">
-        <v>665522</v>
+        <v>757467</v>
       </c>
       <c r="J4" t="n">
         <v>-3720</v>
       </c>
       <c r="K4" t="n">
-        <v>507032</v>
+        <v>564565</v>
       </c>
     </row>
     <row r="5">
@@ -617,11 +617,11 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>1446274.36</v>
+        <v>1506000.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -629,20 +629,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1087126.82</v>
+        <v>1146852.82</v>
       </c>
       <c r="I5" t="n">
-        <v>876303</v>
+        <v>924029</v>
       </c>
       <c r="J5" t="n">
-        <v>210823</v>
+        <v>222823</v>
       </c>
       <c r="K5" t="n">
-        <v>837078</v>
+        <v>884206</v>
       </c>
     </row>
     <row r="6">
@@ -660,11 +660,11 @@
         <v>1300000</v>
       </c>
       <c r="D6" t="n">
-        <v>588664</v>
+        <v>549614</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -672,20 +672,20 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>543904</v>
+        <v>504854</v>
       </c>
       <c r="I6" t="n">
-        <v>542824</v>
+        <v>503774</v>
       </c>
       <c r="J6" t="n">
         <v>1080</v>
       </c>
       <c r="K6" t="n">
-        <v>484910</v>
+        <v>445860</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>2500000</v>
       </c>
       <c r="D7" t="n">
-        <v>1184871</v>
+        <v>1419809.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>60819</v>
+        <v>65819</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1124052</v>
+        <v>1353990.8</v>
       </c>
       <c r="I7" t="n">
-        <v>428226</v>
+        <v>560491</v>
       </c>
       <c r="J7" t="n">
-        <v>695826</v>
+        <v>793499</v>
       </c>
       <c r="K7" t="n">
-        <v>1086460</v>
+        <v>1319800</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>500000</v>
       </c>
       <c r="D8" t="n">
-        <v>153032.84</v>
+        <v>178081.84</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7857</v>
+        <v>15857</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>145175.84</v>
+        <v>162224.84</v>
       </c>
       <c r="I8" t="n">
-        <v>92776</v>
+        <v>106431</v>
       </c>
       <c r="J8" t="n">
-        <v>51999</v>
+        <v>55393</v>
       </c>
       <c r="K8" t="n">
-        <v>33015</v>
+        <v>46272</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>600000</v>
       </c>
       <c r="D9" t="n">
-        <v>413102</v>
+        <v>439088</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>401822</v>
+        <v>427808</v>
       </c>
       <c r="I9" t="n">
-        <v>25044</v>
+        <v>25442</v>
       </c>
       <c r="J9" t="n">
-        <v>376778</v>
+        <v>402366</v>
       </c>
       <c r="K9" t="n">
-        <v>91066</v>
+        <v>106654</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>1000000</v>
       </c>
       <c r="D10" t="n">
-        <v>471427.33</v>
+        <v>501128.33</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>36519</v>
+        <v>53319</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>434908.33</v>
+        <v>447809.33</v>
       </c>
       <c r="I10" t="n">
-        <v>43646</v>
+        <v>43884</v>
       </c>
       <c r="J10" t="n">
-        <v>365638</v>
+        <v>376736</v>
       </c>
       <c r="K10" t="n">
-        <v>37660</v>
+        <v>22663</v>
       </c>
     </row>
     <row r="11">
@@ -875,32 +875,32 @@
         <v>1100000</v>
       </c>
       <c r="D11" t="n">
-        <v>684757.87</v>
+        <v>705956.27</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>265441</v>
+        <v>265839</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>38.8%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>419316.87</v>
+        <v>440117.27</v>
       </c>
       <c r="I11" t="n">
-        <v>110109</v>
+        <v>115663</v>
       </c>
       <c r="J11" t="n">
-        <v>295442</v>
+        <v>309234</v>
       </c>
       <c r="K11" t="n">
-        <v>337148</v>
+        <v>343359</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>80605.8</v>
+        <v>108424.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>38655.47</v>
+        <v>66474.47</v>
       </c>
       <c r="I12" t="n">
-        <v>-4495</v>
+        <v>-4476</v>
       </c>
       <c r="J12" t="n">
-        <v>43150</v>
+        <v>70950</v>
       </c>
       <c r="K12" t="n">
-        <v>-10835</v>
+        <v>8983</v>
       </c>
     </row>
     <row r="13">
@@ -961,32 +961,32 @@
         <v>500000</v>
       </c>
       <c r="D13" t="n">
-        <v>262957</v>
+        <v>263772</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>15838</v>
+        <v>45638</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>247119</v>
+        <v>218134</v>
       </c>
       <c r="I13" t="n">
-        <v>55829</v>
+        <v>56246</v>
       </c>
       <c r="J13" t="n">
-        <v>191290</v>
+        <v>161888</v>
       </c>
       <c r="K13" t="n">
-        <v>91457</v>
+        <v>61676</v>
       </c>
     </row>
     <row r="14">
@@ -1004,32 +1004,32 @@
         <v>1900000</v>
       </c>
       <c r="D14" t="n">
-        <v>1465620.4</v>
+        <v>1880717.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>305912</v>
+        <v>314950</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1159708.4</v>
+        <v>1565767.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1016671</v>
+        <v>1295876</v>
       </c>
       <c r="J14" t="n">
-        <v>111868</v>
+        <v>236922</v>
       </c>
       <c r="K14" t="n">
-        <v>1085474</v>
+        <v>1392123</v>
       </c>
     </row>
     <row r="15">
@@ -1047,32 +1047,32 @@
         <v>1000000</v>
       </c>
       <c r="D15" t="n">
-        <v>966916.14</v>
+        <v>1165591.04</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>96.7%</t>
+          <t>116.6%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>114266.59</v>
+        <v>115766.59</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>852649.55</v>
+        <v>1049824.45</v>
       </c>
       <c r="I15" t="n">
-        <v>126849</v>
+        <v>180724</v>
       </c>
       <c r="J15" t="n">
-        <v>704299</v>
+        <v>847599</v>
       </c>
       <c r="K15" t="n">
-        <v>384209</v>
+        <v>443370</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>408765.21</v>
+        <v>556070.89</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>341818.21</v>
+        <v>489123.89</v>
       </c>
       <c r="I16" t="n">
-        <v>97128</v>
+        <v>124122</v>
       </c>
       <c r="J16" t="n">
-        <v>193491</v>
+        <v>312889</v>
       </c>
       <c r="K16" t="n">
-        <v>36030</v>
+        <v>62743</v>
       </c>
     </row>
     <row r="17">
@@ -1133,11 +1133,11 @@
         <v>900000</v>
       </c>
       <c r="D17" t="n">
-        <v>183273</v>
+        <v>244358</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1145,20 +1145,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>144423</v>
+        <v>205508</v>
       </c>
       <c r="I17" t="n">
-        <v>26849</v>
+        <v>47934</v>
       </c>
       <c r="J17" t="n">
-        <v>117574</v>
+        <v>157574</v>
       </c>
       <c r="K17" t="n">
-        <v>41219</v>
+        <v>42304</v>
       </c>
     </row>
     <row r="18">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>881795.39</v>
+        <v>919807.3899999999</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>134561.15</v>
+        <v>134760.15</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>747234.24</v>
+        <v>785047.2399999999</v>
       </c>
       <c r="I2" t="n">
-        <v>714980</v>
+        <v>752774</v>
       </c>
       <c r="J2" t="n">
-        <v>32253</v>
+        <v>32272</v>
       </c>
       <c r="K2" t="n">
-        <v>684174</v>
+        <v>721589</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>383448.41</v>
+        <v>385575.41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>250667.07</v>
+        <v>250956.07</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>132781.34</v>
+        <v>134619.34</v>
       </c>
       <c r="I3" t="n">
-        <v>93565</v>
+        <v>95403</v>
       </c>
       <c r="J3" t="n">
         <v>39215</v>
       </c>
       <c r="K3" t="n">
-        <v>146487</v>
+        <v>147927</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>920969.78</v>
+        <v>964120.78</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>167221.87</v>
+        <v>167325.87</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>753747.91</v>
+        <v>796794.91</v>
       </c>
       <c r="I4" t="n">
-        <v>757467</v>
+        <v>800514</v>
       </c>
       <c r="J4" t="n">
         <v>-3720</v>
       </c>
       <c r="K4" t="n">
-        <v>564565</v>
+        <v>607612</v>
       </c>
     </row>
     <row r="5">
@@ -617,11 +617,11 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>1506000.36</v>
+        <v>1536337.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -629,20 +629,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1146852.82</v>
+        <v>1177189.82</v>
       </c>
       <c r="I5" t="n">
-        <v>924029</v>
+        <v>944366</v>
       </c>
       <c r="J5" t="n">
-        <v>222823</v>
+        <v>232823</v>
       </c>
       <c r="K5" t="n">
-        <v>884206</v>
+        <v>904543</v>
       </c>
     </row>
     <row r="6">
@@ -703,11 +703,11 @@
         <v>2500000</v>
       </c>
       <c r="D7" t="n">
-        <v>1419809.8</v>
+        <v>1498813.799999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -715,20 +715,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1353990.8</v>
+        <v>1432994.799999999</v>
       </c>
       <c r="I7" t="n">
-        <v>560491</v>
+        <v>583091</v>
       </c>
       <c r="J7" t="n">
-        <v>793499</v>
+        <v>849903</v>
       </c>
       <c r="K7" t="n">
-        <v>1319800</v>
+        <v>1398804</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>500000</v>
       </c>
       <c r="D8" t="n">
-        <v>178081.84</v>
+        <v>186081.84</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35.6%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>15857</v>
+        <v>15876</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>162224.84</v>
+        <v>170205.84</v>
       </c>
       <c r="I8" t="n">
-        <v>106431</v>
+        <v>106014</v>
       </c>
       <c r="J8" t="n">
-        <v>55393</v>
+        <v>63791</v>
       </c>
       <c r="K8" t="n">
-        <v>46272</v>
+        <v>46253</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>600000</v>
       </c>
       <c r="D9" t="n">
-        <v>439088</v>
+        <v>439884</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -805,13 +805,13 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>427808</v>
+        <v>428604</v>
       </c>
       <c r="I9" t="n">
-        <v>25442</v>
+        <v>25840</v>
       </c>
       <c r="J9" t="n">
-        <v>402366</v>
+        <v>402764</v>
       </c>
       <c r="K9" t="n">
         <v>106654</v>
@@ -832,11 +832,11 @@
         <v>1000000</v>
       </c>
       <c r="D10" t="n">
-        <v>501128.33</v>
+        <v>517343.33</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -844,20 +844,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>447809.33</v>
+        <v>464024.33</v>
       </c>
       <c r="I10" t="n">
-        <v>43884</v>
+        <v>44501</v>
       </c>
       <c r="J10" t="n">
-        <v>376736</v>
+        <v>392334</v>
       </c>
       <c r="K10" t="n">
-        <v>22663</v>
+        <v>22882</v>
       </c>
     </row>
     <row r="11">
@@ -875,11 +875,11 @@
         <v>1100000</v>
       </c>
       <c r="D11" t="n">
-        <v>705956.27</v>
+        <v>759104.4700000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>69.0%</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -887,20 +887,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>440117.27</v>
+        <v>493265.4700000001</v>
       </c>
       <c r="I11" t="n">
-        <v>115663</v>
+        <v>145720</v>
       </c>
       <c r="J11" t="n">
-        <v>309234</v>
+        <v>329670</v>
       </c>
       <c r="K11" t="n">
-        <v>343359</v>
+        <v>395909</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>108424.8</v>
+        <v>125262.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>31.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>66474.47</v>
+        <v>83312.47</v>
       </c>
       <c r="I12" t="n">
-        <v>-4476</v>
+        <v>-4036</v>
       </c>
       <c r="J12" t="n">
-        <v>70950</v>
+        <v>87348</v>
       </c>
       <c r="K12" t="n">
-        <v>8983</v>
+        <v>9025</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>500000</v>
       </c>
       <c r="D13" t="n">
-        <v>263772</v>
+        <v>264787</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>218134</v>
+        <v>219149</v>
       </c>
       <c r="I13" t="n">
-        <v>56246</v>
+        <v>57261</v>
       </c>
       <c r="J13" t="n">
         <v>161888</v>
       </c>
       <c r="K13" t="n">
-        <v>61676</v>
+        <v>61695</v>
       </c>
     </row>
     <row r="14">
@@ -1004,32 +1004,32 @@
         <v>1900000</v>
       </c>
       <c r="D14" t="n">
-        <v>1880717.1</v>
+        <v>2080770.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>314950</v>
+        <v>314959</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1565767.1</v>
+        <v>1765811.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1295876</v>
+        <v>1361425</v>
       </c>
       <c r="J14" t="n">
-        <v>236922</v>
+        <v>321417</v>
       </c>
       <c r="K14" t="n">
-        <v>1392123</v>
+        <v>1489571</v>
       </c>
     </row>
     <row r="15">
@@ -1047,11 +1047,11 @@
         <v>1000000</v>
       </c>
       <c r="D15" t="n">
-        <v>1165591.04</v>
+        <v>1249760.04</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>116.6%</t>
+          <t>125.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1049824.45</v>
+        <v>1133993.45</v>
       </c>
       <c r="I15" t="n">
-        <v>180724</v>
+        <v>214715</v>
       </c>
       <c r="J15" t="n">
-        <v>847599</v>
+        <v>897777</v>
       </c>
       <c r="K15" t="n">
-        <v>443370</v>
+        <v>485045</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>556070.89</v>
+        <v>614278.62</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>489123.89</v>
+        <v>547331.62</v>
       </c>
       <c r="I16" t="n">
-        <v>124122</v>
+        <v>124922</v>
       </c>
       <c r="J16" t="n">
-        <v>312889</v>
+        <v>369189</v>
       </c>
       <c r="K16" t="n">
-        <v>62743</v>
+        <v>63851</v>
       </c>
     </row>
     <row r="17">
@@ -1133,11 +1133,11 @@
         <v>900000</v>
       </c>
       <c r="D17" t="n">
-        <v>244358</v>
+        <v>306373</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>27.2%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1145,20 +1145,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>205508</v>
+        <v>267523</v>
       </c>
       <c r="I17" t="n">
-        <v>47934</v>
+        <v>39153</v>
       </c>
       <c r="J17" t="n">
-        <v>157574</v>
+        <v>228370</v>
       </c>
       <c r="K17" t="n">
-        <v>42304</v>
+        <v>42323</v>
       </c>
     </row>
     <row r="18">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>919807.3899999999</v>
+        <v>1017174.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>134760.15</v>
+        <v>166896.15</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>785047.2399999999</v>
+        <v>850278.2499999999</v>
       </c>
       <c r="I2" t="n">
-        <v>752774</v>
+        <v>818005</v>
       </c>
       <c r="J2" t="n">
         <v>32272</v>
       </c>
       <c r="K2" t="n">
-        <v>721589</v>
+        <v>805426</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>385575.41</v>
+        <v>442206.41</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>250956.07</v>
+        <v>251409.07</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>134619.34</v>
+        <v>190797.34</v>
       </c>
       <c r="I3" t="n">
-        <v>95403</v>
+        <v>151562</v>
       </c>
       <c r="J3" t="n">
-        <v>39215</v>
+        <v>39234</v>
       </c>
       <c r="K3" t="n">
-        <v>147927</v>
+        <v>203707</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>964120.78</v>
+        <v>1066399.78</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>167325.87</v>
+        <v>175994.87</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>796794.91</v>
+        <v>890404.91</v>
       </c>
       <c r="I4" t="n">
-        <v>800514</v>
+        <v>895804</v>
       </c>
       <c r="J4" t="n">
-        <v>-3720</v>
+        <v>-5400</v>
       </c>
       <c r="K4" t="n">
-        <v>607612</v>
+        <v>701222</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>1536337.36</v>
+        <v>1558573.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>359147.54</v>
+        <v>365747.54</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1177189.82</v>
+        <v>1192825.82</v>
       </c>
       <c r="I5" t="n">
-        <v>944366</v>
+        <v>960002</v>
       </c>
       <c r="J5" t="n">
         <v>232823</v>
       </c>
       <c r="K5" t="n">
-        <v>904543</v>
+        <v>899781</v>
       </c>
     </row>
     <row r="6">
@@ -703,15 +703,15 @@
         <v>2500000</v>
       </c>
       <c r="D7" t="n">
-        <v>1498813.799999999</v>
+        <v>1577089.09</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>65819</v>
+        <v>68819</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -719,16 +719,16 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1432994.799999999</v>
+        <v>1508270.09</v>
       </c>
       <c r="I7" t="n">
-        <v>583091</v>
+        <v>581489</v>
       </c>
       <c r="J7" t="n">
-        <v>849903</v>
+        <v>926781</v>
       </c>
       <c r="K7" t="n">
-        <v>1398804</v>
+        <v>1477080</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>500000</v>
       </c>
       <c r="D8" t="n">
-        <v>186081.84</v>
+        <v>200698.84</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>15876</v>
+        <v>16376</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>170205.84</v>
+        <v>184322.84</v>
       </c>
       <c r="I8" t="n">
-        <v>106014</v>
+        <v>105533</v>
       </c>
       <c r="J8" t="n">
-        <v>63791</v>
+        <v>78389</v>
       </c>
       <c r="K8" t="n">
-        <v>46253</v>
+        <v>45772</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>600000</v>
       </c>
       <c r="D9" t="n">
-        <v>439884</v>
+        <v>449903</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>428604</v>
+        <v>438623</v>
       </c>
       <c r="I9" t="n">
-        <v>25840</v>
+        <v>25859</v>
       </c>
       <c r="J9" t="n">
-        <v>402764</v>
+        <v>412764</v>
       </c>
       <c r="K9" t="n">
-        <v>106654</v>
+        <v>106673</v>
       </c>
     </row>
     <row r="10">
@@ -832,11 +832,11 @@
         <v>1000000</v>
       </c>
       <c r="D10" t="n">
-        <v>517343.33</v>
+        <v>590248.33</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -844,20 +844,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>464024.33</v>
+        <v>536929.33</v>
       </c>
       <c r="I10" t="n">
-        <v>44501</v>
+        <v>44956</v>
       </c>
       <c r="J10" t="n">
-        <v>392334</v>
+        <v>464634</v>
       </c>
       <c r="K10" t="n">
-        <v>22882</v>
+        <v>68889</v>
       </c>
     </row>
     <row r="11">
@@ -875,32 +875,32 @@
         <v>1100000</v>
       </c>
       <c r="D11" t="n">
-        <v>759104.4700000001</v>
+        <v>766457.4700000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>69.0%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>265839</v>
+        <v>265858</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>493265.4700000001</v>
+        <v>500599.4700000001</v>
       </c>
       <c r="I11" t="n">
-        <v>145720</v>
+        <v>132754</v>
       </c>
       <c r="J11" t="n">
-        <v>329670</v>
+        <v>349470</v>
       </c>
       <c r="K11" t="n">
-        <v>395909</v>
+        <v>403243</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>125262.8</v>
+        <v>141376.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>83312.47</v>
+        <v>99426.46999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-4036</v>
+        <v>-3718</v>
       </c>
       <c r="J12" t="n">
-        <v>87348</v>
+        <v>103144</v>
       </c>
       <c r="K12" t="n">
-        <v>9025</v>
+        <v>9343</v>
       </c>
     </row>
     <row r="13">
@@ -961,11 +961,11 @@
         <v>500000</v>
       </c>
       <c r="D13" t="n">
-        <v>264787</v>
+        <v>274768</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -973,20 +973,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>16.6%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>219149</v>
+        <v>229130</v>
       </c>
       <c r="I13" t="n">
-        <v>57261</v>
+        <v>57242</v>
       </c>
       <c r="J13" t="n">
-        <v>161888</v>
+        <v>171888</v>
       </c>
       <c r="K13" t="n">
-        <v>61695</v>
+        <v>61676</v>
       </c>
     </row>
     <row r="14">
@@ -1004,32 +1004,32 @@
         <v>1900000</v>
       </c>
       <c r="D14" t="n">
-        <v>2080770.1</v>
+        <v>2122778.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>111.7%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>314959</v>
+        <v>342899</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1765811.1</v>
+        <v>1779879.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1361425</v>
+        <v>1347095</v>
       </c>
       <c r="J14" t="n">
-        <v>321417</v>
+        <v>349815</v>
       </c>
       <c r="K14" t="n">
-        <v>1489571</v>
+        <v>1465639</v>
       </c>
     </row>
     <row r="15">
@@ -1047,32 +1047,32 @@
         <v>1000000</v>
       </c>
       <c r="D15" t="n">
-        <v>1249760.04</v>
+        <v>1279877.04</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>125.0%</t>
+          <t>128.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>115766.59</v>
+        <v>116966.59</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1133993.45</v>
+        <v>1162910.45</v>
       </c>
       <c r="I15" t="n">
-        <v>214715</v>
+        <v>236434</v>
       </c>
       <c r="J15" t="n">
-        <v>897777</v>
+        <v>904975</v>
       </c>
       <c r="K15" t="n">
-        <v>485045</v>
+        <v>513962</v>
       </c>
     </row>
     <row r="16">
@@ -1090,32 +1090,32 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>614278.62</v>
+        <v>693127.48</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>66947</v>
+        <v>91447</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>547331.62</v>
+        <v>601680.48</v>
       </c>
       <c r="I16" t="n">
-        <v>124922</v>
+        <v>128031</v>
       </c>
       <c r="J16" t="n">
-        <v>369189</v>
+        <v>410089</v>
       </c>
       <c r="K16" t="n">
-        <v>63851</v>
+        <v>75900</v>
       </c>
     </row>
     <row r="17">
@@ -1133,11 +1133,11 @@
         <v>900000</v>
       </c>
       <c r="D17" t="n">
-        <v>306373</v>
+        <v>346889</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1145,20 +1145,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>267523</v>
+        <v>308039</v>
       </c>
       <c r="I17" t="n">
-        <v>39153</v>
+        <v>69271</v>
       </c>
       <c r="J17" t="n">
-        <v>228370</v>
+        <v>238768</v>
       </c>
       <c r="K17" t="n">
-        <v>42323</v>
+        <v>62441</v>
       </c>
     </row>
     <row r="18">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>1017174.4</v>
+        <v>1151853.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>166896.15</v>
+        <v>193989.15</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>850278.2499999999</v>
+        <v>957864.2499999999</v>
       </c>
       <c r="I2" t="n">
-        <v>818005</v>
+        <v>942092</v>
       </c>
       <c r="J2" t="n">
-        <v>32272</v>
+        <v>15771</v>
       </c>
       <c r="K2" t="n">
-        <v>805426</v>
+        <v>903012</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>442206.41</v>
+        <v>453012.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>251409.07</v>
+        <v>275426.07</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>190797.34</v>
+        <v>177586.33</v>
       </c>
       <c r="I3" t="n">
-        <v>151562</v>
+        <v>133371</v>
       </c>
       <c r="J3" t="n">
-        <v>39234</v>
+        <v>44214</v>
       </c>
       <c r="K3" t="n">
-        <v>203707</v>
+        <v>213996</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>1066399.78</v>
+        <v>1125699.78</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>175994.87</v>
+        <v>176540.87</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.5%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>890404.91</v>
+        <v>949158.91</v>
       </c>
       <c r="I4" t="n">
-        <v>895804</v>
+        <v>954259</v>
       </c>
       <c r="J4" t="n">
-        <v>-5400</v>
+        <v>-5101</v>
       </c>
       <c r="K4" t="n">
-        <v>701222</v>
+        <v>759976</v>
       </c>
     </row>
     <row r="5">
@@ -617,11 +617,11 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>1558573.36</v>
+        <v>1635045.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>102.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -629,20 +629,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1192825.82</v>
+        <v>1269297.82</v>
       </c>
       <c r="I5" t="n">
-        <v>960002</v>
+        <v>1016674</v>
       </c>
       <c r="J5" t="n">
-        <v>232823</v>
+        <v>252623</v>
       </c>
       <c r="K5" t="n">
-        <v>899781</v>
+        <v>927433</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>1300000</v>
       </c>
       <c r="D6" t="n">
-        <v>549614</v>
+        <v>692174</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>44760</v>
+        <v>44940</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>504854</v>
+        <v>647234</v>
       </c>
       <c r="I6" t="n">
-        <v>503774</v>
+        <v>642194</v>
       </c>
       <c r="J6" t="n">
-        <v>1080</v>
+        <v>5040</v>
       </c>
       <c r="K6" t="n">
-        <v>445860</v>
+        <v>568440</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>2500000</v>
       </c>
       <c r="D7" t="n">
-        <v>1577089.09</v>
+        <v>1590885.09</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>68819</v>
+        <v>74819</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1508270.09</v>
+        <v>1516066.09</v>
       </c>
       <c r="I7" t="n">
-        <v>581489</v>
+        <v>591489</v>
       </c>
       <c r="J7" t="n">
-        <v>926781</v>
+        <v>924577</v>
       </c>
       <c r="K7" t="n">
-        <v>1477080</v>
+        <v>1490478</v>
       </c>
     </row>
     <row r="8">
@@ -746,11 +746,11 @@
         <v>500000</v>
       </c>
       <c r="D8" t="n">
-        <v>200698.84</v>
+        <v>211296.84</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -758,17 +758,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>184322.84</v>
+        <v>194920.84</v>
       </c>
       <c r="I8" t="n">
         <v>105533</v>
       </c>
       <c r="J8" t="n">
-        <v>78389</v>
+        <v>88987</v>
       </c>
       <c r="K8" t="n">
         <v>45772</v>
@@ -789,32 +789,32 @@
         <v>600000</v>
       </c>
       <c r="D9" t="n">
-        <v>449903</v>
+        <v>516522</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>86.1%</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>11280</v>
+        <v>20280</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>438623</v>
+        <v>496242</v>
       </c>
       <c r="I9" t="n">
-        <v>25859</v>
+        <v>45678</v>
       </c>
       <c r="J9" t="n">
-        <v>412764</v>
+        <v>450564</v>
       </c>
       <c r="K9" t="n">
-        <v>106673</v>
+        <v>163292</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>1000000</v>
       </c>
       <c r="D10" t="n">
-        <v>590248.33</v>
+        <v>668540.33</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>53319</v>
+        <v>61319</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>536929.33</v>
+        <v>607221.33</v>
       </c>
       <c r="I10" t="n">
-        <v>44956</v>
+        <v>59956</v>
       </c>
       <c r="J10" t="n">
-        <v>464634</v>
+        <v>519926</v>
       </c>
       <c r="K10" t="n">
-        <v>68889</v>
+        <v>68983</v>
       </c>
     </row>
     <row r="11">
@@ -875,7 +875,7 @@
         <v>1100000</v>
       </c>
       <c r="D11" t="n">
-        <v>766457.4700000001</v>
+        <v>767192.6200000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -883,24 +883,24 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>265858</v>
+        <v>267838</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>500599.4700000001</v>
+        <v>499354.6200000001</v>
       </c>
       <c r="I11" t="n">
-        <v>132754</v>
+        <v>131429</v>
       </c>
       <c r="J11" t="n">
         <v>349470</v>
       </c>
       <c r="K11" t="n">
-        <v>403243</v>
+        <v>401400</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>141376.8</v>
+        <v>149089.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>99426.46999999999</v>
+        <v>107139.47</v>
       </c>
       <c r="I12" t="n">
-        <v>-3718</v>
+        <v>-2801</v>
       </c>
       <c r="J12" t="n">
-        <v>103144</v>
+        <v>109940</v>
       </c>
       <c r="K12" t="n">
-        <v>9343</v>
+        <v>9862</v>
       </c>
     </row>
     <row r="13">
@@ -961,32 +961,32 @@
         <v>500000</v>
       </c>
       <c r="D13" t="n">
-        <v>274768</v>
+        <v>294568</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>45638</v>
+        <v>49238</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>229130</v>
+        <v>245330</v>
       </c>
       <c r="I13" t="n">
-        <v>57242</v>
+        <v>77042</v>
       </c>
       <c r="J13" t="n">
-        <v>171888</v>
+        <v>168288</v>
       </c>
       <c r="K13" t="n">
-        <v>61676</v>
+        <v>81476</v>
       </c>
     </row>
     <row r="14">
@@ -1004,32 +1004,32 @@
         <v>1900000</v>
       </c>
       <c r="D14" t="n">
-        <v>2122778.1</v>
+        <v>2142791.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>111.7%</t>
+          <t>112.8%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>342899</v>
+        <v>359718</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1779879.1</v>
+        <v>1783073.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1347095</v>
+        <v>1334293</v>
       </c>
       <c r="J14" t="n">
-        <v>349815</v>
+        <v>365811</v>
       </c>
       <c r="K14" t="n">
-        <v>1465639</v>
+        <v>1452837</v>
       </c>
     </row>
     <row r="15">
@@ -1047,32 +1047,32 @@
         <v>1000000</v>
       </c>
       <c r="D15" t="n">
-        <v>1279877.04</v>
+        <v>1312030.18</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>128.0%</t>
+          <t>131.2%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>116966.59</v>
+        <v>168085.59</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1162910.45</v>
+        <v>1143944.59</v>
       </c>
       <c r="I15" t="n">
-        <v>236434</v>
+        <v>209412</v>
       </c>
       <c r="J15" t="n">
-        <v>904975</v>
+        <v>913031</v>
       </c>
       <c r="K15" t="n">
-        <v>513962</v>
+        <v>489700</v>
       </c>
     </row>
     <row r="16">
@@ -1090,11 +1090,11 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>693127.48</v>
+        <v>733442.48</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1102,20 +1102,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>601680.48</v>
+        <v>641995.48</v>
       </c>
       <c r="I16" t="n">
-        <v>128031</v>
+        <v>134846</v>
       </c>
       <c r="J16" t="n">
-        <v>410089</v>
+        <v>443589</v>
       </c>
       <c r="K16" t="n">
-        <v>75900</v>
+        <v>75919</v>
       </c>
     </row>
     <row r="17">
@@ -1133,32 +1133,32 @@
         <v>900000</v>
       </c>
       <c r="D17" t="n">
-        <v>346889</v>
+        <v>358083</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>38850</v>
+        <v>53269</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>308039</v>
+        <v>304814</v>
       </c>
       <c r="I17" t="n">
-        <v>69271</v>
+        <v>69650</v>
       </c>
       <c r="J17" t="n">
-        <v>238768</v>
+        <v>235164</v>
       </c>
       <c r="K17" t="n">
-        <v>62441</v>
+        <v>62422</v>
       </c>
     </row>
     <row r="18">

--- a/导出_按分组.xlsx
+++ b/导出_按分组.xlsx
@@ -488,32 +488,32 @@
         <v>1450000</v>
       </c>
       <c r="D2" t="n">
-        <v>1151853.4</v>
+        <v>1374062.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>193989.15</v>
+        <v>243970.15</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>957864.2499999999</v>
+        <v>1130092.25</v>
       </c>
       <c r="I2" t="n">
-        <v>942092</v>
+        <v>1100341</v>
       </c>
       <c r="J2" t="n">
-        <v>15771</v>
+        <v>29750</v>
       </c>
       <c r="K2" t="n">
-        <v>903012</v>
+        <v>1016866</v>
       </c>
     </row>
     <row r="3">
@@ -531,32 +531,32 @@
         <v>1450000</v>
       </c>
       <c r="D3" t="n">
-        <v>453012.4</v>
+        <v>571005.39</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>275426.07</v>
+        <v>426148.0699999999</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>177586.33</v>
+        <v>144857.3200000001</v>
       </c>
       <c r="I3" t="n">
-        <v>133371</v>
+        <v>94042</v>
       </c>
       <c r="J3" t="n">
-        <v>44214</v>
+        <v>50814</v>
       </c>
       <c r="K3" t="n">
-        <v>213996</v>
+        <v>201869</v>
       </c>
     </row>
     <row r="4">
@@ -574,32 +574,32 @@
         <v>1400000</v>
       </c>
       <c r="D4" t="n">
-        <v>1125699.78</v>
+        <v>1248222.37</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>176540.87</v>
+        <v>199952.87</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>949158.91</v>
+        <v>1048269.5</v>
       </c>
       <c r="I4" t="n">
-        <v>954259</v>
+        <v>1055050</v>
       </c>
       <c r="J4" t="n">
-        <v>-5101</v>
+        <v>-6781</v>
       </c>
       <c r="K4" t="n">
-        <v>759976</v>
+        <v>859087</v>
       </c>
     </row>
     <row r="5">
@@ -617,32 +617,32 @@
         <v>1600000</v>
       </c>
       <c r="D5" t="n">
-        <v>1635045.36</v>
+        <v>1893422.36</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>102.2%</t>
+          <t>118.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>365747.54</v>
+        <v>449505.54</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1269297.82</v>
+        <v>1443916.82</v>
       </c>
       <c r="I5" t="n">
-        <v>1016674</v>
+        <v>1191773</v>
       </c>
       <c r="J5" t="n">
-        <v>252623</v>
+        <v>252143</v>
       </c>
       <c r="K5" t="n">
-        <v>927433</v>
+        <v>942972</v>
       </c>
     </row>
     <row r="6">
@@ -660,32 +660,32 @@
         <v>1300000</v>
       </c>
       <c r="D6" t="n">
-        <v>692174</v>
+        <v>827354</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>44940</v>
+        <v>46900</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>647234</v>
+        <v>780454</v>
       </c>
       <c r="I6" t="n">
-        <v>642194</v>
+        <v>775414</v>
       </c>
       <c r="J6" t="n">
         <v>5040</v>
       </c>
       <c r="K6" t="n">
-        <v>568440</v>
+        <v>657860</v>
       </c>
     </row>
     <row r="7">
@@ -703,32 +703,32 @@
         <v>2500000</v>
       </c>
       <c r="D7" t="n">
-        <v>1590885.09</v>
+        <v>1753603.389999999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>74819</v>
+        <v>95619</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1516066.09</v>
+        <v>1657984.389999999</v>
       </c>
       <c r="I7" t="n">
-        <v>591489</v>
+        <v>643391</v>
       </c>
       <c r="J7" t="n">
-        <v>924577</v>
+        <v>1014593</v>
       </c>
       <c r="K7" t="n">
-        <v>1490478</v>
+        <v>1631998</v>
       </c>
     </row>
     <row r="8">
@@ -746,32 +746,32 @@
         <v>500000</v>
       </c>
       <c r="D8" t="n">
-        <v>211296.84</v>
+        <v>272888.84</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>16376</v>
+        <v>21793</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>194920.84</v>
+        <v>251095.84</v>
       </c>
       <c r="I8" t="n">
-        <v>105533</v>
+        <v>106310</v>
       </c>
       <c r="J8" t="n">
-        <v>88987</v>
+        <v>144385</v>
       </c>
       <c r="K8" t="n">
-        <v>45772</v>
+        <v>45753</v>
       </c>
     </row>
     <row r="9">
@@ -789,11 +789,11 @@
         <v>600000</v>
       </c>
       <c r="D9" t="n">
-        <v>516522</v>
+        <v>532508</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>86.1%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -801,20 +801,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>496242</v>
+        <v>512228</v>
       </c>
       <c r="I9" t="n">
-        <v>45678</v>
+        <v>46474</v>
       </c>
       <c r="J9" t="n">
-        <v>450564</v>
+        <v>465754</v>
       </c>
       <c r="K9" t="n">
-        <v>163292</v>
+        <v>176492</v>
       </c>
     </row>
     <row r="10">
@@ -832,32 +832,32 @@
         <v>1000000</v>
       </c>
       <c r="D10" t="n">
-        <v>668540.33</v>
+        <v>778254.72</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>61319</v>
+        <v>66538</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>607221.33</v>
+        <v>711716.72</v>
       </c>
       <c r="I10" t="n">
-        <v>59956</v>
+        <v>96290</v>
       </c>
       <c r="J10" t="n">
-        <v>519926</v>
+        <v>585220</v>
       </c>
       <c r="K10" t="n">
-        <v>68983</v>
+        <v>71468</v>
       </c>
     </row>
     <row r="11">
@@ -875,32 +875,32 @@
         <v>1100000</v>
       </c>
       <c r="D11" t="n">
-        <v>767192.6200000001</v>
+        <v>779274.0200000001</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>267838</v>
+        <v>292338</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>499354.6200000001</v>
+        <v>486936.0200000001</v>
       </c>
       <c r="I11" t="n">
-        <v>131429</v>
+        <v>128083</v>
       </c>
       <c r="J11" t="n">
-        <v>349470</v>
+        <v>338550</v>
       </c>
       <c r="K11" t="n">
-        <v>401400</v>
+        <v>413084</v>
       </c>
     </row>
     <row r="12">
@@ -918,11 +918,11 @@
         <v>400000</v>
       </c>
       <c r="D12" t="n">
-        <v>149089.8</v>
+        <v>158961.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -930,20 +930,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>107139.47</v>
+        <v>117011.47</v>
       </c>
       <c r="I12" t="n">
-        <v>-2801</v>
+        <v>-1929</v>
       </c>
       <c r="J12" t="n">
-        <v>109940</v>
+        <v>118940</v>
       </c>
       <c r="K12" t="n">
-        <v>9862</v>
+        <v>9938</v>
       </c>
     </row>
     <row r="13">
@@ -961,29 +961,29 @@
         <v>500000</v>
       </c>
       <c r="D13" t="n">
-        <v>294568</v>
+        <v>301781</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>49238</v>
+        <v>49257</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>245330</v>
+        <v>252524</v>
       </c>
       <c r="I13" t="n">
-        <v>77042</v>
+        <v>77838</v>
       </c>
       <c r="J13" t="n">
-        <v>168288</v>
+        <v>174686</v>
       </c>
       <c r="K13" t="n">
         <v>81476</v>
@@ -1004,32 +1004,32 @@
         <v>1900000</v>
       </c>
       <c r="D14" t="n">
-        <v>2142791.1</v>
+        <v>2355634.46</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>112.8%</t>
+          <t>124.0%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>359718</v>
+        <v>463642</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1783073.1</v>
+        <v>1891992.46</v>
       </c>
       <c r="I14" t="n">
-        <v>1334293</v>
+        <v>1360400</v>
       </c>
       <c r="J14" t="n">
-        <v>365811</v>
+        <v>449259</v>
       </c>
       <c r="K14" t="n">
-        <v>1452837</v>
+        <v>1461558</v>
       </c>
     </row>
     <row r="15">
@@ -1047,32 +1047,32 @@
         <v>1000000</v>
       </c>
       <c r="D15" t="n">
-        <v>1312030.18</v>
+        <v>1434096.68</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>131.2%</t>
+          <t>143.4%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>168085.59</v>
+        <v>177085.59</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1143944.59</v>
+        <v>1257011.09</v>
       </c>
       <c r="I15" t="n">
-        <v>209412</v>
+        <v>240246</v>
       </c>
       <c r="J15" t="n">
-        <v>913031</v>
+        <v>995264</v>
       </c>
       <c r="K15" t="n">
-        <v>489700</v>
+        <v>559665</v>
       </c>
     </row>
     <row r="16">
@@ -1090,32 +1090,32 @@
         <v>900000</v>
       </c>
       <c r="D16" t="n">
-        <v>733442.48</v>
+        <v>813680.04</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>91447</v>
+        <v>113466</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>641995.48</v>
+        <v>700214.04</v>
       </c>
       <c r="I16" t="n">
-        <v>134846</v>
+        <v>156827</v>
       </c>
       <c r="J16" t="n">
-        <v>443589</v>
+        <v>471387</v>
       </c>
       <c r="K16" t="n">
-        <v>75919</v>
+        <v>104140</v>
       </c>
     </row>
     <row r="17">
@@ -1133,32 +1133,32 @@
         <v>900000</v>
       </c>
       <c r="D17" t="n">
-        <v>358083</v>
+        <v>447052</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>53269</v>
+        <v>63686</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>304814</v>
+        <v>383366</v>
       </c>
       <c r="I17" t="n">
-        <v>69650</v>
+        <v>81212</v>
       </c>
       <c r="J17" t="n">
-        <v>235164</v>
+        <v>302154</v>
       </c>
       <c r="K17" t="n">
-        <v>62422</v>
+        <v>68984</v>
       </c>
     </row>
     <row r="18">
@@ -1184,24 +1184,24 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>13377</v>
+        <v>25057</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>19642.8</v>
+        <v>7962.800000000003</v>
       </c>
       <c r="I18" t="n">
-        <v>19461</v>
+        <v>7781</v>
       </c>
       <c r="J18" t="n">
         <v>181</v>
       </c>
       <c r="K18" t="n">
-        <v>6142</v>
+        <v>4462</v>
       </c>
     </row>
   </sheetData>
